--- a/セリフ編集/キャラタイプ別/鷹揚×ノーマル.xlsx
+++ b/セリフ編集/キャラタイプ別/鷹揚×ノーマル.xlsx
@@ -411,7 +411,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H272"/>
+  <dimension ref="A1:H294"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1717,7 +1717,7 @@
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.normal.composed[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.normal.composed[1]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D41" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.normal.composed[1]</t>
+          <t xml:space="preserve">ahead.normal.composed[1]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr" s="2">
@@ -1742,14 +1742,14 @@
       </c>
       <c r="F41" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…認めない。…これで終わりだと思うなよ</t>
+          <t xml:space="preserve">…決着はついてる。…なのに、まだ喉に引っかかってる</t>
         </is>
       </c>
     </row>
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.normal.composed[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.normal.composed[1]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D42" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.normal.composed[1]</t>
+          <t xml:space="preserve">behind.normal.composed[1]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr" s="2">
@@ -1774,14 +1774,14 @@
       </c>
       <c r="F42" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…終わった。…もう、いいだろう</t>
+          <t xml:space="preserve">…片がついたらしいよ。…誰の中で、って話だけど</t>
         </is>
       </c>
     </row>
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.normal.composed[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.normal.composed[1]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D43" t="inlineStr" s="12">
@@ -1806,14 +1806,14 @@
       </c>
       <c r="F43" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…負けたか。…でも、悪くない。あんたが相手でよかった</t>
+          <t xml:space="preserve">…認めない。…これで終わりだと思うなよ</t>
         </is>
       </c>
     </row>
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.normal.composed[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.normal.composed[1]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D44" t="inlineStr" s="12">
@@ -1838,14 +1838,14 @@
       </c>
       <c r="F44" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あんたがいたから、ここまで来れた。……ありがとう</t>
+          <t xml:space="preserve">…終わった。…もう、いいだろう</t>
         </is>
       </c>
     </row>
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.normal.composed[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.normal.composed[1]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1855,12 +1855,12 @@
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D45" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.normal.composed[1]</t>
+          <t xml:space="preserve">loser.normal.composed[1]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr" s="2">
@@ -1870,14 +1870,14 @@
       </c>
       <c r="F45" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…逃がさないよ。ここで終わらせる</t>
+          <t xml:space="preserve">…負けたか。…でも、悪くない。あんたが相手でよかった</t>
         </is>
       </c>
     </row>
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.normal.composed[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.normal.composed[1]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.normal.composed[1]</t>
+          <t xml:space="preserve">winner.normal.composed[1]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr" s="2">
@@ -1902,14 +1902,14 @@
       </c>
       <c r="F46" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いいよ。来なよ</t>
+          <t xml:space="preserve">…あんたがいたから、ここまで来れた。……ありがとう</t>
         </is>
       </c>
     </row>
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.normal.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.normal.composed[1]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
         </is>
       </c>
       <c r="D47" t="inlineStr" s="12">
@@ -1934,14 +1934,14 @@
       </c>
       <c r="F47" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この日を待ってた</t>
+          <t xml:space="preserve">…逃がさないよ。ここで終わらせる</t>
         </is>
       </c>
     </row>
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.normal.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.normal.composed[1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
         </is>
       </c>
       <c r="D48" t="inlineStr" s="12">
@@ -1966,14 +1966,14 @@
       </c>
       <c r="F48" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ええ。…もう言葉はいらない</t>
+          <t xml:space="preserve">…いいよ。来なよ</t>
         </is>
       </c>
     </row>
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.normal.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.normal.composed[1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
         </is>
       </c>
       <c r="D49" t="inlineStr" s="12">
@@ -1998,14 +1998,14 @@
       </c>
       <c r="F49" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そろそろ、決着をつけようか</t>
+          <t xml:space="preserve">…この日を待ってた</t>
         </is>
       </c>
     </row>
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.normal.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.normal.composed[1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
         </is>
       </c>
       <c r="D50" t="inlineStr" s="12">
@@ -2030,14 +2030,14 @@
       </c>
       <c r="F50" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いいよ。来なよ</t>
+          <t xml:space="preserve">…ええ。…もう言葉はいらない</t>
         </is>
       </c>
     </row>
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.normal.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.normal.composed[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateAttacker.normal.composed[1]</t>
+          <t xml:space="preserve">attacker.normal.composed[1]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr" s="2">
@@ -2062,14 +2062,14 @@
       </c>
       <c r="F51" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…長かったね。…今日で終わりにしよう</t>
+          <t xml:space="preserve">…そろそろ、決着をつけようか</t>
         </is>
       </c>
     </row>
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.normal.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.normal.composed[1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateDefender.normal.composed[1]</t>
+          <t xml:space="preserve">defender.normal.composed[1]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr" s="2">
@@ -2094,14 +2094,14 @@
       </c>
       <c r="F52" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…うん。…最高の結末にしよう</t>
+          <t xml:space="preserve">…いいよ。来なよ</t>
         </is>
       </c>
     </row>
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.normal.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.normal.composed[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
         </is>
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.normal.composed[1]</t>
+          <t xml:space="preserve">fateAttacker.normal.composed[1]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr" s="2">
@@ -2126,14 +2126,14 @@
       </c>
       <c r="F53" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…次は負けない</t>
+          <t xml:space="preserve">…長かったね。…今日で終わりにしよう</t>
         </is>
       </c>
     </row>
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.normal.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.normal.composed[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -2143,12 +2143,12 @@
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
         </is>
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.normal.composed[1]</t>
+          <t xml:space="preserve">fateDefender.normal.composed[1]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr" s="2">
@@ -2158,14 +2158,14 @@
       </c>
       <c r="F54" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ終わってない。次もあるよ</t>
+          <t xml:space="preserve">…うん。…最高の結末にしよう</t>
         </is>
       </c>
     </row>
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.normal.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.normal.composed[1]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
         </is>
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateLoser.normal.composed[1]</t>
+          <t xml:space="preserve">loserLines.normal.composed[1]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr" s="2">
@@ -2190,14 +2190,14 @@
       </c>
       <c r="F55" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…敵わなかった。…でも、これで終わりじゃない</t>
+          <t xml:space="preserve">…次は負けない</t>
         </is>
       </c>
     </row>
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.normal.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.normal.composed[1]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -2207,12 +2207,12 @@
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
         </is>
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateWinner.normal.composed[1]</t>
+          <t xml:space="preserve">winnerLines.normal.composed[1]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr" s="2">
@@ -2222,14 +2222,14 @@
       </c>
       <c r="F56" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ようやく一つ答えが出た。…でも、まだ終わらないだろうね</t>
+          <t xml:space="preserve">…まだ終わってない。次もあるよ</t>
         </is>
       </c>
     </row>
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.normal.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.normal.composed[1]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.normal.composed[1]</t>
+          <t xml:space="preserve">fateLoser.normal.composed[1]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr" s="2">
@@ -2254,14 +2254,14 @@
       </c>
       <c r="F57" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…負けたか。…でも、これで終わりじゃないよ</t>
+          <t xml:space="preserve">…敵わなかった。…でも、これで終わりじゃない</t>
         </is>
       </c>
     </row>
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.normal.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.normal.composed[1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.normal.composed[1]</t>
+          <t xml:space="preserve">fateWinner.normal.composed[1]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr" s="2">
@@ -2286,14 +2286,14 @@
       </c>
       <c r="F58" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一つ片がついた。…でも、まだ終わった気はしないね</t>
+          <t xml:space="preserve">…ようやく一つ答えが出た。…でも、まだ終わらないだろうね</t>
         </is>
       </c>
     </row>
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.normal.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.normal.composed[1]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.normal.composed[1]</t>
+          <t xml:space="preserve">loser.normal.composed[1]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr" s="2">
@@ -2318,14 +2318,14 @@
       </c>
       <c r="F59" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…こんなことが。…信じられない</t>
+          <t xml:space="preserve">…負けたか。…でも、これで終わりじゃないよ</t>
         </is>
       </c>
     </row>
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.normal.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.normal.composed[1]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D60" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.normal.composed[1]</t>
+          <t xml:space="preserve">winner.normal.composed[1]</t>
         </is>
       </c>
       <c r="E60" t="inlineStr" s="2">
@@ -2350,14 +2350,14 @@
       </c>
       <c r="F60" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…これが答えだよ。…もう格下なんて言わせない</t>
+          <t xml:space="preserve">…一つ片がついた。…でも、まだ終わった気はしないね</t>
         </is>
       </c>
     </row>
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.normal.composed[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.normal.composed[1]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -2367,12 +2367,12 @@
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
         </is>
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">awakening.normal.composed[1]</t>
+          <t xml:space="preserve">loserLines.normal.composed[1]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr" s="2">
@@ -2382,14 +2382,14 @@
       </c>
       <c r="F61" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameB}の表情が静かに変わった。「…そう。…なら、こちらも覚悟を決めるよ」</t>
+          <t xml:space="preserve">…こんなことが。…信じられない</t>
         </is>
       </c>
     </row>
     <row r="62" ht="40" customHeight="1">
       <c r="A62" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_normal.lose[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.normal.composed[1]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
@@ -2399,29 +2399,29 @@
       </c>
       <c r="C62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
         </is>
       </c>
       <c r="D62" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_normal.lose[1]</t>
+          <t xml:space="preserve">winnerLines.normal.composed[1]</t>
         </is>
       </c>
       <c r="E62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">03 因縁・絆(Bond/Rivalry)イベント</t>
         </is>
       </c>
       <c r="F62" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……負けました。すみません。</t>
+          <t xml:space="preserve">…これが答えだよ。…もう格下なんて言わせない</t>
         </is>
       </c>
     </row>
     <row r="63" ht="40" customHeight="1">
       <c r="A63" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_normal.lose[2]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.normal.composed[1]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
@@ -2431,29 +2431,29 @@
       </c>
       <c r="C63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
         </is>
       </c>
       <c r="D63" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_normal.lose[2]</t>
+          <t xml:space="preserve">awakening.normal.composed[1]</t>
         </is>
       </c>
       <c r="E63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">03 因縁・絆(Bond/Rivalry)イベント</t>
         </is>
       </c>
       <c r="F63" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">完敗です。……悔しいですね、やっぱり。</t>
+          <t xml:space="preserve">{nameB}の表情が静かに変わった。「…そう。…なら、こちらも覚悟を決めるよ」</t>
         </is>
       </c>
     </row>
     <row r="64" ht="40" customHeight="1">
       <c r="A64" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_normal.lose[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_normal.lose[1]</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="2">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="D64" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_normal.lose[3]</t>
+          <t xml:space="preserve">composed_normal.lose[1]</t>
         </is>
       </c>
       <c r="E64" t="inlineStr" s="2">
@@ -2478,14 +2478,14 @@
       </c>
       <c r="F64" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てませんでした。……ご迷惑を、かけました。</t>
+          <t xml:space="preserve">……負けました。すみません。</t>
         </is>
       </c>
     </row>
     <row r="65" ht="40" customHeight="1">
       <c r="A65" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_normal.petition[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_normal.lose[2]</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="2">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="D65" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_normal.petition[1]</t>
+          <t xml:space="preserve">composed_normal.lose[2]</t>
         </is>
       </c>
       <c r="E65" t="inlineStr" s="2">
@@ -2510,14 +2510,14 @@
       </c>
       <c r="F65" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。……頼みがあります。あの人と、やらせてください。</t>
+          <t xml:space="preserve">完敗です。……悔しいですね、やっぱり。</t>
         </is>
       </c>
     </row>
     <row r="66" ht="40" customHeight="1">
       <c r="A66" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_normal.petition[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_normal.lose[3]</t>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="2">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="D66" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_normal.petition[2]</t>
+          <t xml:space="preserve">composed_normal.lose[3]</t>
         </is>
       </c>
       <c r="E66" t="inlineStr" s="2">
@@ -2542,14 +2542,14 @@
       </c>
       <c r="F66" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人と、一度やってみたい。……それだけなんです。</t>
+          <t xml:space="preserve">勝てませんでした。……ご迷惑を、かけました。</t>
         </is>
       </c>
     </row>
     <row r="67" ht="40" customHeight="1">
       <c r="A67" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_normal.petition[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_normal.petition[1]</t>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="2">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="D67" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_normal.petition[3]</t>
+          <t xml:space="preserve">composed_normal.petition[1]</t>
         </is>
       </c>
       <c r="E67" t="inlineStr" s="2">
@@ -2574,14 +2574,14 @@
       </c>
       <c r="F67" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">無茶を言ってる自覚はあります。……それでも、お願いします。</t>
+          <t xml:space="preserve">社長。……頼みがあります。あの人と、やらせてください。</t>
         </is>
       </c>
     </row>
     <row r="68" ht="40" customHeight="1">
       <c r="A68" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_normal.sendoff[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_normal.petition[2]</t>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="2">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="D68" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_normal.sendoff[1]</t>
+          <t xml:space="preserve">composed_normal.petition[2]</t>
         </is>
       </c>
       <c r="E68" t="inlineStr" s="2">
@@ -2606,14 +2606,14 @@
       </c>
       <c r="F68" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。……行ってきます。</t>
+          <t xml:space="preserve">あの人と、一度やってみたい。……それだけなんです。</t>
         </is>
       </c>
     </row>
     <row r="69" ht="40" customHeight="1">
       <c r="A69" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_normal.sendoff[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_normal.petition[3]</t>
         </is>
       </c>
       <c r="B69" t="inlineStr" s="2">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="D69" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_normal.sendoff[2]</t>
+          <t xml:space="preserve">composed_normal.petition[3]</t>
         </is>
       </c>
       <c r="E69" t="inlineStr" s="2">
@@ -2638,14 +2638,14 @@
       </c>
       <c r="F69" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">感謝します。……ちゃんと、勝って帰りますよ。</t>
+          <t xml:space="preserve">無茶を言ってる自覚はあります。……それでも、お願いします。</t>
         </is>
       </c>
     </row>
     <row r="70" ht="40" customHeight="1">
       <c r="A70" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_normal.sendoff[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_normal.sendoff[1]</t>
         </is>
       </c>
       <c r="B70" t="inlineStr" s="2">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="D70" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_normal.sendoff[3]</t>
+          <t xml:space="preserve">composed_normal.sendoff[1]</t>
         </is>
       </c>
       <c r="E70" t="inlineStr" s="2">
@@ -2670,14 +2670,14 @@
       </c>
       <c r="F70" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……助かります。任せてください。</t>
+          <t xml:space="preserve">ありがとうございます。……行ってきます。</t>
         </is>
       </c>
     </row>
     <row r="71" ht="40" customHeight="1">
       <c r="A71" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_normal.win[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_normal.sendoff[2]</t>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="2">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="D71" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_normal.win[1]</t>
+          <t xml:space="preserve">composed_normal.sendoff[2]</t>
         </is>
       </c>
       <c r="E71" t="inlineStr" s="2">
@@ -2702,14 +2702,14 @@
       </c>
       <c r="F71" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ちました。……ありがとうございました。</t>
+          <t xml:space="preserve">感謝します。……ちゃんと、勝って帰りますよ。</t>
         </is>
       </c>
     </row>
     <row r="72" ht="40" customHeight="1">
       <c r="A72" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_normal.win[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_normal.sendoff[3]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr" s="2">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="D72" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_normal.win[2]</t>
+          <t xml:space="preserve">composed_normal.sendoff[3]</t>
         </is>
       </c>
       <c r="E72" t="inlineStr" s="2">
@@ -2734,14 +2734,14 @@
       </c>
       <c r="F72" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ま、こんなものかな。社長、感謝します。</t>
+          <t xml:space="preserve">……助かります。任せてください。</t>
         </is>
       </c>
     </row>
     <row r="73" ht="40" customHeight="1">
       <c r="A73" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_normal.win[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_normal.win[1]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="2">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D73" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_normal.win[3]</t>
+          <t xml:space="preserve">composed_normal.win[1]</t>
         </is>
       </c>
       <c r="E73" t="inlineStr" s="2">
@@ -2766,14 +2766,14 @@
       </c>
       <c r="F73" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てました。……言い出して、よかった。</t>
+          <t xml:space="preserve">勝ちました。……ありがとうございました。</t>
         </is>
       </c>
     </row>
     <row r="74" ht="40" customHeight="1">
       <c r="A74" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_normal._accept[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_normal.win[2]</t>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="2">
@@ -2783,12 +2783,12 @@
       </c>
       <c r="C74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D74" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_normal._accept[1]</t>
+          <t xml:space="preserve">composed_normal.win[2]</t>
         </is>
       </c>
       <c r="E74" t="inlineStr" s="2">
@@ -2798,14 +2798,14 @@
       </c>
       <c r="F74" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……いいよ。受けて立つ。</t>
+          <t xml:space="preserve">……ま、こんなものかな。社長、感謝します。</t>
         </is>
       </c>
     </row>
     <row r="75" ht="40" customHeight="1">
       <c r="A75" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_normal._accept[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_normal.win[3]</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="2">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="C75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D75" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_normal._accept[2]</t>
+          <t xml:space="preserve">composed_normal.win[3]</t>
         </is>
       </c>
       <c r="E75" t="inlineStr" s="2">
@@ -2830,14 +2830,14 @@
       </c>
       <c r="F75" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">名前を呼ばれたなら、応えないとね。</t>
+          <t xml:space="preserve">勝てました。……言い出して、よかった。</t>
         </is>
       </c>
     </row>
     <row r="76" ht="40" customHeight="1">
       <c r="A76" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_normal._accept[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_normal._accept[1]</t>
         </is>
       </c>
       <c r="B76" t="inlineStr" s="2">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="D76" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_normal._accept[3]</t>
+          <t xml:space="preserve">composed_normal._accept[1]</t>
         </is>
       </c>
       <c r="E76" t="inlineStr" s="2">
@@ -2862,14 +2862,14 @@
       </c>
       <c r="F76" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そう来たか。まあ、来なよ。</t>
+          <t xml:space="preserve">……いいよ。受けて立つ。</t>
         </is>
       </c>
     </row>
     <row r="77" ht="40" customHeight="1">
       <c r="A77" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_normal.draw[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_normal._accept[2]</t>
         </is>
       </c>
       <c r="B77" t="inlineStr" s="2">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="D77" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_normal.draw[1]</t>
+          <t xml:space="preserve">composed_normal._accept[2]</t>
         </is>
       </c>
       <c r="E77" t="inlineStr" s="2">
@@ -2894,14 +2894,14 @@
       </c>
       <c r="F77" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……決まらなかったか。まあ、悪くない。</t>
+          <t xml:space="preserve">名前を呼ばれたなら、応えないとね。</t>
         </is>
       </c>
     </row>
     <row r="78" ht="40" customHeight="1">
       <c r="A78" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_normal.draw[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_normal._accept[3]</t>
         </is>
       </c>
       <c r="B78" t="inlineStr" s="2">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="D78" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_normal.draw[2]</t>
+          <t xml:space="preserve">composed_normal._accept[3]</t>
         </is>
       </c>
       <c r="E78" t="inlineStr" s="2">
@@ -2926,14 +2926,14 @@
       </c>
       <c r="F78" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">引き分け。……続きは、そのうちにね。</t>
+          <t xml:space="preserve">……そう来たか。まあ、来なよ。</t>
         </is>
       </c>
     </row>
     <row r="79" ht="40" customHeight="1">
       <c r="A79" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_normal.draw[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_normal.draw[1]</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="2">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="D79" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_normal.draw[3]</t>
+          <t xml:space="preserve">composed_normal.draw[1]</t>
         </is>
       </c>
       <c r="E79" t="inlineStr" s="2">
@@ -2958,14 +2958,14 @@
       </c>
       <c r="F79" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……お互い、まだ何か残してるってことだ。</t>
+          <t xml:space="preserve">……決まらなかったか。まあ、悪くない。</t>
         </is>
       </c>
     </row>
     <row r="80" ht="40" customHeight="1">
       <c r="A80" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_normal.lose[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_normal.draw[2]</t>
         </is>
       </c>
       <c r="B80" t="inlineStr" s="2">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="D80" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_normal.lose[1]</t>
+          <t xml:space="preserve">composed_normal.draw[2]</t>
         </is>
       </c>
       <c r="E80" t="inlineStr" s="2">
@@ -2990,14 +2990,14 @@
       </c>
       <c r="F80" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……完敗だね。潔く認めるよ。</t>
+          <t xml:space="preserve">……決着つかず。続きは、そのうちにね。</t>
         </is>
       </c>
     </row>
     <row r="81" ht="40" customHeight="1">
       <c r="A81" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_normal.lose[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_normal.draw[3]</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="2">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="D81" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_normal.lose[2]</t>
+          <t xml:space="preserve">composed_normal.draw[3]</t>
         </is>
       </c>
       <c r="E81" t="inlineStr" s="2">
@@ -3022,14 +3022,14 @@
       </c>
       <c r="F81" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あんたが上だった。……それだけの話。</t>
+          <t xml:space="preserve">……お互い、まだ何か残してるってことだ。</t>
         </is>
       </c>
     </row>
     <row r="82" ht="40" customHeight="1">
       <c r="A82" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_normal.lose[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_normal.lose[1]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="2">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="D82" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_normal.lose[3]</t>
+          <t xml:space="preserve">composed_normal.lose[1]</t>
         </is>
       </c>
       <c r="E82" t="inlineStr" s="2">
@@ -3054,14 +3054,14 @@
       </c>
       <c r="F82" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……やられたな。次は、こうはいかない。</t>
+          <t xml:space="preserve">……完敗だね。潔く認めるよ。</t>
         </is>
       </c>
     </row>
     <row r="83" ht="40" customHeight="1">
       <c r="A83" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_normal.win[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_normal.lose[2]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="D83" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_normal.win[1]</t>
+          <t xml:space="preserve">composed_normal.lose[2]</t>
         </is>
       </c>
       <c r="E83" t="inlineStr" s="2">
@@ -3086,14 +3086,14 @@
       </c>
       <c r="F83" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ま、こんなものかな。悪くない相手だった。</t>
+          <t xml:space="preserve">あんたが上だった。……それだけの話。</t>
         </is>
       </c>
     </row>
     <row r="84" ht="40" customHeight="1">
       <c r="A84" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_normal.win[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_normal.lose[3]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="D84" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_normal.win[2]</t>
+          <t xml:space="preserve">composed_normal.lose[3]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr" s="2">
@@ -3118,14 +3118,14 @@
       </c>
       <c r="F84" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">受けて正解だったね。……また来るといい。</t>
+          <t xml:space="preserve">……やられたな。次は、こうはいかない。</t>
         </is>
       </c>
     </row>
     <row r="85" ht="40" customHeight="1">
       <c r="A85" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_normal.win[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_normal.win[1]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="D85" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_normal.win[3]</t>
+          <t xml:space="preserve">composed_normal.win[1]</t>
         </is>
       </c>
       <c r="E85" t="inlineStr" s="2">
@@ -3150,14 +3150,14 @@
       </c>
       <c r="F85" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったよ。……いい試合だった、とだけ。</t>
+          <t xml:space="preserve">……ま、こんなものかな。悪くない相手だった。</t>
         </is>
       </c>
     </row>
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.normal.composed[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_normal.win[2]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -3167,29 +3167,29 @@
       </c>
       <c r="C86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
         </is>
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.normal.composed[1]</t>
+          <t xml:space="preserve">composed_normal.win[2]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F86" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここで学んだこと、忘れない。…ありがとう、社長</t>
+          <t xml:space="preserve">受けて正解だったね。……また来るといい。</t>
         </is>
       </c>
     </row>
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.normal.composed[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_normal.win[3]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -3199,29 +3199,29 @@
       </c>
       <c r="C87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
         </is>
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.normal.composed[1]</t>
+          <t xml:space="preserve">composed_normal.win[3]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そこまで言ってくれるなら、残るよ。ありがとう</t>
+          <t xml:space="preserve">勝ったよ。……いい試合だった、とだけ。</t>
         </is>
       </c>
     </row>
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.normal.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.normal.composed[1]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.normal.composed[1]</t>
+          <t xml:space="preserve">accepted.normal.composed[1]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr" s="2">
@@ -3246,14 +3246,14 @@
       </c>
       <c r="F88" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ごめんね、社長。…決めたことだから</t>
+          <t xml:space="preserve">…ここで学んだこと、忘れない。…ありがとう、社長</t>
         </is>
       </c>
     </row>
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.default.normal.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.normal.composed[1]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="C89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">default.normal.composed[1]</t>
+          <t xml:space="preserve">defended.normal.composed[1]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="2">
@@ -3278,14 +3278,14 @@
       </c>
       <c r="F89" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…うん。…もう少しだけ、やってみるよ</t>
+          <t xml:space="preserve">…そこまで言ってくれるなら、残るよ。ありがとう</t>
         </is>
       </c>
     </row>
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.normal.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.normal.composed[1]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="C90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.normal.composed[1]</t>
+          <t xml:space="preserve">defense_failed.normal.composed[1]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr" s="2">
@@ -3310,14 +3310,14 @@
       </c>
       <c r="F90" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう少しだけ。…あのベルトに、もう一度手を伸ばしたい</t>
+          <t xml:space="preserve">…ごめんね、社長。…決めたことだから</t>
         </is>
       </c>
     </row>
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.heel.normal.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.default.normal.composed[1]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heel.normal.composed[1]</t>
+          <t xml:space="preserve">default.normal.composed[1]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr" s="2">
@@ -3342,14 +3342,14 @@
       </c>
       <c r="F91" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふぅん、まだ使い道があるんだ。…いいよ、付き合ってあげる</t>
+          <t xml:space="preserve">…うん。…もう少しだけ、やってみるよ</t>
         </is>
       </c>
     </row>
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.high_trust.normal.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.normal.composed[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high_trust.normal.composed[1]</t>
+          <t xml:space="preserve">former_champ.normal.composed[1]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr" s="2">
@@ -3374,14 +3374,14 @@
       </c>
       <c r="F92" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう言ってくれるなら。…もう少しだけ付き合うよ</t>
+          <t xml:space="preserve">…もう少しだけ。…あのベルトに、もう一度手を伸ばしたい</t>
         </is>
       </c>
     </row>
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.normal.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.heel.normal.composed[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="C93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_former_champ.normal.composed[1]</t>
+          <t xml:space="preserve">heel.normal.composed[1]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="2">
@@ -3406,14 +3406,14 @@
       </c>
       <c r="F93" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…最後に一つだけ。…いい試合がしたいな</t>
+          <t xml:space="preserve">…ふぅん、まだ使い道があるんだ。…いいよ、付き合ってあげる</t>
         </is>
       </c>
     </row>
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.normal.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.high_trust.normal.composed[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="C94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_heel.normal.composed[1]</t>
+          <t xml:space="preserve">high_trust.normal.composed[1]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
@@ -3438,14 +3438,14 @@
       </c>
       <c r="F94" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふぅん。…言われなくても、そのつもりだったよ</t>
+          <t xml:space="preserve">…そう言ってくれるなら。…もう少しだけ付き合うよ</t>
         </is>
       </c>
     </row>
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.normal.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.normal.composed[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_no_title.normal.composed[1]</t>
+          <t xml:space="preserve">accept_former_champ.normal.composed[1]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
@@ -3470,14 +3470,14 @@
       </c>
       <c r="F95" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう。…潮時、だね</t>
+          <t xml:space="preserve">…最後に一つだけ。…いい試合がしたいな</t>
         </is>
       </c>
     </row>
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.normal.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.normal.composed[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.normal.composed[1]</t>
+          <t xml:space="preserve">accept_heel.normal.composed[1]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
@@ -3502,14 +3502,14 @@
       </c>
       <c r="F96" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう。…わかってたよ、自分でも</t>
+          <t xml:space="preserve">…ふぅん。…言われなくても、そのつもりだったよ</t>
         </is>
       </c>
     </row>
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.normal.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.normal.composed[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_winless.normal.composed[1]</t>
+          <t xml:space="preserve">accept_no_title.normal.composed[1]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="F97" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうだね。…追いつけなくなってた</t>
+          <t xml:space="preserve">…そう。…潮時、だね</t>
         </is>
       </c>
     </row>
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.normal.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.normal.composed[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="C98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.normal.composed[1]</t>
+          <t xml:space="preserve">accept_terminal.normal.composed[1]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
@@ -3566,14 +3566,14 @@
       </c>
       <c r="F98" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…チャンピオンに引退、か。…冗談はやめてよ</t>
+          <t xml:space="preserve">…そう。…わかってたよ、自分でも</t>
         </is>
       </c>
     </row>
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.normal.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.normal.composed[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3583,12 +3583,12 @@
       </c>
       <c r="C99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_distrust.normal.composed[1]</t>
+          <t xml:space="preserve">accept_winless.normal.composed[1]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
@@ -3598,14 +3598,14 @@
       </c>
       <c r="F99" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…追い出す、か。…何年ここにいたと思ってるの</t>
+          <t xml:space="preserve">…そうだね。…追いつけなくなってた</t>
         </is>
       </c>
     </row>
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.normal.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.normal.composed[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_fighting.normal.composed[1]</t>
+          <t xml:space="preserve">refuse_champ.normal.composed[1]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
@@ -3630,14 +3630,14 @@
       </c>
       <c r="F100" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ終わらないよ。…体がある限り、リングに立つ</t>
+          <t xml:space="preserve">…チャンピオンに引退、か。…冗談はやめてよ</t>
         </is>
       </c>
     </row>
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.normal.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.normal.composed[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_heel.normal.composed[1]</t>
+          <t xml:space="preserve">refuse_distrust.normal.composed[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
@@ -3662,14 +3662,14 @@
       </c>
       <c r="F101" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…引退、ね。…次の興行を見てからもう一度言って</t>
+          <t xml:space="preserve">…追い出す、か。…何年ここにいたと思ってるの</t>
         </is>
       </c>
     </row>
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.normal.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.normal.composed[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3679,12 +3679,12 @@
       </c>
       <c r="C102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.normal.composed[1]</t>
+          <t xml:space="preserve">refuse_fighting.normal.composed[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
@@ -3694,14 +3694,14 @@
       </c>
       <c r="F102" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くない景色だった。うん、悪くない</t>
+          <t xml:space="preserve">…まだ終わらないよ。…体がある限り、リングに立つ</t>
         </is>
       </c>
     </row>
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.normal.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.normal.composed[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="C103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.normal.composed[1]</t>
+          <t xml:space="preserve">refuse_heel.normal.composed[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
@@ -3726,14 +3726,14 @@
       </c>
       <c r="F103" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…届かなかった。…でもまあ、悔いはないよ</t>
+          <t xml:space="preserve">…引退、ね。…次の興行を見てからもう一度言って</t>
         </is>
       </c>
     </row>
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.normal.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.normal.composed[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.normal.composed[1]</t>
+          <t xml:space="preserve">A1_champion.normal.composed[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
@@ -3758,14 +3758,14 @@
       </c>
       <c r="F104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、こんなもんだろう。…泣くなよ</t>
+          <t xml:space="preserve">…悪くない景色だった。うん、悪くない</t>
         </is>
       </c>
     </row>
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.normal.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.normal.composed[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.normal.composed[1]</t>
+          <t xml:space="preserve">A2_uncrowned.normal.composed[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
@@ -3790,14 +3790,14 @@
       </c>
       <c r="F105" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい時間だった。…うん、全部ね</t>
+          <t xml:space="preserve">…届かなかった。…でもまあ、悔いはないよ</t>
         </is>
       </c>
     </row>
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.normal.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.normal.composed[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.normal.composed[1]</t>
+          <t xml:space="preserve">A3_heel.normal.composed[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
@@ -3822,14 +3822,14 @@
       </c>
       <c r="F106" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…こんなところで、か。…まだ何も…</t>
+          <t xml:space="preserve">…ま、こんなもんだろう。…泣くなよ</t>
         </is>
       </c>
     </row>
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.normal.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.normal.composed[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.normal.composed[1]</t>
+          <t xml:space="preserve">A4_veteran.normal.composed[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
@@ -3854,14 +3854,14 @@
       </c>
       <c r="F107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだやれたのに。…体が、ね</t>
+          <t xml:space="preserve">…いい時間だった。…うん、全部ね</t>
         </is>
       </c>
     </row>
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.normal.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.normal.composed[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.normal.composed[1]</t>
+          <t xml:space="preserve">B1_young.normal.composed[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
@@ -3886,14 +3886,14 @@
       </c>
       <c r="F108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…十分やったよ。…うん、わかってた</t>
+          <t xml:space="preserve">…こんなところで、か。…まだ何も…</t>
         </is>
       </c>
     </row>
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.normal.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.normal.composed[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.normal.composed[1]</t>
+          <t xml:space="preserve">B2_prime.normal.composed[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
@@ -3918,14 +3918,14 @@
       </c>
       <c r="F109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ返したくなかったな。…このベルト</t>
+          <t xml:space="preserve">…まだやれたのに。…体が、ね</t>
         </is>
       </c>
     </row>
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.normal.composed[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">B3_older.normal.composed[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
@@ -3950,14 +3950,14 @@
       </c>
       <c r="F110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、居心地いいからね。ここにいるよ</t>
+          <t xml:space="preserve">…十分やったよ。…うん、わかってた</t>
         </is>
       </c>
     </row>
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.normal.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.normal.composed[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3967,29 +3967,29 @@
       </c>
       <c r="C111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.normal.composed[1]</t>
+          <t xml:space="preserve">B4_champion_injury.normal.composed[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふぅん…悪くないね。まあ、期待に応えるよ。</t>
+          <t xml:space="preserve">…まだ返したくなかったな。…このベルト</t>
         </is>
       </c>
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.normal.composed[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.normal.composed[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3999,29 +3999,29 @@
       </c>
       <c r="C112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
         </is>
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.normal.composed[1]</t>
+          <t xml:space="preserve">normal.composed[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ…気持ちは受け取ったよ。悪くないね。</t>
+          <t xml:space="preserve">…ま、居心地いいからね。ここにいるよ</t>
         </is>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.normal.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.normal.composed[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.normal.composed[1]</t>
+          <t xml:space="preserve">raise_accept.normal.composed[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -4046,14 +4046,14 @@
       </c>
       <c r="F113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう。まあ…そういうこともあるよね。</t>
+          <t xml:space="preserve">ふぅん…悪くないね。まあ、期待に応えるよ。</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.normal.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.normal.composed[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.normal.composed[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.normal.composed[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -4078,14 +4078,14 @@
       </c>
       <c r="F114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ…社長、少しいいかな。{tenure}{record}悪くない環境だと思ってるけど…もう少し、考えてもらえると嬉しいね。</t>
+          <t xml:space="preserve">まあ…気持ちは受け取ったよ。悪くないね。</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.normal.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.normal.composed[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.normal.composed[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.normal.composed[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -4110,14 +4110,14 @@
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう。まあ…残念だけど、仕方ないね。</t>
+          <t xml:space="preserve">…そう。まあ…そういうこともあるよね。</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.normal.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.normal.composed[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.normal.composed[1]</t>
+          <t xml:space="preserve">raise_open.normal.composed[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -4142,14 +4142,14 @@
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長…少し話がある。{tenure}ここを離れようかと…まあ、そういうことです。</t>
+          <t xml:space="preserve">まあ…社長、少しいいかな。{tenure}{record}悪くない環境だと思ってるけど…もう少し、考えてもらえると嬉しいね。</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.normal.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.normal.composed[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.normal.composed[1]</t>
+          <t xml:space="preserve">raise_refuse.normal.composed[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4174,14 +4174,14 @@
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがたいけど…もう決めたんだ。…悪いね。</t>
+          <t xml:space="preserve">…そう。まあ…残念だけど、仕方ないね。</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.normal.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.normal.composed[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.normal.composed[1]</t>
+          <t xml:space="preserve">sudden_departure.normal.composed[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4206,338 +4206,338 @@
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふぅん。そこまでしてくれるんだ。…まあ…もう少しだけ、いるよ。</t>
+          <t xml:space="preserve">社長。手短に言うね。…辞めます。もう決めたことだから。</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.normal.composed[2]</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.normal.composed[2]</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…世話になったよ。…でも、もうここでは続けられない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="40" customHeight="1">
+      <c r="A120" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.normal.composed[1]</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_listen.normal.composed[1]</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…聞いてくれるんだ。{record}…まあ、新しい場所で試してみたくてね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="40" customHeight="1">
+      <c r="A121" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.normal.composed[1]</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_open.normal.composed[1]</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長…少し話がある。{tenure}ここを離れようかと…まあ、そういうことです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="40" customHeight="1">
+      <c r="A122" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.normal.composed[1]</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_release.normal.composed[1]</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…分かった。{tenure_farewell}{rivalry}…ここでの時間は、悪くなかったよ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="40" customHeight="1">
+      <c r="A123" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.normal.composed[1]</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_fail.normal.composed[1]</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがたいけど…もう決めたんだ。…悪いね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="40" customHeight="1">
+      <c r="A124" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.normal.composed[1]</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_success.normal.composed[1]</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ふぅん。そこまでしてくれるんだ。…まあ…もう少しだけ、いるよ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="40" customHeight="1">
+      <c r="A125" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">NEGOTIATE_LINES.blocked.normal.composed[1]</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr" s="2">
+      <c r="B125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr" s="12">
+      <c r="D125" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">blocked.normal.composed[1]</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr" s="2">
+      <c r="E125" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr" s="3">
+      <c r="F125" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…悪いけど、今の仲間を置いていく気にはなれない。
 …ごめんね</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="40" customHeight="1">
-      <c r="A120" t="inlineStr" s="15">
+    <row r="126" ht="40" customHeight="1">
+      <c r="A126" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.fail.normal.composed[1]</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr" s="2">
+      <c r="B126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr" s="12">
+      <c r="D126" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fail.normal.composed[1]</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr" s="2">
+      <c r="E126" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr" s="3">
+      <c r="F126" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…悪いけど、パスで。
 縁があればまた</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="40" customHeight="1">
-      <c r="A121" t="inlineStr" s="15">
+    <row r="127" ht="40" customHeight="1">
+      <c r="A127" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.start.normal.composed[1]</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr" s="2">
+      <c r="B127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr" s="12">
+      <c r="D127" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">start.normal.composed[1]</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr" s="2">
+      <c r="E127" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr" s="3">
+      <c r="F127" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…ふぅん、私に来いって？
 …聞くだけ聞こうか</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="40" customHeight="1">
-      <c r="A122" t="inlineStr" s="15">
+    <row r="128" ht="40" customHeight="1">
+      <c r="A128" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.success.normal.composed[1]</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr" s="2">
+      <c r="B128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr" s="12">
+      <c r="D128" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">success.normal.composed[1]</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr" s="2">
+      <c r="E128" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr" s="3">
+      <c r="F128" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…わかった、行くよ。
 …やるべきことをやるだけだ</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="40" customHeight="1">
-      <c r="A123" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.normal.composed[1]</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">normal.composed[1]</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…なるほど。壁を越えたみたいだね</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="40" customHeight="1">
-      <c r="A124" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">BT_HINT_LINES.normal.composed[1]</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">normal.composed[1]</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">（…ふぅん。…いつもと違う。悪くないね——）</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="40" customHeight="1">
-      <c r="A125" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.normal.composed[1]</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">cap_reached.normal.composed[1]</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…ここが限界か。…まあ、上出来じゃない？</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="40" customHeight="1">
-      <c r="A126" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.normal.composed[1]</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">ovr_elite.normal.composed[1]</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…ここまで来たか。…悪くないね</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="40" customHeight="1">
-      <c r="A127" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.normal.composed[1]</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">ovr_growth.normal.composed[1]</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…悪くないペースだね</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="40" customHeight="1">
-      <c r="A128" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.normal.composed[1]</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">ovr_legend.normal.composed[1]</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…ここまで来ると、逆に静かな気持ちになるね</t>
-        </is>
-      </c>
-    </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.normal.composed[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.normal.composed[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="C129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.normal.composed[1]</t>
+          <t xml:space="preserve">normal.composed[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
@@ -4562,14 +4562,14 @@
       </c>
       <c r="F129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…知ってもらえるのは、素直に嬉しいね</t>
+          <t xml:space="preserve">…なるほど。壁を越えたみたいだね</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.normal.composed[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.normal.composed[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="C130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.normal.composed[1]</t>
+          <t xml:space="preserve">normal.composed[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
@@ -4594,14 +4594,14 @@
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…こんなに応援してくれる人がいるんだ。…頑張らないとね</t>
+          <t xml:space="preserve">（…ふぅん。…いつもと違う。悪くないね——）</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.normal.composed[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="C131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">fresh.normal.composed[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
@@ -4626,14 +4626,14 @@
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…何のために闘ってるのか。…わからなくなった</t>
+          <t xml:space="preserve">…体は軽いね。こういう日は、伸びるんだよ</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.normal.composed[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="C132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">heavy.normal.composed[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
@@ -4658,14 +4658,14 @@
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだやれる。…うん、やってみよう</t>
+          <t xml:space="preserve">…体が重いね。今日やっても、たぶん流れるだけ</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.normal.composed[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="C133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">warm.normal.composed[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
@@ -4690,14 +4690,14 @@
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やっと、戻ってこれたかな</t>
+          <t xml:space="preserve">…悪くはないよ。…ただ、切れが一つ落ちたかな</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.normal.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.normal.composed[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4707,12 +4707,12 @@
       </c>
       <c r="C134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.normal.composed[1]</t>
+          <t xml:space="preserve">cap_reached.normal.composed[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
@@ -4722,14 +4722,14 @@
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの負けから、どこか噛み合わない</t>
+          <t xml:space="preserve">…ここが限界か。…まあ、上出来じゃない？</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.normal.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.normal.composed[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4739,12 +4739,12 @@
       </c>
       <c r="C135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.normal.composed[1]</t>
+          <t xml:space="preserve">ovr_elite.normal.composed[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
@@ -4754,14 +4754,14 @@
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…治ったはずなのに。…まあ、焦らないよ</t>
+          <t xml:space="preserve">…ここまで来たか。…悪くないね</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.normal.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.normal.composed[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="C136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.normal.composed[1]</t>
+          <t xml:space="preserve">ovr_growth.normal.composed[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -4786,14 +4786,14 @@
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…戻ってきた。…のに、少し怖いかな</t>
+          <t xml:space="preserve">…悪くないペースだね</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.normal.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.normal.composed[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="C137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.normal.composed[1]</t>
+          <t xml:space="preserve">ovr_legend.normal.composed[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4818,14 +4818,14 @@
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…怪我は治った。…でも気力が、まだ</t>
+          <t xml:space="preserve">…ここまで来ると、逆に静かな気持ちになるね</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.normal.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.normal.composed[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4835,29 +4835,29 @@
       </c>
       <c r="C138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.normal.composed[1]</t>
+          <t xml:space="preserve">pop_growth.normal.composed[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くなかった。あの相手だから、出せたものがある</t>
+          <t xml:space="preserve">…知ってもらえるのは、素直に嬉しいね</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.normal.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.normal.composed[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4867,29 +4867,29 @@
       </c>
       <c r="C139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.composed[1]</t>
+          <t xml:space="preserve">pop_star.normal.composed[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…このベルトの重さ、悪くない。…来るなら来なよ</t>
+          <t xml:space="preserve">…こんなに応援してくれる人がいるんだ。…頑張らないとね</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.normal.composed[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.normal.composed[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4899,29 +4899,29 @@
       </c>
       <c r="C140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.normal.composed[1]</t>
+          <t xml:space="preserve">normal.composed[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい時間だった。後悔？ …ないよ</t>
+          <t xml:space="preserve">…何のために闘ってるのか。…わからなくなった</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.normal.composed[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.normal.composed[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4931,29 +4931,29 @@
       </c>
       <c r="C141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.normal.composed[1]</t>
+          <t xml:space="preserve">normal.composed[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふぅん、こういう賞もあるんだね。…ありがとう</t>
+          <t xml:space="preserve">…まだやれる。…うん、やってみよう</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.normal.composed[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.normal.composed[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4963,29 +4963,29 @@
       </c>
       <c r="C142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.normal.composed[1]</t>
+          <t xml:space="preserve">normal.composed[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一年間、やるべきことをやった。それだけだよ</t>
+          <t xml:space="preserve">…やっと、戻ってこれたかな</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.normal.composed[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.normal.composed[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4995,29 +4995,29 @@
       </c>
       <c r="C143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.normal.composed[1]</t>
+          <t xml:space="preserve">defeat.normal.composed[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、悪くないスタートかな。ここからだよ</t>
+          <t xml:space="preserve">…あの負けから、どこか噛み合わない</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.normal.composed[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -5027,29 +5027,29 @@
       </c>
       <c r="C144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.normal.composed[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドーム。…ついに辿り着きましたね</t>
+          <t xml:space="preserve">…治ったはずなのに。…まあ、焦らないよ</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.composed[2]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.normal.composed[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -5059,29 +5059,29 @@
       </c>
       <c r="C145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[2]</t>
+          <t xml:space="preserve">injury_severe_recovery.normal.composed[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">感慨深いものがあります。しかし、今は試合に集中します</t>
+          <t xml:space="preserve">…戻ってきた。…のに、少し怖いかな</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.composed[3]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.normal.composed[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -5091,29 +5091,29 @@
       </c>
       <c r="C146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[3]</t>
+          <t xml:space="preserve">penalty_end.normal.composed[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この瞬間を、しっかり刻んでおきます</t>
+          <t xml:space="preserve">…怪我は治った。…でも気力が、まだ</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.normal.composed[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="C147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">bestMatch.normal.composed[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
@@ -5138,14 +5138,14 @@
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員。…団体として、一つの到達点ですね</t>
+          <t xml:space="preserve">…悪くなかった。あの相手だから、出せたものがある</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.composed[2]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.normal.composed[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="C148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[2]</t>
+          <t xml:space="preserve">champion.normal.composed[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
@@ -5170,14 +5170,14 @@
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お客様の拍手、今も胸に響いています</t>
+          <t xml:space="preserve">…このベルトの重さ、悪くない。…来るなら来なよ</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.composed[3]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.normal.composed[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5187,12 +5187,12 @@
       </c>
       <c r="C149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[3]</t>
+          <t xml:space="preserve">hallOfFame.normal.composed[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
@@ -5202,14 +5202,14 @@
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この記録、大切にしていきましょう</t>
+          <t xml:space="preserve">…いい時間だった。後悔？ …ないよ</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.normal.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.normal.composed[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5219,29 +5219,29 @@
       </c>
       <c r="C150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.normal.composed[1]</t>
+          <t xml:space="preserve">mediaAward.normal.composed[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、少しずつ馴染んできたかな</t>
+          <t xml:space="preserve">…ふぅん、こういう賞もあるんだね。…ありがとう</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.normal.composed[2]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.normal.composed[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5251,29 +5251,29 @@
       </c>
       <c r="C151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.normal.composed[2]</t>
+          <t xml:space="preserve">mvp.normal.composed[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悪くない感触だね。この調子で行こう</t>
+          <t xml:space="preserve">…一年間、やるべきことをやった。それだけだよ</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.normal.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.normal.composed[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5283,29 +5283,29 @@
       </c>
       <c r="C152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.normal.composed[1]</t>
+          <t xml:space="preserve">rookie.normal.composed[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい仲間だね。悪くない環境だよ</t>
+          <t xml:space="preserve">…ま、悪くないスタートかな。ここからだよ</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.normal.composed[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.composed[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5315,29 +5315,29 @@
       </c>
       <c r="C153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.normal.composed[1]</t>
+          <t xml:space="preserve">normal.composed[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ちょっと疲れただけ。すぐ戻るよ</t>
+          <t xml:space="preserve">ドーム。…ついに辿り着きましたね</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.normal.composed[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.composed[2]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5347,29 +5347,29 @@
       </c>
       <c r="C154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.normal.composed[1]</t>
+          <t xml:space="preserve">normal.composed[2]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがたいね。ちゃんと届いてるよ</t>
+          <t xml:space="preserve">感慨深いものがあります。しかし、今は試合に集中します</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.normal.composed[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.composed[3]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5379,29 +5379,29 @@
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.normal.composed[1]</t>
+          <t xml:space="preserve">normal.composed[3]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もういいよ。分かったから</t>
+          <t xml:space="preserve">この瞬間を、しっかり刻んでおきます</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.normal.composed[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.composed[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5411,29 +5411,29 @@
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.normal.composed[1]</t>
+          <t xml:space="preserve">normal.composed[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ん、ちょっと考え事。気にしないで</t>
+          <t xml:space="preserve">満員。…団体として、一つの到達点ですね</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.normal.composed[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.composed[2]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5443,29 +5443,29 @@
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">breakthrough.voice.normal.composed[1]</t>
+          <t xml:space="preserve">normal.composed[2]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くない環境だね。…感謝してる</t>
+          <t xml:space="preserve">お客様の拍手、今も胸に響いています</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.normal.composed[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.composed[3]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5475,29 +5475,29 @@
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.normal.composed[1]</t>
+          <t xml:space="preserve">normal.composed[3]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、こんなものか</t>
+          <t xml:space="preserve">この記録、大切にしていきましょう</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.normal.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.normal.composed[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5507,12 +5507,12 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice.normal.composed[1]</t>
+          <t xml:space="preserve">N1.normal.composed[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
@@ -5522,14 +5522,14 @@
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…伸びたね。…まあ、焦ることはない</t>
+          <t xml:space="preserve">…ま、少しずつ馴染んできたかな</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.normal.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.normal.composed[2]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.normal.composed[1]</t>
+          <t xml:space="preserve">N1.normal.composed[2]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
@@ -5554,14 +5554,14 @@
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、待つさ</t>
+          <t xml:space="preserve">悪くない感触だね。この調子で行こう</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.normal.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.normal.composed[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5571,12 +5571,12 @@
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G4.voice.normal.composed[1]</t>
+          <t xml:space="preserve">N2.normal.composed[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
@@ -5586,14 +5586,14 @@
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、待つよ</t>
+          <t xml:space="preserve">…いい仲間だね。悪くない環境だよ</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.normal.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.normal.composed[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5603,12 +5603,12 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice.normal.composed[1]</t>
+          <t xml:space="preserve">N3.normal.composed[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
@@ -5618,14 +5618,14 @@
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…別に。一人でも困らない</t>
+          <t xml:space="preserve">…ちょっと疲れただけ。すぐ戻るよ</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.normal.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.normal.composed[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5635,12 +5635,12 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal.normal.composed[1]</t>
+          <t xml:space="preserve">N4.normal.composed[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
@@ -5650,14 +5650,14 @@
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうか。…{name2}がいなくなるのか</t>
+          <t xml:space="preserve">…ありがたいね。ちゃんと届いてるよ</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.normal.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.normal.composed[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice.normal.composed[1]</t>
+          <t xml:space="preserve">N5_low.normal.composed[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
@@ -5682,14 +5682,14 @@
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くない。…やっと追いついた</t>
+          <t xml:space="preserve">…もういいよ。分かったから</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.normal.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.normal.composed[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5699,12 +5699,12 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice.normal.composed[1]</t>
+          <t xml:space="preserve">N5_warning.normal.composed[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
@@ -5714,14 +5714,14 @@
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…足りなかった。…次、だね</t>
+          <t xml:space="preserve">…ん、ちょっと考え事。気にしないで</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.normal.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.normal.composed[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5731,29 +5731,29 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_insult.normal.composed[1]</t>
+          <t xml:space="preserve">breakthrough.voice.normal.composed[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…これで済ませるつもりかい。そうか</t>
+          <t xml:space="preserve">…悪くない環境だね。…感謝してる</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.normal.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.normal.composed[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5763,29 +5763,29 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.normal.composed[1]</t>
+          <t xml:space="preserve">G1.voice.normal.composed[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう。大事に使うよ</t>
+          <t xml:space="preserve">…まあ、こんなものか</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.normal.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.normal.composed[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5795,29 +5795,29 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.normal.composed[1]</t>
+          <t xml:space="preserve">G2.voice.normal.composed[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…合宿か。じっくりやろう</t>
+          <t xml:space="preserve">…伸びたね。…まあ、焦ることはない</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.normal.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.normal.composed[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5827,29 +5827,29 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.normal.composed[1]</t>
+          <t xml:space="preserve">G3.voice.normal.composed[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…見てくれてたんだ。…悪くないね</t>
+          <t xml:space="preserve">…まあ、待つさ</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.normal.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.normal.composed[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5859,29 +5859,29 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.normal.composed[1]</t>
+          <t xml:space="preserve">G4.voice.normal.composed[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう。もう少しやってみるよ</t>
+          <t xml:space="preserve">…まあ、待つよ</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.normal.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.normal.composed[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5891,29 +5891,29 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.normal.composed[1]</t>
+          <t xml:space="preserve">R2.voice.normal.composed[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なるほど。やってみるよ</t>
+          <t xml:space="preserve">…別に。一人でも困らない</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.normal.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.normal.composed[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5923,29 +5923,29 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.normal.composed[1]</t>
+          <t xml:space="preserve">R3.modal.normal.composed[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい時間だったね。悪くないよ</t>
+          <t xml:space="preserve">…そうか。…{name2}がいなくなるのか</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.normal.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.normal.composed[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5955,29 +5955,29 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.normal.composed[1]</t>
+          <t xml:space="preserve">R4.voice.normal.composed[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう。少し休んでくるよ</t>
+          <t xml:space="preserve">…悪くない。…やっと追いついた</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.normal.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.normal.composed[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5987,29 +5987,29 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.normal.composed[1]</t>
+          <t xml:space="preserve">R5.voice.normal.composed[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう。リング、待たせちゃ悪いね</t>
+          <t xml:space="preserve">…足りなかった。…次、だね</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.normal.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.normal.composed[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.normal.composed[1]</t>
+          <t xml:space="preserve">bonus_insult.normal.composed[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -6034,14 +6034,14 @@
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…了解。しっかり吸収するよ</t>
+          <t xml:space="preserve">…これで済ませるつもりかい。そうか</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.normal.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.normal.composed[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.normal.composed[1]</t>
+          <t xml:space="preserve">bonus.normal.composed[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -6066,14 +6066,14 @@
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…メディアか。いい機会だね</t>
+          <t xml:space="preserve">…ありがとう。大事に使うよ</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.normal.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.normal.composed[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.normal.composed[1]</t>
+          <t xml:space="preserve">camp.normal.composed[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -6098,14 +6098,14 @@
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…他所から話が来てるんだ。一応報告しておくね</t>
+          <t xml:space="preserve">…合宿か。じっくりやろう</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.normal.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.normal.composed[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.normal.composed[1]</t>
+          <t xml:space="preserve">encourage_high_trust.normal.composed[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -6130,14 +6130,14 @@
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…今日はいいかな。少し考えたいことがあって</t>
+          <t xml:space="preserve">…見てくれてたんだ。…悪くないね</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.normal.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.normal.composed[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.normal.composed[1]</t>
+          <t xml:space="preserve">encourage.normal.composed[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6162,14 +6162,14 @@
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（いつもの穏やかさが消え、「…ま、そういうことだよね」と静かに呟いている）</t>
+          <t xml:space="preserve">…ありがとう。もう少しやってみるよ</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.normal.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.normal.composed[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6179,12 +6179,12 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.normal.composed[1]</t>
+          <t xml:space="preserve">media.normal.composed[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6194,14 +6194,14 @@
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに夕焼けの写真と「…少し考える時間が欲しいかな」と投稿。ファンがざわついている）</t>
+          <t xml:space="preserve">…なるほど。やってみるよ</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.normal.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.normal.composed[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6211,12 +6211,12 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.normal.composed[1]</t>
+          <t xml:space="preserve">party.normal.composed[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6226,14 +6226,14 @@
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そろそろベルトに挑戦させてもらえないかな</t>
+          <t xml:space="preserve">…いい時間だったね。悪くないよ</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.normal.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.normal.composed[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.normal.composed[1]</t>
+          <t xml:space="preserve">refresh_leave.normal.composed[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6258,14 +6258,14 @@
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの人との試合、そろそろ組んでもらえないかな</t>
+          <t xml:space="preserve">…ありがとう。少し休んでくるよ</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.normal.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.normal.composed[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.normal.composed[1]</t>
+          <t xml:space="preserve">special_treatment.normal.composed[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6290,14 +6290,14 @@
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…少し休ませてもらえるかな</t>
+          <t xml:space="preserve">…ありがとう。リング、待たせちゃ悪いね</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.normal.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.normal.composed[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6307,12 +6307,12 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.normal.composed[1]</t>
+          <t xml:space="preserve">trainer.normal.composed[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6322,14 +6322,14 @@
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…このままだと困るんだよね。少し考えてもらえるかな</t>
+          <t xml:space="preserve">…了解。しっかり吸収するよ</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.normal.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.normal.composed[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.normal.composed[1]</t>
+          <t xml:space="preserve">E1.normal.composed[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6354,14 +6354,14 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…少し追い込みたいんだ。特訓させてもらえるかな</t>
+          <t xml:space="preserve">…メディアか。いい機会だね</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.normal.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E4.normal.composed[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.normal.composed[1]</t>
+          <t xml:space="preserve">E4.normal.composed[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6386,14 +6386,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…後輩の面倒、見させてもらえないかな</t>
+          <t xml:space="preserve">…スカウトから、新しい話が来てるみたいだよ</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.normal.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.normal.composed[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6403,12 +6403,12 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.normal.composed[1]</t>
+          <t xml:space="preserve">E6.normal.composed[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6418,14 +6418,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やっちゃったね。まあ、焦らず治すよ</t>
+          <t xml:space="preserve">…他所から話が来てるんだ。一応報告しておくね</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.normal.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.normal.composed[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.normal.composed[1]</t>
+          <t xml:space="preserve">S_boycott.normal.composed[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6450,14 +6450,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、合わない人もいるよね。少し距離を置きたいな</t>
+          <t xml:space="preserve">…今日はいいかな。少し考えたいことがあって</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.normal.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.normal.composed[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6467,12 +6467,12 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.normal.composed[1]</t>
+          <t xml:space="preserve">S_grumble.normal.composed[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6482,14 +6482,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふぅん。まあ、お互い様だと思うけどね</t>
+          <t xml:space="preserve">（いつもの穏やかさが消え、「…ま、そういうことだよね」と静かに呟いている）</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.normal.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.normal.composed[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.normal.composed[1]</t>
+          <t xml:space="preserve">S_sns.normal.composed[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6514,14 +6514,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…コラボか。なるほどね、面白そう</t>
+          <t xml:space="preserve">（SNSに夕焼けの写真と「…少し考える時間が欲しいかな」と投稿。ファンがざわついている）</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.normal.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.normal.composed[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6531,12 +6531,12 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.normal.composed[1]</t>
+          <t xml:space="preserve">S1.normal.composed[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6546,14 +6546,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…CMか。まあ、悪くないね</t>
+          <t xml:space="preserve">…そろそろベルトに挑戦させてもらえないかな</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.normal.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.normal.composed[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6563,12 +6563,12 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.normal.composed[1]</t>
+          <t xml:space="preserve">S2.normal.composed[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6578,14 +6578,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…グラビアか。まあ、たまにはいいんじゃない</t>
+          <t xml:space="preserve">…あの人との試合、そろそろ組んでもらえないかな</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.normal.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.normal.composed[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6595,12 +6595,12 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.normal.composed[1]</t>
+          <t xml:space="preserve">S3.normal.composed[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6610,14 +6610,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…バラエティか。まあ、のんびり喋るよ</t>
+          <t xml:space="preserve">…少し休ませてもらえるかな</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.normal.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.normal.composed[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.normal.composed[1]</t>
+          <t xml:space="preserve">S4_direct.normal.composed[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6642,14 +6642,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…取材か。まあ、いつも通りやるよ</t>
+          <t xml:space="preserve">…このままだと困るんだよね。少し考えてもらえるかな</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.normal.composed[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6659,29 +6659,29 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">S4_silent.normal.composed[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…選んでくれるなら、応えるよ</t>
+          <t xml:space="preserve">…（少し間を置いて）…いや、なんでもないよ</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.normal.composed[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6691,29 +6691,29 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">S5.normal.composed[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。精一杯やるよ</t>
+          <t xml:space="preserve">…少し追い込みたいんだ。特訓させてもらえるかな</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.normal.composed[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.normal.composed[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6723,29 +6723,29 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[2]</t>
+          <t xml:space="preserve">S6.normal.composed[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…選んでくれてありがとう</t>
+          <t xml:space="preserve">…後輩の面倒、見させてもらえないかな</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.normal.composed[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6755,29 +6755,29 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">B1.normal.composed[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。力になるよ</t>
+          <t xml:space="preserve">…やっちゃったね。まあ、焦らず治すよ</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.normal.composed[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6787,29 +6787,29 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">B2_fighter1.normal.composed[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。精一杯やるよ</t>
+          <t xml:space="preserve">…まあ、合わない人もいるよね。少し距離を置きたいな</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.normal.composed[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6819,29 +6819,29 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">B2_fighter2.normal.composed[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…少し休むよ。すぐ戻る</t>
+          <t xml:space="preserve">…ふぅん。まあ、お互い様だと思うけどね</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.normal.composed[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.normal.composed[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6851,29 +6851,29 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[2]</t>
+          <t xml:space="preserve">B4_brand.normal.composed[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…大したことじゃないから、安心して</t>
+          <t xml:space="preserve">…コラボか。なるほどね、面白そう</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.normal.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.normal.composed[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6883,29 +6883,29 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.normal.composed[1]</t>
+          <t xml:space="preserve">B4_cm.normal.composed[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…選んでくれるなら、応えるよ</t>
+          <t xml:space="preserve">…CMか。まあ、悪くないね</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.normal.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.normal.composed[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6915,29 +6915,29 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.normal.composed[1]</t>
+          <t xml:space="preserve">B4_fan.normal.composed[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。精一杯やるよ</t>
+          <t xml:space="preserve">…直接話せるんだ。…それは、楽しみだね</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.normal.composed[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.normal.composed[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6947,29 +6947,29 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.normal.composed[2]</t>
+          <t xml:space="preserve">B4_fashion.normal.composed[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…選んでくれてありがとう</t>
+          <t xml:space="preserve">…ランウェイか。歩けるかな。…まあ、やってみるよ</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.normal.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.normal.composed[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6979,29 +6979,29 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.normal.composed[1]</t>
+          <t xml:space="preserve">B4_gravure.normal.composed[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。力になるよ</t>
+          <t xml:space="preserve">…グラビアか。まあ、たまにはいいんじゃない</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.normal.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.normal.composed[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -7011,29 +7011,29 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.normal.composed[1]</t>
+          <t xml:space="preserve">B4_variety.normal.composed[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。精一杯やるよ</t>
+          <t xml:space="preserve">…バラエティか。まあ、のんびり喋るよ</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.normal.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.normal.composed[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -7043,29 +7043,29 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.normal.composed[1]</t>
+          <t xml:space="preserve">B4.normal.composed[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…少し休むよ。すぐ戻る</t>
+          <t xml:space="preserve">…取材か。まあ、いつも通りやるよ</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.normal.composed[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.normal.composed[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.normal.composed[2]</t>
+          <t xml:space="preserve">normal.composed[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -7090,14 +7090,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…大したことじゃないから、安心して</t>
+          <t xml:space="preserve">…選んでくれるなら、応えるよ</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.normal.composed[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -7107,12 +7107,12 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.normal.composed[1]</t>
+          <t xml:space="preserve">normal.composed[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -7122,14 +7122,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうか。お世話になったね</t>
+          <t xml:space="preserve">…よろしく。精一杯やるよ</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.normal.composed[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.normal.composed[2]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.normal.composed[2]</t>
+          <t xml:space="preserve">normal.composed[2]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7154,14 +7154,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…短い間だったけど、ありがとう</t>
+          <t xml:space="preserve">…選んでくれてありがとう</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.normal.composed[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.normal.composed[1]</t>
+          <t xml:space="preserve">normal.composed[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7186,14 +7186,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…短い間だけど、手は抜かないよ</t>
+          <t xml:space="preserve">…よろしく。力になるよ</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.normal.composed[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7203,12 +7203,12 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.normal.composed[1]</t>
+          <t xml:space="preserve">normal.composed[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7218,14 +7218,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…届かなかったか。…次だね</t>
+          <t xml:space="preserve">…よろしく。精一杯やるよ</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.normal.composed[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7235,12 +7235,12 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.normal.composed[1]</t>
+          <t xml:space="preserve">normal.composed[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7250,14 +7250,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…防衛か。…まだ渡すつもりはないよ</t>
+          <t xml:space="preserve">…少し休むよ。すぐ戻る</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.normal.composed[2]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.normal.composed[1]</t>
+          <t xml:space="preserve">normal.composed[2]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7282,14 +7282,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…失ったか。…でも終わりじゃない</t>
+          <t xml:space="preserve">…大したことじゃないから、安心して</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.normal.composed[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.normal.composed[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.normal.composed[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7314,14 +7314,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…チャンピオンか。…悪くないね</t>
+          <t xml:space="preserve">…決着はついてる。…なのに、まだ喉に引っかかってる</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.normal.composed[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7331,12 +7331,12 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.normal.composed[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7346,14 +7346,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうか。お世話になったね</t>
+          <t xml:space="preserve">…片がついたらしいよ。…誰の中で、って話だけど</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.normal.composed[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.normal.composed[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[2]</t>
+          <t xml:space="preserve">draftInterest.normal.composed[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7378,14 +7378,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…短い間だったけど、ありがとう</t>
+          <t xml:space="preserve">…選んでくれるなら、応えるよ</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.normal.composed[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7395,12 +7395,12 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">draftJoin.normal.composed[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7410,14 +7410,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…短い間だけど、手は抜かないよ</t>
+          <t xml:space="preserve">…よろしく。精一杯やるよ</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.normal.composed[2]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">draftJoin.normal.composed[2]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7442,14 +7442,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…届かなかったか。…次だね</t>
+          <t xml:space="preserve">…選んでくれてありがとう</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.normal.composed[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">faGreeting.normal.composed[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7474,14 +7474,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…防衛か。…まだ渡すつもりはないよ</t>
+          <t xml:space="preserve">…また名前を呼ばれる場所ができた。悪くないよ</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.normal.composed[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">faSigning.normal.composed[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7506,14 +7506,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…失ったか。…でも終わりじゃない</t>
+          <t xml:space="preserve">…よろしく。力になるよ</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.normal.composed[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">faWelcome.normal.composed[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7538,14 +7538,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…チャンピオンか。…悪くないね</t>
+          <t xml:space="preserve">…よろしく。精一杯やるよ</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.normal.composed[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7555,29 +7555,29 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.normal.composed[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.normal.composed[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…合わないね。…仕方ない</t>
+          <t xml:space="preserve">…体は軽いね。こういう日は、伸びるんだよ</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.normal.composed[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7587,29 +7587,29 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.normal.composed[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.normal.composed[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…少し距離が開いたかな</t>
+          <t xml:space="preserve">…体が重いね。今日やっても、たぶん流れるだけ</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.normal.composed[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7619,29 +7619,29 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.normal.composed[1]</t>
+          <t xml:space="preserve">heatSelf.warm.normal.composed[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くない距離感だね。一緒にいて楽だ</t>
+          <t xml:space="preserve">…悪くはないよ。…ただ、切れが一つ落ちたかな</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.normal.composed[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7651,29 +7651,29 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.normal.composed[1]</t>
+          <t xml:space="preserve">injury.normal.composed[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…大事な存在。…それだけで十分</t>
+          <t xml:space="preserve">…少し休むよ。すぐ戻る</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.normal.composed[2]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7683,29 +7683,29 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.normal.composed[1]</t>
+          <t xml:space="preserve">injury.normal.composed[2]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう終わったことだね</t>
+          <t xml:space="preserve">…大したことじゃないから、安心して</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.normal.composed[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7715,29 +7715,29 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.normal.composed[1]</t>
+          <t xml:space="preserve">release.normal.composed[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…気になるね。…負けたくない</t>
+          <t xml:space="preserve">…そうか。お世話になったね</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.normal.composed[2]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7747,29 +7747,29 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.normal.composed[1]</t>
+          <t xml:space="preserve">release.normal.composed[2]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…負けるわけにはいかない。…絶対に</t>
+          <t xml:space="preserve">…短い間だったけど、ありがとう</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.normal.composed[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7779,29 +7779,29 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.normal.composed[1]</t>
+          <t xml:space="preserve">rentalGreeting.normal.composed[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…運命みたいなものだね。…この人とは</t>
+          <t xml:space="preserve">…短い間だけど、手は抜かないよ</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.normal.composed[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7811,29 +7811,29 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.normal.composed[1]</t>
+          <t xml:space="preserve">scoutGreeting.normal.composed[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここが自分の居場所だね。…悪くない</t>
+          <t xml:space="preserve">…見込まれたなら、応えるだけだよ</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.normal.composed[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7843,29 +7843,29 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.normal.composed[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.normal.composed[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここにいる理由が、見つからなくなった</t>
+          <t xml:space="preserve">…届かなかったか。…次だね</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.normal.composed[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7875,29 +7875,29 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.normal.composed[1]</t>
+          <t xml:space="preserve">titleDefense.normal.composed[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここで本当にやれるのかな</t>
+          <t xml:space="preserve">…防衛か。…まだ渡すつもりはないよ</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.normal.composed[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7907,29 +7907,29 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-11.normal.composed[1]</t>
+          <t xml:space="preserve">titleLoss.normal.composed[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの子は、わたくしの中にはいないの。それだけのことよ</t>
+          <t xml:space="preserve">…失ったか。…でも終わりじゃない</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.normal.composed[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7939,29 +7939,29 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">titleWin.normal.composed[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…好調は終わったか。…でも悪くない経験だった</t>
+          <t xml:space="preserve">…チャンピオンか。…悪くないね</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.normal.composed[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7971,29 +7971,29 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.normal.composed[1]</t>
+          <t xml:space="preserve">normal.composed[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…満身創痍だね。でも、ここで降りる理由はないよ</t>
+          <t xml:space="preserve">…そうか。お世話になったね</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.normal.composed[2]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.normal.composed[2]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -8003,29 +8003,29 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.normal.composed[2]</t>
+          <t xml:space="preserve">normal.composed[2]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…身体は限界に近い。それでも、最後の一戦だけは立って迎えるよ</t>
+          <t xml:space="preserve">…短い間だったけど、ありがとう</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.normal.composed[3]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.normal.composed[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -8035,29 +8035,29 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.normal.composed[3]</t>
+          <t xml:space="preserve">normal.composed[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…傷は数えきれない。まあ、最後まで残った証だと思えばいいよ</t>
+          <t xml:space="preserve">…短い間だけど、手は抜かないよ</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.normal.composed[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -8067,29 +8067,29 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.composed[1]</t>
+          <t xml:space="preserve">normal.composed[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…相手は選べない。来た順に、真っ向から受けるだけだよ</t>
+          <t xml:space="preserve">…届かなかったか。…次だね</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.normal.composed[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.normal.composed[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -8099,29 +8099,29 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.composed[2]</t>
+          <t xml:space="preserve">normal.composed[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…焦らない。目の前の一人に集中する。それでリングは渡さない</t>
+          <t xml:space="preserve">…防衛か。…まだ渡すつもりはないよ</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.normal.composed[3]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.normal.composed[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8131,29 +8131,29 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.composed[3]</t>
+          <t xml:space="preserve">normal.composed[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この一戦から、始まる。落ち着いていこうか</t>
+          <t xml:space="preserve">…失ったか。…でも終わりじゃない</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.normal.composed[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8163,29 +8163,29 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.normal.composed[1]</t>
+          <t xml:space="preserve">normal.composed[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一人片づけた。息は上がってるけど、退く理由はないよ。次、来なよ</t>
+          <t xml:space="preserve">…チャンピオンか。…悪くないね</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.normal.composed[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.normal.composed[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8195,29 +8195,29 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.normal.composed[2]</t>
+          <t xml:space="preserve">bond_39_down.normal.composed[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ足は動く。このリングは渡さない。次は誰だ</t>
+          <t xml:space="preserve">…合わないね。…仕方ない</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.normal.composed[3]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.normal.composed[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8227,29 +8227,29 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.normal.composed[3]</t>
+          <t xml:space="preserve">bond_59_down.normal.composed[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふぅ。まだ立ってる。この場所、そう簡単には空けないよ。次</t>
+          <t xml:space="preserve">…少し距離が開いたかな</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.normal.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.normal.composed[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8259,29 +8259,29 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.composed[1]</t>
+          <t xml:space="preserve">bond_60_up.normal.composed[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で繋いだ結果だ。誰が欠けても……この景色はなかった</t>
+          <t xml:space="preserve">…悪くない距離感だね。一緒にいて楽だ</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.normal.composed[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.normal.composed[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8291,29 +8291,29 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.composed[2]</t>
+          <t xml:space="preserve">bond_80_up.normal.composed[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人の手柄にするつもりはない。これは、三人の勝利だ</t>
+          <t xml:space="preserve">…大事な存在。…それだけで十分</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.normal.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.normal.composed[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8323,29 +8323,29 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.normal.composed[1]</t>
+          <t xml:space="preserve">rivalry_29_down.normal.composed[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">個人の栄誉は受け取る。だが……これで満足する理由にはならない</t>
+          <t xml:space="preserve">…もう終わったことだね</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.normal.composed[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.normal.composed[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8355,29 +8355,29 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.normal.composed[2]</t>
+          <t xml:space="preserve">rivalry_30_up.normal.composed[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次がある。その時は、チーム全員で最後に立つ</t>
+          <t xml:space="preserve">…気になるね。…負けたくない</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.normal.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.normal.composed[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8387,29 +8387,29 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.normal.composed[1]</t>
+          <t xml:space="preserve">rivalry_50_up.normal.composed[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体は限界を告げている。それでも……最後の一人を見届けるまで、退けなかった</t>
+          <t xml:space="preserve">…負けるわけにはいかない。…絶対に</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.normal.composed[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.normal.composed[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8419,29 +8419,29 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.normal.composed[2]</t>
+          <t xml:space="preserve">rivalry_70_up.normal.composed[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何度か意識が揺れた。だが、リングを降りる理由にはならなかった</t>
+          <t xml:space="preserve">…運命みたいなものだね。…この人とは</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.normal.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.normal.composed[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8451,29 +8451,29 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.composed[1]</t>
+          <t xml:space="preserve">trust_above_75.normal.composed[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…優勝か。…悪くないね。…次も行こう</t>
+          <t xml:space="preserve">…ここが自分の居場所だね。…悪くない</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.normal.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.normal.composed[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8483,29 +8483,29 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.normal.composed[1]</t>
+          <t xml:space="preserve">trust_below_20.normal.composed[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ足りないか。…次までに詰めよう</t>
+          <t xml:space="preserve">…ここにいる理由が、見つからなくなった</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.normal.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.normal.composed[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8515,29 +8515,29 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.normal.composed[1]</t>
+          <t xml:space="preserve">trust_below_35.normal.composed[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一つ勝ち。…次もこの調子で</t>
+          <t xml:space="preserve">…ここで本当にやれるのかな</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.normal.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.normal.composed[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8547,29 +8547,29 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.normal.composed[1]</t>
+          <t xml:space="preserve">GL-11.normal.composed[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くなかったね。…いい経験になった</t>
+          <t xml:space="preserve">あの子は、わたくしの中にはいないの。それだけのことよ</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.normal.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.normal.composed[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8579,29 +8579,29 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.normal.composed[1]</t>
+          <t xml:space="preserve">normal.composed[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…決勝か。…全部出し切るよ</t>
+          <t xml:space="preserve">…好調は終わったか。…でも悪くない経験だった</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.normal.composed[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.normal.composed[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8611,12 +8611,12 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.composed[1]</t>
+          <t xml:space="preserve">preFinal.normal.composed[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8626,14 +8626,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いつも通りやるよ</t>
+          <t xml:space="preserve">…満身創痍だね。でも、ここで降りる理由はないよ</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.normal.composed[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.normal.composed[2]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.composed[2]</t>
+          <t xml:space="preserve">preFinal.normal.composed[2]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8658,14 +8658,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…集中。…行こうか</t>
+          <t xml:space="preserve">…身体は限界に近い。それでも、最後の一戦だけは立って迎えるよ</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.normal.composed[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.normal.composed[3]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8675,12 +8675,12 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.normal.composed[1]</t>
+          <t xml:space="preserve">preFinal.normal.composed[3]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8690,14 +8690,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…出るよ。…やるだけだね</t>
+          <t xml:space="preserve">…傷は数えきれない。まあ、最後まで残った証だと思えばいいよ</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.normal.composed[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.normal.composed[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8707,12 +8707,12 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.normal.composed[2]</t>
+          <t xml:space="preserve">preMatch.normal.composed[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8722,14 +8722,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なるほど。じゃあ、行こうか</t>
+          <t xml:space="preserve">…相手は選べない。来た順に、真っ向から受けるだけだよ</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.normal.composed[2]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8739,12 +8739,12 @@
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">preMatch.normal.composed[2]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8754,14 +8754,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい舞台だね。…全力で行くよ</t>
+          <t xml:space="preserve">…焦らない。目の前の一人に集中する。それでリングは渡さない</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.normal.composed[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.normal.composed[3]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[2]</t>
+          <t xml:space="preserve">preMatch.normal.composed[3]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8786,14 +8786,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…負けるつもりはないよ。よろしく</t>
+          <t xml:space="preserve">…この一戦から、始まる。落ち着いていこうか</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.normal.composed[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8803,12 +8803,12 @@
       </c>
       <c r="C262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">survivor.normal.composed[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8818,14 +8818,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やったよ。…ここまで来れたか</t>
+          <t xml:space="preserve">…一人片づけた。息は上がってるけど、退く理由はないよ。次、来なよ</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.normal.composed[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.normal.composed[2]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[2]</t>
+          <t xml:space="preserve">survivor.normal.composed[2]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8850,14 +8850,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くない結末だね。みんな、ありがとう</t>
+          <t xml:space="preserve">…まだ足は動く。このリングは渡さない。次は誰だ</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.normal.composed[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.normal.composed[3]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8867,12 +8867,12 @@
       </c>
       <c r="C264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">survivor.normal.composed[3]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8882,14 +8882,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そちらの実力、確かめさせてもらうよ</t>
+          <t xml:space="preserve">…ふぅ。まだ立ってる。この場所、そう簡単には空けないよ。次</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.normal.composed[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.normal.composed[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[2]</t>
+          <t xml:space="preserve">champion.normal.composed[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8914,14 +8914,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…本気で来なよ。受けて立つから</t>
+          <t xml:space="preserve">三人で繋いだ結果だ。誰が欠けても……この景色はなかった</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.normal.composed[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.normal.composed[2]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8931,12 +8931,12 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">champion.normal.composed[2]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8946,14 +8946,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふぅん。逃げるんだ</t>
+          <t xml:space="preserve">一人の手柄にするつもりはない。これは、三人の勝利だ</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.normal.composed[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.normal.composed[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[2]</t>
+          <t xml:space="preserve">defiant.normal.composed[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8978,14 +8978,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、そういうこともあるか</t>
+          <t xml:space="preserve">個人の栄誉は受け取る。だが……これで満足する理由にはならない</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.normal.composed[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.normal.composed[2]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.normal.composed[1]</t>
+          <t xml:space="preserve">defiant.normal.composed[2]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -9010,14 +9010,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…負けたか。…次は違う結果にする</t>
+          <t xml:space="preserve">次がある。その時は、チーム全員で最後に立つ</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.normal.composed[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.normal.composed[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -9027,12 +9027,12 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.normal.composed[1]</t>
+          <t xml:space="preserve">gauntlet.normal.composed[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -9042,14 +9042,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝ったね。…いい対抗戦だった</t>
+          <t xml:space="preserve">身体は限界を告げている。それでも……最後の一人を見届けるまで、退けなかった</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.normal.composed[2]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -9059,12 +9059,12 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">gauntlet.normal.composed[2]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -9074,14 +9074,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…団体の看板、守れたかな。…悪くないね</t>
+          <t xml:space="preserve">何度か意識が揺れた。だが、リングを降りる理由にはならなかった</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.normal.composed[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.normal.composed[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -9091,12 +9091,12 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[2]</t>
+          <t xml:space="preserve">champion.normal.composed[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -9106,44 +9106,748 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝った。…うちの力を見せられたと思う</t>
+          <t xml:space="preserve">…優勝か。…悪くないね。…次も行こう</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.normal.composed[1]</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postLose.normal.composed[1]</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…まだ足りないか。…次までに詰めよう</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="40" customHeight="1">
+      <c r="A273" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.normal.composed[1]</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postMatchWin.normal.composed[1]</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…一つ勝ち。…次もこの調子で</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="40" customHeight="1">
+      <c r="A274" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.normal.composed[1]</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postWin.normal.composed[1]</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…悪くなかったね。…いい経験になった</t>
+        </is>
+      </c>
+    </row>
+    <row r="275" ht="40" customHeight="1">
+      <c r="A275" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.normal.composed[1]</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.normal.composed[1]</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…決勝か。…全部出し切るよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="276" ht="40" customHeight="1">
+      <c r="A276" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.normal.composed[1]</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.normal.composed[1]</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…いつも通りやるよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="277" ht="40" customHeight="1">
+      <c r="A277" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.normal.composed[2]</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.normal.composed[2]</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…集中。…行こうか</t>
+        </is>
+      </c>
+    </row>
+    <row r="278" ht="40" customHeight="1">
+      <c r="A278" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.normal.composed[1]</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">summon.normal.composed[1]</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…出るよ。…やるだけだね</t>
+        </is>
+      </c>
+    </row>
+    <row r="279" ht="40" customHeight="1">
+      <c r="A279" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.normal.composed[2]</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">summon.normal.composed[2]</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…なるほど。じゃあ、行こうか</t>
+        </is>
+      </c>
+    </row>
+    <row r="280" ht="40" customHeight="1">
+      <c r="A280" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.normal.composed[1]</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.composed[1]</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…いい舞台だね。…全力で行くよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="281" ht="40" customHeight="1">
+      <c r="A281" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.normal.composed[2]</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.composed[2]</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…負けるつもりはないよ。よろしく</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" ht="40" customHeight="1">
+      <c r="A282" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.normal.composed[1]</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.composed[1]</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…やったよ。…ここまで来れたか</t>
+        </is>
+      </c>
+    </row>
+    <row r="283" ht="40" customHeight="1">
+      <c r="A283" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.normal.composed[2]</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.composed[2]</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…悪くない結末だね。みんな、ありがとう</t>
+        </is>
+      </c>
+    </row>
+    <row r="284" ht="40" customHeight="1">
+      <c r="A284" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.normal.composed[1]</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.composed[1]</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…そちらの実力、確かめさせてもらうよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="40" customHeight="1">
+      <c r="A285" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.normal.composed[2]</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.composed[2]</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…本気で来なよ。受けて立つから</t>
+        </is>
+      </c>
+    </row>
+    <row r="286" ht="40" customHeight="1">
+      <c r="A286" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.normal.composed[1]</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.composed[1]</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ふぅん。逃げるんだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="287" ht="40" customHeight="1">
+      <c r="A287" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.normal.composed[2]</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.composed[2]</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…まあ、そういうこともあるか</t>
+        </is>
+      </c>
+    </row>
+    <row r="288" ht="40" customHeight="1">
+      <c r="A288" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.normal.composed[1]</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.normal.composed[1]</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…負けたか。…次は違う結果にする</t>
+        </is>
+      </c>
+    </row>
+    <row r="289" ht="40" customHeight="1">
+      <c r="A289" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.normal.composed[1]</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.normal.composed[1]</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…勝ったね。…いい対抗戦だった</t>
+        </is>
+      </c>
+    </row>
+    <row r="290" ht="40" customHeight="1">
+      <c r="A290" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.normal.composed[1]</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.composed[1]</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…団体の看板、守れたかな。…悪くないね</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="40" customHeight="1">
+      <c r="A291" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.normal.composed[2]</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.composed[2]</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…勝った。…うちの力を見せられたと思う</t>
+        </is>
+      </c>
+    </row>
+    <row r="292" ht="40" customHeight="1">
+      <c r="A292" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">ENDING_LINES.fighter.normal.composed[1]</t>
         </is>
       </c>
-      <c r="B272" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr" s="2">
+      <c r="B292" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr" s="12">
+      <c r="D292" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fighter.normal.composed[1]</t>
         </is>
       </c>
-      <c r="E272" t="inlineStr" s="2">
+      <c r="E292" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
-      <c r="F272" t="inlineStr" s="3">
+      <c r="F292" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…ここまで来れたか。…悪くない景色だね</t>
         </is>
       </c>
     </row>
+    <row r="293" ht="40" customHeight="1">
+      <c r="A293" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.normal.composed[1]</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.composed[1]</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…また名前を呼ばれる場所ができた。悪くないよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="40" customHeight="1">
+      <c r="A294" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.normal.composed[1]</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.composed[1]</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…見込まれたなら、応えるだけだよ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H272"/>
+  <autoFilter ref="A1:H294"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/鷹揚×ノーマル.xlsx
+++ b/セリフ編集/キャラタイプ別/鷹揚×ノーマル.xlsx
@@ -469,7 +469,7 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.normal.composed[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.composed.normal[1]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
@@ -484,7 +484,7 @@
       </c>
       <c r="D2" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.normal.composed[1]</t>
+          <t xml:space="preserve">atk.composed.normal[1]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr" s="2">
@@ -501,7 +501,7 @@
     <row r="3" ht="40" customHeight="1">
       <c r="A3" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.normal.composed[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.composed.normal[2]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
@@ -516,7 +516,7 @@
       </c>
       <c r="D3" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.normal.composed[2]</t>
+          <t xml:space="preserve">atk.composed.normal[2]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="2">
@@ -533,7 +533,7 @@
     <row r="4" ht="40" customHeight="1">
       <c r="A4" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.normal.composed[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.composed.normal[3]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
@@ -548,7 +548,7 @@
       </c>
       <c r="D4" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.normal.composed[3]</t>
+          <t xml:space="preserve">atk.composed.normal[3]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr" s="2">
@@ -565,7 +565,7 @@
     <row r="5" ht="40" customHeight="1">
       <c r="A5" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.normal.composed[4]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.composed.normal[4]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
@@ -580,7 +580,7 @@
       </c>
       <c r="D5" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.normal.composed[4]</t>
+          <t xml:space="preserve">atk.composed.normal[4]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr" s="2">
@@ -597,7 +597,7 @@
     <row r="6" ht="40" customHeight="1">
       <c r="A6" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.normal.composed[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.composed.normal[1]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
@@ -612,7 +612,7 @@
       </c>
       <c r="D6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.normal.composed[1]</t>
+          <t xml:space="preserve">bigmove.composed.normal[1]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr" s="2">
@@ -629,7 +629,7 @@
     <row r="7" ht="40" customHeight="1">
       <c r="A7" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.normal.composed[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.composed.normal[2]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
@@ -644,7 +644,7 @@
       </c>
       <c r="D7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.normal.composed[2]</t>
+          <t xml:space="preserve">bigmove.composed.normal[2]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr" s="2">
@@ -661,7 +661,7 @@
     <row r="8" ht="40" customHeight="1">
       <c r="A8" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.normal.composed[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.composed.normal[3]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
@@ -676,7 +676,7 @@
       </c>
       <c r="D8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.normal.composed[3]</t>
+          <t xml:space="preserve">bigmove.composed.normal[3]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr" s="2">
@@ -693,7 +693,7 @@
     <row r="9" ht="40" customHeight="1">
       <c r="A9" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.normal.composed[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.composed.normal[1]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
@@ -708,7 +708,7 @@
       </c>
       <c r="D9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.normal.composed[1]</t>
+          <t xml:space="preserve">climax.composed.normal[1]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr" s="2">
@@ -725,7 +725,7 @@
     <row r="10" ht="40" customHeight="1">
       <c r="A10" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.normal.composed[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.composed.normal[2]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
@@ -740,7 +740,7 @@
       </c>
       <c r="D10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.normal.composed[2]</t>
+          <t xml:space="preserve">climax.composed.normal[2]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr" s="2">
@@ -757,7 +757,7 @@
     <row r="11" ht="40" customHeight="1">
       <c r="A11" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.normal.composed[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.composed.normal[1]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
@@ -772,7 +772,7 @@
       </c>
       <c r="D11" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">badWinner.normal.composed[1]</t>
+          <t xml:space="preserve">badWinner.composed.normal[1]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr" s="2">
@@ -789,7 +789,7 @@
     <row r="12" ht="40" customHeight="1">
       <c r="A12" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.normal.composed[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.composed.normal[1]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
@@ -804,7 +804,7 @@
       </c>
       <c r="D12" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodWinner.normal.composed[1]</t>
+          <t xml:space="preserve">goodWinner.composed.normal[1]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr" s="2">
@@ -821,7 +821,7 @@
     <row r="13" ht="40" customHeight="1">
       <c r="A13" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">FIRST_MEET_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
@@ -836,7 +836,7 @@
       </c>
       <c r="D13" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr" s="2">
@@ -853,7 +853,7 @@
     <row r="14" ht="40" customHeight="1">
       <c r="A14" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.normal.composed[1]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.composed.normal[1]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
@@ -868,7 +868,7 @@
       </c>
       <c r="D14" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.normal.composed[1]</t>
+          <t xml:space="preserve">loser.composed.normal[1]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr" s="2">
@@ -885,7 +885,7 @@
     <row r="15" ht="40" customHeight="1">
       <c r="A15" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.normal.composed[2]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.composed.normal[2]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
@@ -900,7 +900,7 @@
       </c>
       <c r="D15" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.normal.composed[2]</t>
+          <t xml:space="preserve">loser.composed.normal[2]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr" s="2">
@@ -917,7 +917,7 @@
     <row r="16" ht="40" customHeight="1">
       <c r="A16" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.normal.composed[1]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.composed.normal[1]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
@@ -932,7 +932,7 @@
       </c>
       <c r="D16" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.normal.composed[1]</t>
+          <t xml:space="preserve">winner.composed.normal[1]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr" s="2">
@@ -949,7 +949,7 @@
     <row r="17" ht="40" customHeight="1">
       <c r="A17" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.normal.composed[2]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.composed.normal[2]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
@@ -964,7 +964,7 @@
       </c>
       <c r="D17" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.normal.composed[2]</t>
+          <t xml:space="preserve">winner.composed.normal[2]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr" s="2">
@@ -981,7 +981,7 @@
     <row r="18" ht="40" customHeight="1">
       <c r="A18" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.normal.composed[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.composed.normal[1]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
@@ -996,7 +996,7 @@
       </c>
       <c r="D18" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.normal.composed[1]</t>
+          <t xml:space="preserve">competition_won.composed.normal[1]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="2">
@@ -1013,7 +1013,7 @@
     <row r="19" ht="40" customHeight="1">
       <c r="A19" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.normal.composed[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.composed.normal[1]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="D19" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.normal.composed[1]</t>
+          <t xml:space="preserve">direct.composed.normal[1]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr" s="2">
@@ -1045,7 +1045,7 @@
     <row r="20" ht="40" customHeight="1">
       <c r="A20" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.normal.composed[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.composed.normal[1]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="D20" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.normal.composed[1]</t>
+          <t xml:space="preserve">fa_signing.composed.normal[1]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="2">
@@ -1077,7 +1077,7 @@
     <row r="21" ht="40" customHeight="1">
       <c r="A21" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.normal.composed.hit[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.composed.normal.hit[1]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="D21" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed.hit[1]</t>
+          <t xml:space="preserve">composed.normal.hit[1]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr" s="2">
@@ -1109,7 +1109,7 @@
     <row r="22" ht="40" customHeight="1">
       <c r="A22" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.normal.composed.hit[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.composed.normal.hit[2]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="D22" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed.hit[2]</t>
+          <t xml:space="preserve">composed.normal.hit[2]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="2">
@@ -1141,7 +1141,7 @@
     <row r="23" ht="40" customHeight="1">
       <c r="A23" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.normal.composed.win[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.composed.normal.win[1]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="D23" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed.win[1]</t>
+          <t xml:space="preserve">composed.normal.win[1]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="2">
@@ -1173,7 +1173,7 @@
     <row r="24" ht="40" customHeight="1">
       <c r="A24" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.normal.composed.win[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.composed.normal.win[2]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D24" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed.win[2]</t>
+          <t xml:space="preserve">composed.normal.win[2]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr" s="2">
@@ -1205,7 +1205,7 @@
     <row r="25" ht="40" customHeight="1">
       <c r="A25" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="D25" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr" s="2">
@@ -1237,7 +1237,7 @@
     <row r="26" ht="40" customHeight="1">
       <c r="A26" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.normal.composed[2]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.composed.normal[2]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="D26" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[2]</t>
+          <t xml:space="preserve">composed.normal[2]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr" s="2">
@@ -1269,7 +1269,7 @@
     <row r="27" ht="40" customHeight="1">
       <c r="A27" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.normal.composed[3]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.composed.normal[3]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="D27" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[3]</t>
+          <t xml:space="preserve">composed.normal[3]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr" s="2">
@@ -1301,7 +1301,7 @@
     <row r="28" ht="40" customHeight="1">
       <c r="A28" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="D28" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr" s="2">
@@ -1333,7 +1333,7 @@
     <row r="29" ht="40" customHeight="1">
       <c r="A29" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.normal.composed[2]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.composed.normal[2]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D29" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[2]</t>
+          <t xml:space="preserve">composed.normal[2]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr" s="2">
@@ -1365,7 +1365,7 @@
     <row r="30" ht="40" customHeight="1">
       <c r="A30" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.normal.composed[3]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.composed.normal[3]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="D30" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[3]</t>
+          <t xml:space="preserve">composed.normal[3]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr" s="2">
@@ -1397,7 +1397,7 @@
     <row r="31" ht="40" customHeight="1">
       <c r="A31" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="D31" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr" s="2">
@@ -1429,7 +1429,7 @@
     <row r="32" ht="40" customHeight="1">
       <c r="A32" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.normal.composed[2]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.composed.normal[2]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D32" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[2]</t>
+          <t xml:space="preserve">composed.normal[2]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr" s="2">
@@ -1461,7 +1461,7 @@
     <row r="33" ht="40" customHeight="1">
       <c r="A33" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.normal.composed[3]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.composed.normal[3]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="D33" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[3]</t>
+          <t xml:space="preserve">composed.normal[3]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr" s="2">
@@ -1493,7 +1493,7 @@
     <row r="34" ht="40" customHeight="1">
       <c r="A34" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="D34" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr" s="2">
@@ -1525,7 +1525,7 @@
     <row r="35" ht="40" customHeight="1">
       <c r="A35" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.normal.composed[2]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.composed.normal[2]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D35" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[2]</t>
+          <t xml:space="preserve">composed.normal[2]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr" s="2">
@@ -1557,7 +1557,7 @@
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.normal.composed[3]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.composed.normal[3]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="D36" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[3]</t>
+          <t xml:space="preserve">composed.normal[3]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr" s="2">
@@ -1589,7 +1589,7 @@
     <row r="37" ht="40" customHeight="1">
       <c r="A37" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="D37" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr" s="2">
@@ -1621,7 +1621,7 @@
     <row r="38" ht="40" customHeight="1">
       <c r="A38" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.normal.composed[2]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.composed.normal[2]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="D38" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[2]</t>
+          <t xml:space="preserve">composed.normal[2]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr" s="2">
@@ -1653,7 +1653,7 @@
     <row r="39" ht="40" customHeight="1">
       <c r="A39" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="D39" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr" s="2">
@@ -1685,7 +1685,7 @@
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.normal.composed[2]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.composed.normal[2]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D40" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[2]</t>
+          <t xml:space="preserve">composed.normal[2]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr" s="2">
@@ -1717,7 +1717,7 @@
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.normal.composed[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.composed.normal[1]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="D41" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ahead.normal.composed[1]</t>
+          <t xml:space="preserve">ahead.composed.normal[1]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr" s="2">
@@ -1749,7 +1749,7 @@
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.normal.composed[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.composed.normal[1]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="D42" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">behind.normal.composed[1]</t>
+          <t xml:space="preserve">behind.composed.normal[1]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr" s="2">
@@ -1781,7 +1781,7 @@
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.normal.composed[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.composed.normal[1]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="D43" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.normal.composed[1]</t>
+          <t xml:space="preserve">loser.composed.normal[1]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr" s="2">
@@ -1813,7 +1813,7 @@
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.normal.composed[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.composed.normal[1]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="D44" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.normal.composed[1]</t>
+          <t xml:space="preserve">winner.composed.normal[1]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr" s="2">
@@ -1845,7 +1845,7 @@
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.normal.composed[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.composed.normal[1]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="D45" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.normal.composed[1]</t>
+          <t xml:space="preserve">loser.composed.normal[1]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr" s="2">
@@ -1877,7 +1877,7 @@
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.normal.composed[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.composed.normal[1]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.normal.composed[1]</t>
+          <t xml:space="preserve">winner.composed.normal[1]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr" s="2">
@@ -1909,7 +1909,7 @@
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.normal.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.composed.normal[1]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="D47" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.normal.composed[1]</t>
+          <t xml:space="preserve">attacker.composed.normal[1]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr" s="2">
@@ -1941,7 +1941,7 @@
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.normal.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.composed.normal[1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="D48" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.normal.composed[1]</t>
+          <t xml:space="preserve">defender.composed.normal[1]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr" s="2">
@@ -1973,7 +1973,7 @@
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.normal.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.composed.normal[1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1988,7 +1988,7 @@
       </c>
       <c r="D49" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.normal.composed[1]</t>
+          <t xml:space="preserve">attacker.composed.normal[1]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr" s="2">
@@ -2005,7 +2005,7 @@
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.normal.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.composed.normal[1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.normal.composed[1]</t>
+          <t xml:space="preserve">defender.composed.normal[1]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr" s="2">
@@ -2037,7 +2037,7 @@
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.normal.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.composed.normal[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.normal.composed[1]</t>
+          <t xml:space="preserve">attacker.composed.normal[1]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr" s="2">
@@ -2069,7 +2069,7 @@
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.normal.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.composed.normal[1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.normal.composed[1]</t>
+          <t xml:space="preserve">defender.composed.normal[1]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr" s="2">
@@ -2101,7 +2101,7 @@
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.normal.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.composed.normal[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateAttacker.normal.composed[1]</t>
+          <t xml:space="preserve">fateAttacker.composed.normal[1]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr" s="2">
@@ -2133,7 +2133,7 @@
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.normal.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.composed.normal[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateDefender.normal.composed[1]</t>
+          <t xml:space="preserve">fateDefender.composed.normal[1]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr" s="2">
@@ -2165,7 +2165,7 @@
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.normal.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.composed.normal[1]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.normal.composed[1]</t>
+          <t xml:space="preserve">loserLines.composed.normal[1]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr" s="2">
@@ -2197,7 +2197,7 @@
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.normal.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.composed.normal[1]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.normal.composed[1]</t>
+          <t xml:space="preserve">winnerLines.composed.normal[1]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr" s="2">
@@ -2229,7 +2229,7 @@
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.normal.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.composed.normal[1]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateLoser.normal.composed[1]</t>
+          <t xml:space="preserve">fateLoser.composed.normal[1]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr" s="2">
@@ -2261,7 +2261,7 @@
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.normal.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.composed.normal[1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateWinner.normal.composed[1]</t>
+          <t xml:space="preserve">fateWinner.composed.normal[1]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr" s="2">
@@ -2293,7 +2293,7 @@
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.normal.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.composed.normal[1]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.normal.composed[1]</t>
+          <t xml:space="preserve">loser.composed.normal[1]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr" s="2">
@@ -2325,7 +2325,7 @@
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.normal.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.composed.normal[1]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="D60" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.normal.composed[1]</t>
+          <t xml:space="preserve">winner.composed.normal[1]</t>
         </is>
       </c>
       <c r="E60" t="inlineStr" s="2">
@@ -2357,7 +2357,7 @@
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.normal.composed[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.composed.normal[1]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.normal.composed[1]</t>
+          <t xml:space="preserve">loserLines.composed.normal[1]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr" s="2">
@@ -2389,7 +2389,7 @@
     <row r="62" ht="40" customHeight="1">
       <c r="A62" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.normal.composed[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.composed.normal[1]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="D62" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.normal.composed[1]</t>
+          <t xml:space="preserve">winnerLines.composed.normal[1]</t>
         </is>
       </c>
       <c r="E62" t="inlineStr" s="2">
@@ -2421,7 +2421,7 @@
     <row r="63" ht="40" customHeight="1">
       <c r="A63" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.normal.composed[1]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.composed.normal[1]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="D63" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">awakening.normal.composed[1]</t>
+          <t xml:space="preserve">awakening.composed.normal[1]</t>
         </is>
       </c>
       <c r="E63" t="inlineStr" s="2">
@@ -3221,7 +3221,7 @@
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.normal.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.composed.normal[1]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.normal.composed[1]</t>
+          <t xml:space="preserve">accepted.composed.normal[1]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr" s="2">
@@ -3253,7 +3253,7 @@
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.normal.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.composed.normal[1]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.normal.composed[1]</t>
+          <t xml:space="preserve">defended.composed.normal[1]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="2">
@@ -3285,7 +3285,7 @@
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.normal.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.composed.normal[1]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.normal.composed[1]</t>
+          <t xml:space="preserve">defense_failed.composed.normal[1]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr" s="2">
@@ -3317,7 +3317,7 @@
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.default.normal.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.default.composed.normal[1]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">default.normal.composed[1]</t>
+          <t xml:space="preserve">default.composed.normal[1]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr" s="2">
@@ -3349,7 +3349,7 @@
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.normal.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.composed.normal[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.normal.composed[1]</t>
+          <t xml:space="preserve">former_champ.composed.normal[1]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr" s="2">
@@ -3381,7 +3381,7 @@
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.heel.normal.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.heel.composed.normal[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heel.normal.composed[1]</t>
+          <t xml:space="preserve">heel.composed.normal[1]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="2">
@@ -3413,7 +3413,7 @@
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.high_trust.normal.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.high_trust.composed.normal[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high_trust.normal.composed[1]</t>
+          <t xml:space="preserve">high_trust.composed.normal[1]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
@@ -3445,7 +3445,7 @@
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.normal.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.composed.normal[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_former_champ.normal.composed[1]</t>
+          <t xml:space="preserve">accept_former_champ.composed.normal[1]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
@@ -3477,7 +3477,7 @@
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.normal.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.composed.normal[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_heel.normal.composed[1]</t>
+          <t xml:space="preserve">accept_heel.composed.normal[1]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
@@ -3509,7 +3509,7 @@
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.normal.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.composed.normal[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_no_title.normal.composed[1]</t>
+          <t xml:space="preserve">accept_no_title.composed.normal[1]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
@@ -3541,7 +3541,7 @@
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.normal.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.composed.normal[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.normal.composed[1]</t>
+          <t xml:space="preserve">accept_terminal.composed.normal[1]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
@@ -3573,7 +3573,7 @@
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.normal.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.composed.normal[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_winless.normal.composed[1]</t>
+          <t xml:space="preserve">accept_winless.composed.normal[1]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
@@ -3605,7 +3605,7 @@
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.normal.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.composed.normal[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.normal.composed[1]</t>
+          <t xml:space="preserve">refuse_champ.composed.normal[1]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
@@ -3637,7 +3637,7 @@
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.normal.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.composed.normal[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_distrust.normal.composed[1]</t>
+          <t xml:space="preserve">refuse_distrust.composed.normal[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
@@ -3669,7 +3669,7 @@
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.normal.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.composed.normal[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_fighting.normal.composed[1]</t>
+          <t xml:space="preserve">refuse_fighting.composed.normal[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
@@ -3701,7 +3701,7 @@
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.normal.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.composed.normal[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_heel.normal.composed[1]</t>
+          <t xml:space="preserve">refuse_heel.composed.normal[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
@@ -3733,7 +3733,7 @@
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.normal.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.composed.normal[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.normal.composed[1]</t>
+          <t xml:space="preserve">A1_champion.composed.normal[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
@@ -3765,7 +3765,7 @@
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.normal.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.composed.normal[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.normal.composed[1]</t>
+          <t xml:space="preserve">A2_uncrowned.composed.normal[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
@@ -3797,7 +3797,7 @@
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.normal.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.composed.normal[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.normal.composed[1]</t>
+          <t xml:space="preserve">A3_heel.composed.normal[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
@@ -3829,7 +3829,7 @@
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.normal.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.composed.normal[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.normal.composed[1]</t>
+          <t xml:space="preserve">A4_veteran.composed.normal[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
@@ -3861,7 +3861,7 @@
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.normal.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.composed.normal[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.normal.composed[1]</t>
+          <t xml:space="preserve">B1_young.composed.normal[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
@@ -3893,7 +3893,7 @@
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.normal.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.composed.normal[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.normal.composed[1]</t>
+          <t xml:space="preserve">B2_prime.composed.normal[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
@@ -3925,7 +3925,7 @@
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.normal.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.composed.normal[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.normal.composed[1]</t>
+          <t xml:space="preserve">B3_older.composed.normal[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
@@ -3957,7 +3957,7 @@
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.normal.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.composed.normal[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3972,7 +3972,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.normal.composed[1]</t>
+          <t xml:space="preserve">B4_champion_injury.composed.normal[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -3989,7 +3989,7 @@
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -4021,7 +4021,7 @@
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.normal.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.composed.normal[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.normal.composed[1]</t>
+          <t xml:space="preserve">raise_accept.composed.normal[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -4053,7 +4053,7 @@
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.normal.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.composed.normal[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.normal.composed[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.composed.normal[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -4085,7 +4085,7 @@
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.normal.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.composed.normal[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.normal.composed[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.composed.normal[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -4117,7 +4117,7 @@
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.normal.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.composed.normal[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.normal.composed[1]</t>
+          <t xml:space="preserve">raise_open.composed.normal[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -4149,7 +4149,7 @@
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.normal.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.composed.normal[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.normal.composed[1]</t>
+          <t xml:space="preserve">raise_refuse.composed.normal[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4181,7 +4181,7 @@
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.normal.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.composed.normal[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.normal.composed[1]</t>
+          <t xml:space="preserve">sudden_departure.composed.normal[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4213,7 +4213,7 @@
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.normal.composed[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.composed.normal[2]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.normal.composed[2]</t>
+          <t xml:space="preserve">sudden_departure.composed.normal[2]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -4245,7 +4245,7 @@
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.normal.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.composed.normal[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.normal.composed[1]</t>
+          <t xml:space="preserve">transfer_listen.composed.normal[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -4277,7 +4277,7 @@
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.normal.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.composed.normal[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.normal.composed[1]</t>
+          <t xml:space="preserve">transfer_open.composed.normal[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
@@ -4309,7 +4309,7 @@
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.normal.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.composed.normal[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4324,7 +4324,7 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.normal.composed[1]</t>
+          <t xml:space="preserve">transfer_release.composed.normal[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -4341,7 +4341,7 @@
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.normal.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.composed.normal[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.normal.composed[1]</t>
+          <t xml:space="preserve">transfer_retain_fail.composed.normal[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
@@ -4373,7 +4373,7 @@
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.normal.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.composed.normal[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.normal.composed[1]</t>
+          <t xml:space="preserve">transfer_retain_success.composed.normal[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
@@ -4405,7 +4405,7 @@
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.blocked.normal.composed[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.blocked.composed.normal[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">blocked.normal.composed[1]</t>
+          <t xml:space="preserve">blocked.composed.normal[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
@@ -4438,7 +4438,7 @@
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.fail.normal.composed[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.fail.composed.normal[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fail.normal.composed[1]</t>
+          <t xml:space="preserve">fail.composed.normal[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
@@ -4471,7 +4471,7 @@
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.normal.composed[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.composed.normal[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.normal.composed[1]</t>
+          <t xml:space="preserve">start.composed.normal[1]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
@@ -4504,7 +4504,7 @@
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.success.normal.composed[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.success.composed.normal[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">success.normal.composed[1]</t>
+          <t xml:space="preserve">success.composed.normal[1]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
@@ -4537,7 +4537,7 @@
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
@@ -4569,7 +4569,7 @@
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
@@ -4601,7 +4601,7 @@
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.normal.composed[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.composed.normal[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fresh.normal.composed[1]</t>
+          <t xml:space="preserve">fresh.composed.normal[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
@@ -4633,7 +4633,7 @@
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.normal.composed[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.composed.normal[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heavy.normal.composed[1]</t>
+          <t xml:space="preserve">heavy.composed.normal[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
@@ -4665,7 +4665,7 @@
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.normal.composed[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.composed.normal[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warm.normal.composed[1]</t>
+          <t xml:space="preserve">warm.composed.normal[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
@@ -4697,7 +4697,7 @@
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.normal.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.composed.normal[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.normal.composed[1]</t>
+          <t xml:space="preserve">cap_reached.composed.normal[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
@@ -4729,7 +4729,7 @@
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.normal.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.composed.normal[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.normal.composed[1]</t>
+          <t xml:space="preserve">ovr_elite.composed.normal[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
@@ -4761,7 +4761,7 @@
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.normal.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.composed.normal[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.normal.composed[1]</t>
+          <t xml:space="preserve">ovr_growth.composed.normal[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -4793,7 +4793,7 @@
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.normal.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.composed.normal[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.normal.composed[1]</t>
+          <t xml:space="preserve">ovr_legend.composed.normal[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4825,7 +4825,7 @@
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.normal.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.composed.normal[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.normal.composed[1]</t>
+          <t xml:space="preserve">pop_growth.composed.normal[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
@@ -4857,7 +4857,7 @@
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.normal.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.composed.normal[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.normal.composed[1]</t>
+          <t xml:space="preserve">pop_star.composed.normal[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
@@ -4889,7 +4889,7 @@
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
@@ -4921,7 +4921,7 @@
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
@@ -4953,7 +4953,7 @@
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
@@ -4985,7 +4985,7 @@
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.normal.composed[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.composed.normal[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.normal.composed[1]</t>
+          <t xml:space="preserve">defeat.composed.normal[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
@@ -5017,7 +5017,7 @@
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.normal.composed[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.composed.normal[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.normal.composed[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.composed.normal[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
@@ -5049,7 +5049,7 @@
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.normal.composed[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.composed.normal[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.normal.composed[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.composed.normal[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
@@ -5081,7 +5081,7 @@
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.normal.composed[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.composed.normal[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.normal.composed[1]</t>
+          <t xml:space="preserve">penalty_end.composed.normal[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
@@ -5113,7 +5113,7 @@
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.normal.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.composed.normal[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.normal.composed[1]</t>
+          <t xml:space="preserve">bestMatch.composed.normal[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
@@ -5145,7 +5145,7 @@
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.normal.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.composed.normal[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.composed[1]</t>
+          <t xml:space="preserve">champion.composed.normal[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
@@ -5177,7 +5177,7 @@
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.normal.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.composed.normal[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.normal.composed[1]</t>
+          <t xml:space="preserve">hallOfFame.composed.normal[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
@@ -5209,7 +5209,7 @@
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.normal.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.composed.normal[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.normal.composed[1]</t>
+          <t xml:space="preserve">mediaAward.composed.normal[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
@@ -5241,7 +5241,7 @@
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.normal.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.composed.normal[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.normal.composed[1]</t>
+          <t xml:space="preserve">mvp.composed.normal[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
@@ -5273,7 +5273,7 @@
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.normal.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.composed.normal[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.normal.composed[1]</t>
+          <t xml:space="preserve">rookie.composed.normal[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
@@ -5305,7 +5305,7 @@
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
@@ -5337,7 +5337,7 @@
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.composed[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.normal[2]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[2]</t>
+          <t xml:space="preserve">composed.normal[2]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
@@ -5369,7 +5369,7 @@
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.composed[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.normal[3]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[3]</t>
+          <t xml:space="preserve">composed.normal[3]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
@@ -5401,7 +5401,7 @@
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
@@ -5433,7 +5433,7 @@
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.composed[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.normal[2]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[2]</t>
+          <t xml:space="preserve">composed.normal[2]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
@@ -5465,7 +5465,7 @@
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.composed[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.normal[3]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[3]</t>
+          <t xml:space="preserve">composed.normal[3]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
@@ -5497,7 +5497,7 @@
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.normal.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.composed.normal[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.normal.composed[1]</t>
+          <t xml:space="preserve">N1.composed.normal[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
@@ -5529,7 +5529,7 @@
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.normal.composed[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.composed.normal[2]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.normal.composed[2]</t>
+          <t xml:space="preserve">N1.composed.normal[2]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
@@ -5561,7 +5561,7 @@
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.normal.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.composed.normal[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.normal.composed[1]</t>
+          <t xml:space="preserve">N2.composed.normal[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
@@ -5593,7 +5593,7 @@
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.normal.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.composed.normal[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.normal.composed[1]</t>
+          <t xml:space="preserve">N3.composed.normal[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
@@ -5625,7 +5625,7 @@
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.normal.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.composed.normal[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.normal.composed[1]</t>
+          <t xml:space="preserve">N4.composed.normal[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
@@ -5657,7 +5657,7 @@
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.normal.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.composed.normal[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.normal.composed[1]</t>
+          <t xml:space="preserve">N5_low.composed.normal[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
@@ -5689,7 +5689,7 @@
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.normal.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.composed.normal[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.normal.composed[1]</t>
+          <t xml:space="preserve">N5_warning.composed.normal[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
@@ -5721,7 +5721,7 @@
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.normal.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">breakthrough.voice.normal.composed[1]</t>
+          <t xml:space="preserve">breakthrough.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
@@ -5753,7 +5753,7 @@
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.normal.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.normal.composed[1]</t>
+          <t xml:space="preserve">G1.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
@@ -5785,7 +5785,7 @@
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.normal.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice.normal.composed[1]</t>
+          <t xml:space="preserve">G2.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
@@ -5817,7 +5817,7 @@
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.normal.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.normal.composed[1]</t>
+          <t xml:space="preserve">G3.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
@@ -5849,7 +5849,7 @@
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.normal.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G4.voice.normal.composed[1]</t>
+          <t xml:space="preserve">G4.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5881,7 +5881,7 @@
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.normal.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice.normal.composed[1]</t>
+          <t xml:space="preserve">R2.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5913,7 +5913,7 @@
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.normal.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.composed.normal[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal.normal.composed[1]</t>
+          <t xml:space="preserve">R3.modal.composed.normal[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -5945,7 +5945,7 @@
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.normal.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice.normal.composed[1]</t>
+          <t xml:space="preserve">R4.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -5977,7 +5977,7 @@
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.normal.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice.normal.composed[1]</t>
+          <t xml:space="preserve">R5.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -6009,7 +6009,7 @@
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.normal.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.composed.normal[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_insult.normal.composed[1]</t>
+          <t xml:space="preserve">bonus_insult.composed.normal[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -6041,7 +6041,7 @@
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.normal.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.composed.normal[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.normal.composed[1]</t>
+          <t xml:space="preserve">bonus.composed.normal[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -6073,7 +6073,7 @@
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.normal.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.composed.normal[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.normal.composed[1]</t>
+          <t xml:space="preserve">camp.composed.normal[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -6105,7 +6105,7 @@
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.normal.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.composed.normal[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.normal.composed[1]</t>
+          <t xml:space="preserve">encourage_high_trust.composed.normal[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -6137,7 +6137,7 @@
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.normal.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.composed.normal[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.normal.composed[1]</t>
+          <t xml:space="preserve">encourage.composed.normal[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6169,7 +6169,7 @@
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.normal.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.composed.normal[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6184,7 +6184,7 @@
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.normal.composed[1]</t>
+          <t xml:space="preserve">media.composed.normal[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6201,7 +6201,7 @@
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.normal.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.composed.normal[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.normal.composed[1]</t>
+          <t xml:space="preserve">party.composed.normal[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6233,7 +6233,7 @@
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.normal.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.composed.normal[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.normal.composed[1]</t>
+          <t xml:space="preserve">refresh_leave.composed.normal[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6265,7 +6265,7 @@
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.normal.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.composed.normal[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.normal.composed[1]</t>
+          <t xml:space="preserve">special_treatment.composed.normal[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6297,7 +6297,7 @@
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.normal.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.composed.normal[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.normal.composed[1]</t>
+          <t xml:space="preserve">trainer.composed.normal[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6329,7 +6329,7 @@
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.normal.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.composed.normal[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.normal.composed[1]</t>
+          <t xml:space="preserve">E1.composed.normal[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6361,7 +6361,7 @@
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E4.normal.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E4.composed.normal[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E4.normal.composed[1]</t>
+          <t xml:space="preserve">E4.composed.normal[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6393,7 +6393,7 @@
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.normal.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.composed.normal[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6408,7 +6408,7 @@
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.normal.composed[1]</t>
+          <t xml:space="preserve">E6.composed.normal[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6425,7 +6425,7 @@
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.normal.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.normal[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.normal.composed[1]</t>
+          <t xml:space="preserve">S_boycott.composed.normal[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6457,7 +6457,7 @@
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.normal.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.composed.normal[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.normal.composed[1]</t>
+          <t xml:space="preserve">S_grumble.composed.normal[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6489,7 +6489,7 @@
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.normal.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.composed.normal[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.normal.composed[1]</t>
+          <t xml:space="preserve">S_sns.composed.normal[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6521,7 +6521,7 @@
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.normal.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.composed.normal[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.normal.composed[1]</t>
+          <t xml:space="preserve">S1.composed.normal[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6553,7 +6553,7 @@
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.normal.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.composed.normal[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.normal.composed[1]</t>
+          <t xml:space="preserve">S2.composed.normal[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6585,7 +6585,7 @@
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.normal.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.composed.normal[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6600,7 +6600,7 @@
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.normal.composed[1]</t>
+          <t xml:space="preserve">S3.composed.normal[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6617,7 +6617,7 @@
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.normal.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.composed.normal[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6632,7 +6632,7 @@
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.normal.composed[1]</t>
+          <t xml:space="preserve">S4_direct.composed.normal[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6649,7 +6649,7 @@
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.normal.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.composed.normal[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.normal.composed[1]</t>
+          <t xml:space="preserve">S4_silent.composed.normal[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6681,7 +6681,7 @@
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.normal.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.composed.normal[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.normal.composed[1]</t>
+          <t xml:space="preserve">S5.composed.normal[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6713,7 +6713,7 @@
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.normal.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.composed.normal[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.normal.composed[1]</t>
+          <t xml:space="preserve">S6.composed.normal[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6745,7 +6745,7 @@
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.normal.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.composed.normal[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.normal.composed[1]</t>
+          <t xml:space="preserve">B1.composed.normal[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6777,7 +6777,7 @@
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.normal.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.composed.normal[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6792,7 +6792,7 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.normal.composed[1]</t>
+          <t xml:space="preserve">B2_fighter1.composed.normal[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6809,7 +6809,7 @@
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.normal.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.composed.normal[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6824,7 +6824,7 @@
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.normal.composed[1]</t>
+          <t xml:space="preserve">B2_fighter2.composed.normal[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6841,7 +6841,7 @@
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.normal.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.composed.normal[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.normal.composed[1]</t>
+          <t xml:space="preserve">B4_brand.composed.normal[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6873,7 +6873,7 @@
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.normal.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.composed.normal[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.normal.composed[1]</t>
+          <t xml:space="preserve">B4_cm.composed.normal[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6905,7 +6905,7 @@
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.normal.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.composed.normal[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.normal.composed[1]</t>
+          <t xml:space="preserve">B4_fan.composed.normal[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6937,7 +6937,7 @@
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.normal.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.composed.normal[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.normal.composed[1]</t>
+          <t xml:space="preserve">B4_fashion.composed.normal[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6969,7 +6969,7 @@
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.normal.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.composed.normal[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6984,7 +6984,7 @@
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.normal.composed[1]</t>
+          <t xml:space="preserve">B4_gravure.composed.normal[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -7001,7 +7001,7 @@
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.normal.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.composed.normal[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.normal.composed[1]</t>
+          <t xml:space="preserve">B4_variety.composed.normal[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -7033,7 +7033,7 @@
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.normal.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.composed.normal[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -7048,7 +7048,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.normal.composed[1]</t>
+          <t xml:space="preserve">B4.composed.normal[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -7065,7 +7065,7 @@
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -7097,7 +7097,7 @@
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -7112,7 +7112,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -7129,7 +7129,7 @@
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.normal.composed[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.composed.normal[2]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[2]</t>
+          <t xml:space="preserve">composed.normal[2]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7161,7 +7161,7 @@
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7193,7 +7193,7 @@
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7208,7 +7208,7 @@
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7225,7 +7225,7 @@
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7257,7 +7257,7 @@
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.normal.composed[2]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.composed.normal[2]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[2]</t>
+          <t xml:space="preserve">composed.normal[2]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7289,7 +7289,7 @@
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.composed.normal[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.normal.composed[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.composed.normal[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7321,7 +7321,7 @@
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.composed.normal[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.normal.composed[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.composed.normal[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7353,7 +7353,7 @@
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.composed.normal[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.normal.composed[1]</t>
+          <t xml:space="preserve">draftInterest.composed.normal[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7385,7 +7385,7 @@
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.composed.normal[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.normal.composed[1]</t>
+          <t xml:space="preserve">draftJoin.composed.normal[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7417,7 +7417,7 @@
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.normal.composed[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.composed.normal[2]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.normal.composed[2]</t>
+          <t xml:space="preserve">draftJoin.composed.normal[2]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7449,7 +7449,7 @@
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.composed.normal[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.normal.composed[1]</t>
+          <t xml:space="preserve">faGreeting.composed.normal[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7481,7 +7481,7 @@
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.composed.normal[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.normal.composed[1]</t>
+          <t xml:space="preserve">faSigning.composed.normal[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7513,7 +7513,7 @@
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.composed.normal[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.normal.composed[1]</t>
+          <t xml:space="preserve">faWelcome.composed.normal[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7545,7 +7545,7 @@
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.composed.normal[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.normal.composed[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.composed.normal[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7577,7 +7577,7 @@
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.composed.normal[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.normal.composed[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.composed.normal[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7609,7 +7609,7 @@
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.composed.normal[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7624,7 +7624,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.normal.composed[1]</t>
+          <t xml:space="preserve">heatSelf.warm.composed.normal[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7641,7 +7641,7 @@
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.composed.normal[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7656,7 +7656,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.normal.composed[1]</t>
+          <t xml:space="preserve">injury.composed.normal[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7673,7 +7673,7 @@
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.normal.composed[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.composed.normal[2]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7688,7 +7688,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.normal.composed[2]</t>
+          <t xml:space="preserve">injury.composed.normal[2]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7705,7 +7705,7 @@
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.composed.normal[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7720,7 +7720,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.normal.composed[1]</t>
+          <t xml:space="preserve">release.composed.normal[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7737,7 +7737,7 @@
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.normal.composed[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.composed.normal[2]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7752,7 +7752,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.normal.composed[2]</t>
+          <t xml:space="preserve">release.composed.normal[2]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7769,7 +7769,7 @@
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.composed.normal[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.normal.composed[1]</t>
+          <t xml:space="preserve">rentalGreeting.composed.normal[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7801,7 +7801,7 @@
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.composed.normal[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.normal.composed[1]</t>
+          <t xml:space="preserve">scoutGreeting.composed.normal[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7833,7 +7833,7 @@
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.composed.normal[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.normal.composed[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.composed.normal[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7865,7 +7865,7 @@
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.composed.normal[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.normal.composed[1]</t>
+          <t xml:space="preserve">titleDefense.composed.normal[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7897,7 +7897,7 @@
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.composed.normal[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7912,7 +7912,7 @@
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.normal.composed[1]</t>
+          <t xml:space="preserve">titleLoss.composed.normal[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7929,7 +7929,7 @@
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.composed.normal[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7944,7 +7944,7 @@
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.normal.composed[1]</t>
+          <t xml:space="preserve">titleWin.composed.normal[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7961,7 +7961,7 @@
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7993,7 +7993,7 @@
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.normal.composed[2]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.composed.normal[2]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -8008,7 +8008,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[2]</t>
+          <t xml:space="preserve">composed.normal[2]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -8025,7 +8025,7 @@
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -8057,7 +8057,7 @@
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -8089,7 +8089,7 @@
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -8121,7 +8121,7 @@
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8136,7 +8136,7 @@
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8153,7 +8153,7 @@
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8537,7 +8537,7 @@
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.normal.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.composed.normal[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-11.normal.composed[1]</t>
+          <t xml:space="preserve">GL-11.composed.normal[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8569,7 +8569,7 @@
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8601,7 +8601,7 @@
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.normal.composed[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.normal[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.normal.composed[1]</t>
+          <t xml:space="preserve">preFinal.composed.normal[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8633,7 +8633,7 @@
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.normal.composed[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.normal[2]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.normal.composed[2]</t>
+          <t xml:space="preserve">preFinal.composed.normal[2]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8665,7 +8665,7 @@
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.normal.composed[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.normal[3]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.normal.composed[3]</t>
+          <t xml:space="preserve">preFinal.composed.normal[3]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8697,7 +8697,7 @@
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.normal.composed[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.normal[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8712,7 +8712,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.composed[1]</t>
+          <t xml:space="preserve">preMatch.composed.normal[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8729,7 +8729,7 @@
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.normal.composed[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.normal[2]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8744,7 +8744,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.composed[2]</t>
+          <t xml:space="preserve">preMatch.composed.normal[2]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8761,7 +8761,7 @@
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.normal.composed[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.normal[3]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.composed[3]</t>
+          <t xml:space="preserve">preMatch.composed.normal[3]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8793,7 +8793,7 @@
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.normal.composed[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.normal[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8808,7 +8808,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.normal.composed[1]</t>
+          <t xml:space="preserve">survivor.composed.normal[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8825,7 +8825,7 @@
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.normal.composed[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.normal[2]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.normal.composed[2]</t>
+          <t xml:space="preserve">survivor.composed.normal[2]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8857,7 +8857,7 @@
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.normal.composed[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.normal[3]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8872,7 +8872,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.normal.composed[3]</t>
+          <t xml:space="preserve">survivor.composed.normal[3]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8889,7 +8889,7 @@
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.normal.composed[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.normal[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.composed[1]</t>
+          <t xml:space="preserve">champion.composed.normal[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8921,7 +8921,7 @@
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.normal.composed[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.normal[2]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8936,7 +8936,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.composed[2]</t>
+          <t xml:space="preserve">champion.composed.normal[2]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8953,7 +8953,7 @@
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.normal.composed[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.normal[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8968,7 +8968,7 @@
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.normal.composed[1]</t>
+          <t xml:space="preserve">defiant.composed.normal[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8985,7 +8985,7 @@
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.normal.composed[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.normal[2]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -9000,7 +9000,7 @@
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.normal.composed[2]</t>
+          <t xml:space="preserve">defiant.composed.normal[2]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -9017,7 +9017,7 @@
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.normal.composed[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.normal[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -9032,7 +9032,7 @@
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.normal.composed[1]</t>
+          <t xml:space="preserve">gauntlet.composed.normal[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -9049,7 +9049,7 @@
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.normal.composed[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.normal[2]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.normal.composed[2]</t>
+          <t xml:space="preserve">gauntlet.composed.normal[2]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -9081,7 +9081,7 @@
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.normal.composed[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.composed.normal[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -9096,7 +9096,7 @@
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.composed[1]</t>
+          <t xml:space="preserve">champion.composed.normal[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -9113,7 +9113,7 @@
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.normal.composed[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.composed.normal[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9128,7 +9128,7 @@
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.normal.composed[1]</t>
+          <t xml:space="preserve">postLose.composed.normal[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9145,7 +9145,7 @@
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.normal.composed[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.composed.normal[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9160,7 +9160,7 @@
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.normal.composed[1]</t>
+          <t xml:space="preserve">postMatchWin.composed.normal[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9177,7 +9177,7 @@
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.normal.composed[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.composed.normal[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9192,7 +9192,7 @@
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.normal.composed[1]</t>
+          <t xml:space="preserve">postWin.composed.normal[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9209,7 +9209,7 @@
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.normal.composed[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.composed.normal[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.normal.composed[1]</t>
+          <t xml:space="preserve">preFinal.composed.normal[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9241,7 +9241,7 @@
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.normal.composed[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.normal[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.composed[1]</t>
+          <t xml:space="preserve">preMatch.composed.normal[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9273,7 +9273,7 @@
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.normal.composed[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.normal[2]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.composed[2]</t>
+          <t xml:space="preserve">preMatch.composed.normal[2]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9305,7 +9305,7 @@
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.normal.composed[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.normal[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.normal.composed[1]</t>
+          <t xml:space="preserve">summon.composed.normal[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9337,7 +9337,7 @@
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.normal.composed[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.normal[2]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.normal.composed[2]</t>
+          <t xml:space="preserve">summon.composed.normal[2]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9369,7 +9369,7 @@
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9384,7 +9384,7 @@
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9401,7 +9401,7 @@
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.normal.composed[2]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.normal[2]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[2]</t>
+          <t xml:space="preserve">composed.normal[2]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9433,7 +9433,7 @@
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9465,7 +9465,7 @@
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.normal.composed[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.normal[2]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[2]</t>
+          <t xml:space="preserve">composed.normal[2]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9497,7 +9497,7 @@
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.normal.composed[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.normal[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9512,7 +9512,7 @@
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9529,7 +9529,7 @@
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.normal.composed[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.normal[2]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[2]</t>
+          <t xml:space="preserve">composed.normal[2]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9561,7 +9561,7 @@
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.normal.composed[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.normal[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9593,7 +9593,7 @@
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.normal.composed[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.normal[2]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[2]</t>
+          <t xml:space="preserve">composed.normal[2]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9625,7 +9625,7 @@
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.normal.composed[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.composed.normal[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9640,7 +9640,7 @@
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.normal.composed[1]</t>
+          <t xml:space="preserve">result_lose.composed.normal[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9657,7 +9657,7 @@
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.normal.composed[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.composed.normal[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9672,7 +9672,7 @@
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.normal.composed[1]</t>
+          <t xml:space="preserve">result_win.composed.normal[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9689,7 +9689,7 @@
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9704,7 +9704,7 @@
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9721,7 +9721,7 @@
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.normal.composed[2]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.composed.normal[2]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[2]</t>
+          <t xml:space="preserve">composed.normal[2]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9753,7 +9753,7 @@
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.normal.composed[1]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.composed.normal[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9768,7 +9768,7 @@
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.normal.composed[1]</t>
+          <t xml:space="preserve">fighter.composed.normal[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9785,7 +9785,7 @@
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9817,7 +9817,7 @@
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.normal.composed[1]</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9832,7 +9832,7 @@
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.composed[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">

--- a/セリフ編集/キャラタイプ別/鷹揚×ノーマル.xlsx
+++ b/セリフ編集/キャラタイプ別/鷹揚×ノーマル.xlsx
@@ -411,7 +411,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H294"/>
+  <dimension ref="A1:H296"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="F19" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしくね。のんびりだけど、頑張るよ</t>
+          <t xml:space="preserve">…よろしくね。それなりには、頑張るよ</t>
         </is>
       </c>
     </row>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="F43" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…認めない。…これで終わりだと思うなよ</t>
+          <t xml:space="preserve">…認めない。…これで終わりのつもりなら、間違いだ</t>
         </is>
       </c>
     </row>
@@ -5113,7 +5113,7 @@
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.composed.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.composed.normal[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.composed.normal[1]</t>
+          <t xml:space="preserve">autumnWarChampion.composed.normal[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
@@ -5138,14 +5138,14 @@
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くなかった。あの相手だから、出せたものがある</t>
+          <t xml:space="preserve">団体の看板を守れた。それが何よりだ。</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.composed.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.composed.normal[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.normal[1]</t>
+          <t xml:space="preserve">bestMatch.composed.normal[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
@@ -5170,14 +5170,14 @@
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…このベルトの重さ、悪くない。…来るなら来なよ</t>
+          <t xml:space="preserve">…悪くなかった。あの相手だから、出せたものがある</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.composed.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.composed.normal[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.composed.normal[1]</t>
+          <t xml:space="preserve">champion.composed.normal[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
@@ -5202,14 +5202,14 @@
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい時間だった。後悔？ …ないよ</t>
+          <t xml:space="preserve">…このベルトの重さ、悪くない。…来るなら来なよ</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.composed.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.composed.normal[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.composed.normal[1]</t>
+          <t xml:space="preserve">hallOfFame.composed.normal[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
@@ -5234,14 +5234,14 @@
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふぅん、こういう賞もあるんだね。…ありがとう</t>
+          <t xml:space="preserve">…いい時間だった。後悔？ …ないよ</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.composed.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.composed.normal[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.composed.normal[1]</t>
+          <t xml:space="preserve">mediaAward.composed.normal[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
@@ -5266,14 +5266,14 @@
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一年間、やるべきことをやった。それだけだよ</t>
+          <t xml:space="preserve">…ふぅん、こういう賞もあるんだね。…ありがとう</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.composed.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.composed.normal[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.composed.normal[1]</t>
+          <t xml:space="preserve">mvp.composed.normal[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
@@ -5298,14 +5298,14 @@
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、悪くないスタートかな。ここからだよ</t>
+          <t xml:space="preserve">…一年間、やるべきことをやった。それだけだよ</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.composed.normal[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5315,12 +5315,12 @@
       </c>
       <c r="C153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[1]</t>
+          <t xml:space="preserve">rookie.composed.normal[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
@@ -5330,14 +5330,14 @@
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドーム。…ついに辿り着きましたね</t>
+          <t xml:space="preserve">…ま、悪くないスタートかな。ここからだよ</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.normal[2]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.composed.normal[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="C154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[2]</t>
+          <t xml:space="preserve">springTagChampion.composed.normal[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
@@ -5362,14 +5362,14 @@
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">感慨深いものがあります。しかし、今は試合に集中します</t>
+          <t xml:space="preserve">相棒との信頼を、結果として示せてよかった。</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.normal[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[3]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
@@ -5394,14 +5394,14 @@
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この瞬間を、しっかり刻んでおきます</t>
+          <t xml:space="preserve">ドーム。…ついに辿り着きましたね</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.normal[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.normal[2]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[1]</t>
+          <t xml:space="preserve">composed.normal[2]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
@@ -5426,14 +5426,14 @@
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員。…団体として、一つの到達点ですね</t>
+          <t xml:space="preserve">感慨深いものがあります。しかし、今は試合に集中します</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.normal[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.normal[3]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[2]</t>
+          <t xml:space="preserve">composed.normal[3]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
@@ -5458,14 +5458,14 @@
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お客様の拍手、今も胸に響いています</t>
+          <t xml:space="preserve">この瞬間を、しっかり刻んでおきます</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.normal[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[3]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
@@ -5490,14 +5490,14 @@
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この記録、大切にしていきましょう</t>
+          <t xml:space="preserve">満員。…団体として、一つの到達点ですね</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.composed.normal[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.normal[2]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5507,29 +5507,29 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.composed.normal[1]</t>
+          <t xml:space="preserve">composed.normal[2]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、少しずつ馴染んできたかな</t>
+          <t xml:space="preserve">お客様の拍手、今も胸に響いています</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.composed.normal[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.normal[3]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5539,29 +5539,29 @@
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.composed.normal[2]</t>
+          <t xml:space="preserve">composed.normal[3]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悪くない感触だね。この調子で行こう</t>
+          <t xml:space="preserve">この記録、大切にしていきましょう</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.composed.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.composed.normal[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.composed.normal[1]</t>
+          <t xml:space="preserve">N1.composed.normal[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
@@ -5586,14 +5586,14 @@
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい仲間だね。悪くない環境だよ</t>
+          <t xml:space="preserve">…ま、少しずつ馴染んできたかな</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.composed.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.composed.normal[2]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.composed.normal[1]</t>
+          <t xml:space="preserve">N1.composed.normal[2]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
@@ -5618,14 +5618,14 @@
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ちょっと疲れただけ。すぐ戻るよ</t>
+          <t xml:space="preserve">悪くない感触だね。この調子で行こう</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.composed.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.composed.normal[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.composed.normal[1]</t>
+          <t xml:space="preserve">N2.composed.normal[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
@@ -5650,14 +5650,14 @@
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがたいね。ちゃんと届いてるよ</t>
+          <t xml:space="preserve">…いい仲間だね。悪くない環境だよ</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.composed.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.composed.normal[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.composed.normal[1]</t>
+          <t xml:space="preserve">N3.composed.normal[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
@@ -5682,14 +5682,14 @@
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もういいよ。分かったから</t>
+          <t xml:space="preserve">…ちょっと疲れただけ。すぐ戻るよ</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.composed.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.composed.normal[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.composed.normal[1]</t>
+          <t xml:space="preserve">N4.composed.normal[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
@@ -5714,14 +5714,14 @@
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ん、ちょっと考え事。気にしないで</t>
+          <t xml:space="preserve">…ありがたいね。ちゃんと届いてるよ</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.composed.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.composed.normal[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5731,12 +5731,12 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">breakthrough.voice.composed.normal[1]</t>
+          <t xml:space="preserve">N5_low.composed.normal[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
@@ -5746,14 +5746,14 @@
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くない環境だね。…感謝してる</t>
+          <t xml:space="preserve">…もういいよ。分かったから</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.composed.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.composed.normal[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.composed.normal[1]</t>
+          <t xml:space="preserve">N5_warning.composed.normal[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
@@ -5778,14 +5778,14 @@
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、こんなものか</t>
+          <t xml:space="preserve">…ん、ちょっと考え事。気にしないで</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.composed.normal[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice.composed.normal[1]</t>
+          <t xml:space="preserve">breakthrough.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
@@ -5810,14 +5810,14 @@
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…伸びたね。…まあ、焦ることはない</t>
+          <t xml:space="preserve">…悪くない環境だね。…感謝してる</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.composed.normal[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.composed.normal[1]</t>
+          <t xml:space="preserve">G1.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
@@ -5842,14 +5842,14 @@
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、待つさ</t>
+          <t xml:space="preserve">…まあ、こんなものか</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.composed.normal[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G4.voice.composed.normal[1]</t>
+          <t xml:space="preserve">G2.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5874,14 +5874,14 @@
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、待つよ</t>
+          <t xml:space="preserve">…伸びたね。…まあ、焦ることはない</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.composed.normal[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice.composed.normal[1]</t>
+          <t xml:space="preserve">G3.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5906,14 +5906,14 @@
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…別に。一人でも困らない</t>
+          <t xml:space="preserve">…まあ、待つさ</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.composed.normal[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal.composed.normal[1]</t>
+          <t xml:space="preserve">G4.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -5938,14 +5938,14 @@
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうか。…{name2}がいなくなるのか</t>
+          <t xml:space="preserve">…まあ、待つよ</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.composed.normal[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice.composed.normal[1]</t>
+          <t xml:space="preserve">R2.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -5970,14 +5970,14 @@
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くない。…やっと追いついた</t>
+          <t xml:space="preserve">…別に。一人でも困らない</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.composed.normal[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.composed.normal[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice.composed.normal[1]</t>
+          <t xml:space="preserve">R3.modal.composed.normal[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -6002,14 +6002,14 @@
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…足りなかった。…次、だね</t>
+          <t xml:space="preserve">…そうか。…{name2}がいなくなるのか</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.composed.normal[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -6019,29 +6019,29 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_insult.composed.normal[1]</t>
+          <t xml:space="preserve">R4.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…これで済ませるつもりかい。そうか</t>
+          <t xml:space="preserve">…悪くない。…やっと追いついた</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.composed.normal[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -6051,29 +6051,29 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.composed.normal[1]</t>
+          <t xml:space="preserve">R5.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう。大事に使うよ</t>
+          <t xml:space="preserve">…足りなかった。…次、だね</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.composed.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.composed.normal[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.composed.normal[1]</t>
+          <t xml:space="preserve">bonus_insult.composed.normal[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -6098,14 +6098,14 @@
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…合宿か。じっくりやろう</t>
+          <t xml:space="preserve">…これで済ませるつもりかい。そうか</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.composed.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.composed.normal[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.composed.normal[1]</t>
+          <t xml:space="preserve">bonus.composed.normal[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -6130,14 +6130,14 @@
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…見てくれてたんだ。…悪くないね</t>
+          <t xml:space="preserve">…ありがとう。大事に使うよ</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.composed.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.composed.normal[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.composed.normal[1]</t>
+          <t xml:space="preserve">camp.composed.normal[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6162,14 +6162,14 @@
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう。もう少しやってみるよ</t>
+          <t xml:space="preserve">…合宿か。じっくりやろう</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.composed.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.composed.normal[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6184,7 +6184,7 @@
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.composed.normal[1]</t>
+          <t xml:space="preserve">encourage_high_trust.composed.normal[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6194,14 +6194,14 @@
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なるほど。やってみるよ</t>
+          <t xml:space="preserve">…見てくれてたんだ。…悪くないね</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.composed.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.composed.normal[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.composed.normal[1]</t>
+          <t xml:space="preserve">encourage.composed.normal[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6226,14 +6226,14 @@
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい時間だったね。悪くないよ</t>
+          <t xml:space="preserve">…ありがとう。もう少しやってみるよ</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.composed.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.composed.normal[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.composed.normal[1]</t>
+          <t xml:space="preserve">media.composed.normal[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6258,14 +6258,14 @@
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう。少し休んでくるよ</t>
+          <t xml:space="preserve">…なるほど。やってみるよ</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.composed.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.composed.normal[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.composed.normal[1]</t>
+          <t xml:space="preserve">party.composed.normal[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6290,14 +6290,14 @@
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう。リング、待たせちゃ悪いね</t>
+          <t xml:space="preserve">…いい時間だったね。悪くないよ</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.composed.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.composed.normal[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.composed.normal[1]</t>
+          <t xml:space="preserve">refresh_leave.composed.normal[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6322,14 +6322,14 @@
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…了解。しっかり吸収するよ</t>
+          <t xml:space="preserve">…ありがとう。少し休んでくるよ</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.composed.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.composed.normal[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.composed.normal[1]</t>
+          <t xml:space="preserve">special_treatment.composed.normal[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6354,14 +6354,14 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…メディアか。いい機会だね</t>
+          <t xml:space="preserve">…ありがとう。リング、待たせちゃ悪いね</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E4.composed.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.composed.normal[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E4.composed.normal[1]</t>
+          <t xml:space="preserve">trainer.composed.normal[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6386,14 +6386,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…スカウトから、新しい話が来てるみたいだよ</t>
+          <t xml:space="preserve">…了解。しっかり吸収するよ</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.composed.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.composed.normal[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6408,7 +6408,7 @@
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.composed.normal[1]</t>
+          <t xml:space="preserve">E1.composed.normal[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6418,14 +6418,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…他所から話が来てるんだ。一応報告しておくね</t>
+          <t xml:space="preserve">…メディアか。いい機会だね</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E4.composed.normal[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.composed.normal[1]</t>
+          <t xml:space="preserve">E4.composed.normal[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6450,14 +6450,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…今日はいいかな。少し考えたいことがあって</t>
+          <t xml:space="preserve">…スカウトから、新しい話が来てるみたいだよ</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.composed.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.composed.normal[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.composed.normal[1]</t>
+          <t xml:space="preserve">E6.composed.normal[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6482,14 +6482,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（いつもの穏やかさが消え、「…ま、そういうことだよね」と静かに呟いている）</t>
+          <t xml:space="preserve">…他所から話が来てるんだ。一応報告しておくね</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.composed.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.normal[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.composed.normal[1]</t>
+          <t xml:space="preserve">S_boycott.composed.normal[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6514,14 +6514,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに夕焼けの写真と「…少し考える時間が欲しいかな」と投稿。ファンがざわついている）</t>
+          <t xml:space="preserve">…今日はいいかな。少し考えたいことがあって</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.composed.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.composed.normal[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.composed.normal[1]</t>
+          <t xml:space="preserve">S_grumble.composed.normal[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6546,14 +6546,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そろそろベルトに挑戦させてもらえないかな</t>
+          <t xml:space="preserve">（いつもの穏やかさが消え、「…ま、そういうことだよね」と静かに呟いている）</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.composed.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.composed.normal[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.composed.normal[1]</t>
+          <t xml:space="preserve">S_sns.composed.normal[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6578,14 +6578,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの人との試合、そろそろ組んでもらえないかな</t>
+          <t xml:space="preserve">（SNSに夕焼けの写真と「…少し考える時間が欲しいかな」と投稿。ファンがざわついている）</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.composed.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.composed.normal[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6600,7 +6600,7 @@
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.composed.normal[1]</t>
+          <t xml:space="preserve">S1.composed.normal[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6610,14 +6610,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…少し休ませてもらえるかな</t>
+          <t xml:space="preserve">…そろそろベルトに挑戦させてもらえないかな</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.composed.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.composed.normal[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6632,7 +6632,7 @@
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.composed.normal[1]</t>
+          <t xml:space="preserve">S2.composed.normal[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6642,14 +6642,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…このままだと困るんだよね。少し考えてもらえるかな</t>
+          <t xml:space="preserve">…あの人との試合、そろそろ組んでもらえないかな</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.composed.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.composed.normal[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.composed.normal[1]</t>
+          <t xml:space="preserve">S3.composed.normal[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6674,14 +6674,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…（少し間を置いて）…いや、なんでもないよ</t>
+          <t xml:space="preserve">…少し休ませてもらえるかな</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.composed.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.composed.normal[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.composed.normal[1]</t>
+          <t xml:space="preserve">S4_direct.composed.normal[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6706,14 +6706,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…少し追い込みたいんだ。特訓させてもらえるかな</t>
+          <t xml:space="preserve">…このままだと困るんだよね。少し考えてもらえるかな</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.composed.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.composed.normal[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.composed.normal[1]</t>
+          <t xml:space="preserve">S4_silent.composed.normal[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6738,14 +6738,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…後輩の面倒、見させてもらえないかな</t>
+          <t xml:space="preserve">…（少し間を置いて）…いや、なんでもないよ</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.composed.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.composed.normal[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6755,12 +6755,12 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.composed.normal[1]</t>
+          <t xml:space="preserve">S5.composed.normal[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6770,14 +6770,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やっちゃったね。まあ、焦らず治すよ</t>
+          <t xml:space="preserve">…少し追い込みたいんだ。特訓させてもらえるかな</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.composed.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.composed.normal[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6787,12 +6787,12 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.composed.normal[1]</t>
+          <t xml:space="preserve">S6.composed.normal[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6802,14 +6802,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、合わない人もいるよね。少し距離を置きたいな</t>
+          <t xml:space="preserve">…後輩の面倒、見させてもらえないかな</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.composed.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.composed.normal[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6824,7 +6824,7 @@
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.composed.normal[1]</t>
+          <t xml:space="preserve">B1.composed.normal[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6834,14 +6834,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふぅん。まあ、お互い様だと思うけどね</t>
+          <t xml:space="preserve">…やっちゃったね。まあ、焦らず治すよ</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.composed.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.composed.normal[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.composed.normal[1]</t>
+          <t xml:space="preserve">B2_fighter1.composed.normal[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6866,14 +6866,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…コラボか。なるほどね、面白そう</t>
+          <t xml:space="preserve">…まあ、合わない人もいるよね。少し距離を置きたいな</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.composed.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.composed.normal[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.composed.normal[1]</t>
+          <t xml:space="preserve">B2_fighter2.composed.normal[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6898,14 +6898,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…CMか。まあ、悪くないね</t>
+          <t xml:space="preserve">…ふぅん。まあ、お互い様だと思うけどね</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.composed.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.composed.normal[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.composed.normal[1]</t>
+          <t xml:space="preserve">B4_brand.composed.normal[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6930,14 +6930,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…直接話せるんだ。…それは、楽しみだね</t>
+          <t xml:space="preserve">…コラボか。なるほどね、面白そう</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.composed.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.composed.normal[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.composed.normal[1]</t>
+          <t xml:space="preserve">B4_cm.composed.normal[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6962,14 +6962,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ランウェイか。歩けるかな。…まあ、やってみるよ</t>
+          <t xml:space="preserve">…CMか。まあ、悪くないね</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.composed.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.composed.normal[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6984,7 +6984,7 @@
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.composed.normal[1]</t>
+          <t xml:space="preserve">B4_fan.composed.normal[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6994,14 +6994,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…グラビアか。まあ、たまにはいいんじゃない</t>
+          <t xml:space="preserve">…直接話せるんだ。…それは、楽しみだね</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.composed.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.composed.normal[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.composed.normal[1]</t>
+          <t xml:space="preserve">B4_fashion.composed.normal[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -7026,14 +7026,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…バラエティか。まあ、のんびり喋るよ</t>
+          <t xml:space="preserve">…ランウェイか。歩けるかな。…まあ、やってみるよ</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.composed.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.composed.normal[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -7048,7 +7048,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.composed.normal[1]</t>
+          <t xml:space="preserve">B4_gravure.composed.normal[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -7058,14 +7058,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…取材か。まあ、いつも通りやるよ</t>
+          <t xml:space="preserve">…グラビアか。まあ、たまにはいいんじゃない</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.composed.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.composed.normal[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -7075,29 +7075,29 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[1]</t>
+          <t xml:space="preserve">B4_variety.composed.normal[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…選んでくれるなら、応えるよ</t>
+          <t xml:space="preserve">…バラエティか。まあ、のんびり喋るよ</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.composed.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.composed.normal[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -7107,29 +7107,29 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[1]</t>
+          <t xml:space="preserve">B4.composed.normal[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。精一杯やるよ</t>
+          <t xml:space="preserve">…取材か。まあ、いつも通りやるよ</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.composed.normal[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[2]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7154,14 +7154,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…選んでくれてありがとう</t>
+          <t xml:space="preserve">…選んでくれるなら、応えるよ</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
@@ -7186,14 +7186,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。力になるよ</t>
+          <t xml:space="preserve">…よろしく。精一杯やるよ</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.composed.normal[2]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7203,12 +7203,12 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[1]</t>
+          <t xml:space="preserve">composed.normal[2]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7218,14 +7218,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。精一杯やるよ</t>
+          <t xml:space="preserve">…選んでくれてありがとう</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7235,7 +7235,7 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
@@ -7250,14 +7250,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…少し休むよ。すぐ戻る</t>
+          <t xml:space="preserve">…よろしく。力になるよ</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.composed.normal[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[2]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7282,14 +7282,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…大したことじゃないから、安心して</t>
+          <t xml:space="preserve">…よろしく。精一杯やるよ</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7299,12 +7299,12 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.composed.normal[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7314,14 +7314,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…決着はついてる。…なのに、まだ喉に引っかかってる</t>
+          <t xml:space="preserve">…少し休むよ。すぐ戻る</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.composed.normal[2]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7331,12 +7331,12 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.composed.normal[1]</t>
+          <t xml:space="preserve">composed.normal[2]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7346,14 +7346,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…片がついたらしいよ。…誰の中で、って話だけど</t>
+          <t xml:space="preserve">…大したことじゃないから、安心して</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.composed.normal[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.composed.normal[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.composed.normal[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7378,14 +7378,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…選んでくれるなら、応えるよ</t>
+          <t xml:space="preserve">…決着はついてる。…なのに、まだ喉に引っかかってる</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.composed.normal[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.composed.normal[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.composed.normal[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7410,14 +7410,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。精一杯やるよ</t>
+          <t xml:space="preserve">…片がついたらしいよ。…誰の中で、って話だけど</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.composed.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.composed.normal[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.composed.normal[2]</t>
+          <t xml:space="preserve">draftInterest.composed.normal[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7442,14 +7442,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…選んでくれてありがとう</t>
+          <t xml:space="preserve">…選んでくれるなら、応えるよ</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.composed.normal[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.composed.normal[1]</t>
+          <t xml:space="preserve">draftJoin.composed.normal[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7474,14 +7474,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…また名前を呼ばれる場所ができた。悪くないよ</t>
+          <t xml:space="preserve">…よろしく。精一杯やるよ</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.composed.normal[2]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.composed.normal[1]</t>
+          <t xml:space="preserve">draftJoin.composed.normal[2]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7506,14 +7506,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。力になるよ</t>
+          <t xml:space="preserve">…選んでくれてありがとう</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.composed.normal[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.composed.normal[1]</t>
+          <t xml:space="preserve">faGreeting.composed.normal[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7538,14 +7538,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。精一杯やるよ</t>
+          <t xml:space="preserve">…また名前を呼ばれる場所ができた。悪くないよ</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.composed.normal[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.composed.normal[1]</t>
+          <t xml:space="preserve">faSigning.composed.normal[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7570,14 +7570,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…体は軽いね。こういう日は、伸びるんだよ</t>
+          <t xml:space="preserve">…よろしく。力になるよ</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.composed.normal[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.composed.normal[1]</t>
+          <t xml:space="preserve">faWelcome.composed.normal[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7602,14 +7602,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…体が重いね。今日やっても、たぶん流れるだけ</t>
+          <t xml:space="preserve">…よろしく。精一杯やるよ</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.composed.normal[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7624,7 +7624,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.composed.normal[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.composed.normal[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7634,14 +7634,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くはないよ。…ただ、切れが一つ落ちたかな</t>
+          <t xml:space="preserve">…体は軽いね。こういう日は、伸びるんだよ</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.composed.normal[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7656,7 +7656,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.composed.normal[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.composed.normal[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7666,14 +7666,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…少し休むよ。すぐ戻る</t>
+          <t xml:space="preserve">…体が重いね。今日やっても、たぶん流れるだけ</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.composed.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.composed.normal[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7688,7 +7688,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.composed.normal[2]</t>
+          <t xml:space="preserve">heatSelf.warm.composed.normal[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7698,14 +7698,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…大したことじゃないから、安心して</t>
+          <t xml:space="preserve">…悪くはないよ。…ただ、切れが一つ落ちたかな</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.composed.normal[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7720,7 +7720,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.composed.normal[1]</t>
+          <t xml:space="preserve">injury.composed.normal[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7730,14 +7730,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうか。お世話になったね</t>
+          <t xml:space="preserve">…少し休むよ。すぐ戻る</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.composed.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.composed.normal[2]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7752,7 +7752,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.composed.normal[2]</t>
+          <t xml:space="preserve">injury.composed.normal[2]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7762,14 +7762,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…短い間だったけど、ありがとう</t>
+          <t xml:space="preserve">…大したことじゃないから、安心して</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.composed.normal[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.composed.normal[1]</t>
+          <t xml:space="preserve">release.composed.normal[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7794,14 +7794,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…短い間だけど、手は抜かないよ</t>
+          <t xml:space="preserve">…そうか。お世話になったね</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.composed.normal[2]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.composed.normal[1]</t>
+          <t xml:space="preserve">release.composed.normal[2]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7826,14 +7826,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…見込まれたなら、応えるだけだよ</t>
+          <t xml:space="preserve">…短い間だったけど、ありがとう</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.composed.normal[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.composed.normal[1]</t>
+          <t xml:space="preserve">rentalGreeting.composed.normal[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7858,14 +7858,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…届かなかったか。…次だね</t>
+          <t xml:space="preserve">…短い間だけど、手は抜かないよ</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.composed.normal[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.composed.normal[1]</t>
+          <t xml:space="preserve">scoutGreeting.composed.normal[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7890,14 +7890,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…防衛か。…まだ渡すつもりはないよ</t>
+          <t xml:space="preserve">…見込まれたなら、応えるだけだよ</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.composed.normal[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7912,7 +7912,7 @@
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.composed.normal[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.composed.normal[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7922,14 +7922,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…失ったか。…でも終わりじゃない</t>
+          <t xml:space="preserve">…届かなかったか。…次だね</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.composed.normal[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7944,7 +7944,7 @@
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.composed.normal[1]</t>
+          <t xml:space="preserve">titleDefense.composed.normal[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7954,14 +7954,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…チャンピオンか。…悪くないね</t>
+          <t xml:space="preserve">…防衛か。…まだ渡すつもりはないよ</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.composed.normal[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[1]</t>
+          <t xml:space="preserve">titleLoss.composed.normal[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7986,14 +7986,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうか。お世話になったね</t>
+          <t xml:space="preserve">…失ったか。…でも終わりじゃない</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.composed.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.composed.normal[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -8003,12 +8003,12 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[2]</t>
+          <t xml:space="preserve">titleWin.composed.normal[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -8018,14 +8018,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…短い間だったけど、ありがとう</t>
+          <t xml:space="preserve">…チャンピオンか。…悪くないね</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -8035,7 +8035,7 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
@@ -8050,14 +8050,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…短い間だけど、手は抜かないよ</t>
+          <t xml:space="preserve">…そうか。お世話になったね</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.composed.normal[2]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[1]</t>
+          <t xml:space="preserve">composed.normal[2]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -8082,14 +8082,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…届かなかったか。…次だね</t>
+          <t xml:space="preserve">…短い間だったけど、ありがとう</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -8099,7 +8099,7 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
@@ -8114,14 +8114,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…防衛か。…まだ渡すつもりはないよ</t>
+          <t xml:space="preserve">…短い間だけど、手は抜かないよ</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8131,7 +8131,7 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
@@ -8146,14 +8146,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…失ったか。…でも終わりじゃない</t>
+          <t xml:space="preserve">…届かなかったか。…次だね</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
@@ -8178,14 +8178,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…チャンピオンか。…悪くないね</t>
+          <t xml:space="preserve">…防衛か。…まだ渡すつもりはないよ</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8195,29 +8195,29 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.normal.composed[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…合わないね。…仕方ない</t>
+          <t xml:space="preserve">…失ったか。…でも終わりじゃない</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8227,29 +8227,29 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.normal.composed[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…少し距離が開いたかな</t>
+          <t xml:space="preserve">…チャンピオンか。…悪くないね</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.normal.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.normal.composed[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8264,7 +8264,7 @@
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.normal.composed[1]</t>
+          <t xml:space="preserve">bond_39_down.normal.composed[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8274,14 +8274,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くない距離感だね。一緒にいて楽だ</t>
+          <t xml:space="preserve">…合わないね。…仕方ない</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.normal.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.normal.composed[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.normal.composed[1]</t>
+          <t xml:space="preserve">bond_59_down.normal.composed[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8306,14 +8306,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…大事な存在。…それだけで十分</t>
+          <t xml:space="preserve">…少し距離が開いたかな</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.normal.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.normal.composed[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.normal.composed[1]</t>
+          <t xml:space="preserve">bond_60_up.normal.composed[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8338,14 +8338,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう終わったことだね</t>
+          <t xml:space="preserve">…悪くない距離感だね。一緒にいて楽だ</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.normal.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.normal.composed[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.normal.composed[1]</t>
+          <t xml:space="preserve">bond_80_up.normal.composed[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8370,14 +8370,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…気になるね。…負けたくない</t>
+          <t xml:space="preserve">…大事な存在。…それだけで十分</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.normal.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.normal.composed[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.normal.composed[1]</t>
+          <t xml:space="preserve">rivalry_29_down.normal.composed[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8402,14 +8402,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…負けるわけにはいかない。…絶対に</t>
+          <t xml:space="preserve">…もう終わったことだね</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.normal.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.normal.composed[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8424,7 +8424,7 @@
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.normal.composed[1]</t>
+          <t xml:space="preserve">rivalry_30_up.normal.composed[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8434,14 +8434,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…運命みたいなものだね。…この人とは</t>
+          <t xml:space="preserve">…気になるね。…負けたくない</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.normal.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.normal.composed[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8456,7 +8456,7 @@
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.normal.composed[1]</t>
+          <t xml:space="preserve">rivalry_50_up.normal.composed[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8466,14 +8466,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここが自分の居場所だね。…悪くない</t>
+          <t xml:space="preserve">…負けるわけにはいかない。…絶対に</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.normal.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.normal.composed[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.normal.composed[1]</t>
+          <t xml:space="preserve">rivalry_70_up.normal.composed[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8498,14 +8498,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここにいる理由が、見つからなくなった</t>
+          <t xml:space="preserve">…運命みたいなものだね。…この人とは</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.normal.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.normal.composed[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.normal.composed[1]</t>
+          <t xml:space="preserve">trust_above_75.normal.composed[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8530,14 +8530,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここで本当にやれるのかな</t>
+          <t xml:space="preserve">…ここが自分の居場所だね。…悪くない</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.composed.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.normal.composed[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-11.composed.normal[1]</t>
+          <t xml:space="preserve">trust_below_20.normal.composed[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8562,14 +8562,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの子は、わたくしの中にはいないの。それだけのことよ</t>
+          <t xml:space="preserve">…ここにいる理由が、見つからなくなった</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.composed.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.normal.composed[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8579,12 +8579,12 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[1]</t>
+          <t xml:space="preserve">trust_below_35.normal.composed[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8594,14 +8594,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…好調は終わったか。…でも悪くない経験だった</t>
+          <t xml:space="preserve">…ここで本当にやれるのかな</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.composed.normal[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8611,29 +8611,29 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.normal[1]</t>
+          <t xml:space="preserve">GL-11.composed.normal[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…満身創痍だね。でも、ここで降りる理由はないよ</t>
+          <t xml:space="preserve">あの子は、もう心の中にはいない。ただ、それだけのことだ</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8643,29 +8643,29 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.normal[2]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…身体は限界に近い。それでも、最後の一戦だけは立って迎えるよ</t>
+          <t xml:space="preserve">…好調は終わったか。…でも悪くない経験だった</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.normal[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.normal[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.normal[3]</t>
+          <t xml:space="preserve">preFinal.composed.normal[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8690,14 +8690,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…傷は数えきれない。まあ、最後まで残った証だと思えばいいよ</t>
+          <t xml:space="preserve">…満身創痍だね。でも、ここで降りる理由はないよ</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.normal[2]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8712,7 +8712,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.normal[1]</t>
+          <t xml:space="preserve">preFinal.composed.normal[2]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8722,14 +8722,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…相手は選べない。来た順に、真っ向から受けるだけだよ</t>
+          <t xml:space="preserve">…身体は限界に近い。それでも、最後の一戦だけは立って迎えるよ</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.normal[3]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8744,7 +8744,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.normal[2]</t>
+          <t xml:space="preserve">preFinal.composed.normal[3]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8754,14 +8754,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…焦らない。目の前の一人に集中する。それでリングは渡さない</t>
+          <t xml:space="preserve">…傷は数えきれない。まあ、最後まで残った証だと思えばいいよ</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.normal[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.normal[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.normal[3]</t>
+          <t xml:space="preserve">preMatch.composed.normal[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8786,14 +8786,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この一戦から、始まる。落ち着いていこうか</t>
+          <t xml:space="preserve">…相手は選べない。来た順に、真っ向から受けるだけだよ</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.normal[2]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8808,7 +8808,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.composed.normal[1]</t>
+          <t xml:space="preserve">preMatch.composed.normal[2]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8818,14 +8818,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一人片づけた。息は上がってるけど、退く理由はないよ。次、来なよ</t>
+          <t xml:space="preserve">…焦らない。目の前の一人に集中する。それでリングは渡さない</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.normal[3]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.composed.normal[2]</t>
+          <t xml:space="preserve">preMatch.composed.normal[3]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8850,14 +8850,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ足は動く。このリングは渡さない。次は誰だ</t>
+          <t xml:space="preserve">…この一戦から、始まる。落ち着いていこうか</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.normal[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.normal[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8872,7 +8872,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.composed.normal[3]</t>
+          <t xml:space="preserve">survivor.composed.normal[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8882,14 +8882,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふぅ。まだ立ってる。この場所、そう簡単には空けないよ。次</t>
+          <t xml:space="preserve">…一人片づけた。息は上がってるけど、退く理由はないよ。次、来なよ</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.normal[2]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.normal[1]</t>
+          <t xml:space="preserve">survivor.composed.normal[2]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8914,14 +8914,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で繋いだ結果だ。誰が欠けても……この景色はなかった</t>
+          <t xml:space="preserve">…まだ足は動く。このリングは渡さない。次は誰だ</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.normal[3]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8931,12 +8931,12 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.normal[2]</t>
+          <t xml:space="preserve">survivor.composed.normal[3]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8946,14 +8946,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人の手柄にするつもりはない。これは、三人の勝利だ</t>
+          <t xml:space="preserve">…ふぅ。まだ立ってる。この場所、そう簡単には空けないよ。次</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.normal[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8968,7 +8968,7 @@
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.composed.normal[1]</t>
+          <t xml:space="preserve">champion.composed.normal[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8978,14 +8978,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">個人の栄誉は受け取る。だが……これで満足する理由にはならない</t>
+          <t xml:space="preserve">三人で繋いだ結果だ。誰が欠けても……この景色はなかった</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.normal[2]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -9000,7 +9000,7 @@
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.composed.normal[2]</t>
+          <t xml:space="preserve">champion.composed.normal[2]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -9010,14 +9010,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次がある。その時は、チーム全員で最後に立つ</t>
+          <t xml:space="preserve">一人の手柄にするつもりはない。これは、三人の勝利だ</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.normal[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -9032,7 +9032,7 @@
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.composed.normal[1]</t>
+          <t xml:space="preserve">defiant.composed.normal[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -9042,14 +9042,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体は限界を告げている。それでも……最後の一人を見届けるまで、退けなかった</t>
+          <t xml:space="preserve">個人の栄誉は受け取る。だが……これで満足する理由にはならない</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.normal[2]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.composed.normal[2]</t>
+          <t xml:space="preserve">defiant.composed.normal[2]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -9074,14 +9074,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何度か意識が揺れた。だが、リングを降りる理由にはならなかった</t>
+          <t xml:space="preserve">次がある。その時は、チーム全員で最後に立つ</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.composed.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.normal[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -9091,12 +9091,12 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.normal[1]</t>
+          <t xml:space="preserve">gauntlet.composed.normal[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -9106,14 +9106,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…優勝か。…悪くないね。…次も行こう</t>
+          <t xml:space="preserve">身体は限界を告げている。それでも……最後の一人を見届けるまで、退けなかった</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.composed.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.normal[2]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.composed.normal[1]</t>
+          <t xml:space="preserve">gauntlet.composed.normal[2]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9138,14 +9138,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ足りないか。…次までに詰めよう</t>
+          <t xml:space="preserve">何度か意識が揺れた。だが、リングを降りる理由にはならなかった</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.composed.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.composed.normal[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9160,7 +9160,7 @@
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.composed.normal[1]</t>
+          <t xml:space="preserve">champion.composed.normal[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9170,14 +9170,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一つ勝ち。…次もこの調子で</t>
+          <t xml:space="preserve">…優勝か。…悪くないね。…次も行こう</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.composed.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.composed.normal[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9192,7 +9192,7 @@
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.composed.normal[1]</t>
+          <t xml:space="preserve">postLose.composed.normal[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9202,14 +9202,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くなかったね。…いい経験になった</t>
+          <t xml:space="preserve">…まだ足りないか。…次までに詰めよう</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.composed.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.composed.normal[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.normal[1]</t>
+          <t xml:space="preserve">postMatchWin.composed.normal[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9234,14 +9234,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…決勝か。…全部出し切るよ</t>
+          <t xml:space="preserve">…一つ勝ち。…次もこの調子で</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.composed.normal[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.normal[1]</t>
+          <t xml:space="preserve">postWin.composed.normal[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9266,14 +9266,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いつも通りやるよ</t>
+          <t xml:space="preserve">…悪くなかったね。…いい経験になった</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.composed.normal[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.normal[2]</t>
+          <t xml:space="preserve">preFinal.composed.normal[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9298,14 +9298,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…集中。…行こうか</t>
+          <t xml:space="preserve">…決勝か。…全部出し切るよ</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.normal[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.composed.normal[1]</t>
+          <t xml:space="preserve">preMatch.composed.normal[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9330,14 +9330,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…出るよ。…やるだけだね</t>
+          <t xml:space="preserve">…いつも通りやるよ</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.normal[2]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.composed.normal[2]</t>
+          <t xml:space="preserve">preMatch.composed.normal[2]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9362,14 +9362,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なるほど。じゃあ、行こうか</t>
+          <t xml:space="preserve">…集中。…行こうか</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.normal[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[1]</t>
+          <t xml:space="preserve">summon.composed.normal[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9394,14 +9394,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい舞台だね。…全力で行くよ</t>
+          <t xml:space="preserve">…出るよ。…やるだけだね</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.normal[2]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[2]</t>
+          <t xml:space="preserve">summon.composed.normal[2]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9426,14 +9426,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…負けるつもりはないよ。よろしく</t>
+          <t xml:space="preserve">…なるほど。じゃあ、行こうか</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.normal[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9443,7 +9443,7 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="12">
@@ -9458,14 +9458,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やったよ。…ここまで来れたか</t>
+          <t xml:space="preserve">…いい舞台だね。…全力で行くよ</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.normal[2]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.normal[2]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="12">
@@ -9490,14 +9490,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くない結末だね。みんな、ありがとう</t>
+          <t xml:space="preserve">…負けるつもりはないよ。よろしく</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.normal[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9507,7 +9507,7 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="12">
@@ -9522,14 +9522,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そちらの実力、確かめさせてもらうよ</t>
+          <t xml:space="preserve">…やったよ。…ここまで来れたか</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.normal[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.normal[2]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9539,7 +9539,7 @@
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="12">
@@ -9554,14 +9554,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…本気で来なよ。受けて立つから</t>
+          <t xml:space="preserve">…悪くない結末だね。みんな、ありがとう</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.normal[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.normal[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9571,7 +9571,7 @@
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="12">
@@ -9586,14 +9586,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふぅん。逃げるんだ</t>
+          <t xml:space="preserve">…そちらの実力、確かめさせてもらうよ</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.normal[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.normal[2]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9603,7 +9603,7 @@
       </c>
       <c r="C287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D287" t="inlineStr" s="12">
@@ -9618,14 +9618,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、そういうこともあるか</t>
+          <t xml:space="preserve">…本気で来なよ。受けて立つから</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.composed.normal[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.normal[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.composed.normal[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9650,14 +9650,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…負けたか。…次は違う結果にする</t>
+          <t xml:space="preserve">…そうか。そんな時もあるね</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.composed.normal[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.normal[2]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9667,12 +9667,12 @@
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.composed.normal[1]</t>
+          <t xml:space="preserve">composed.normal[2]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9682,14 +9682,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝ったね。…いい対抗戦だった</t>
+          <t xml:space="preserve">…まあ、そういうこともあるか</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.composed.normal[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.composed.normal[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9699,12 +9699,12 @@
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[1]</t>
+          <t xml:space="preserve">result_lose.composed.normal[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9714,14 +9714,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…団体の看板、守れたかな。…悪くないね</t>
+          <t xml:space="preserve">…負けたか。…次は違う結果にする</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.composed.normal[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.composed.normal[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[2]</t>
+          <t xml:space="preserve">result_win.composed.normal[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9746,14 +9746,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝った。…うちの力を見せられたと思う</t>
+          <t xml:space="preserve">…勝ったね。…いい対抗戦だった</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.composed.normal[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9763,29 +9763,29 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.composed.normal[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここまで来れたか。…悪くない景色だね</t>
+          <t xml:space="preserve">…団体の看板、守れたかな。…悪くないね</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.composed.normal[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.composed.normal[2]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9795,59 +9795,123 @@
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[1]</t>
+          <t xml:space="preserve">composed.normal[2]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…また名前を呼ばれる場所ができた。悪くないよ</t>
+          <t xml:space="preserve">…勝った。…うちの力を見せられたと思う</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.composed.normal[1]</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.composed.normal[1]</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ここまで来れたか。…悪くない景色だね</t>
+        </is>
+      </c>
+    </row>
+    <row r="295" ht="40" customHeight="1">
+      <c r="A295" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.composed.normal[1]</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.normal[1]</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…また名前を呼ばれる場所ができた。悪くないよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="40" customHeight="1">
+      <c r="A296" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.composed.normal[1]</t>
         </is>
       </c>
-      <c r="B294" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr" s="2">
+      <c r="B296" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr" s="12">
+      <c r="D296" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
-      <c r="E294" t="inlineStr" s="2">
+      <c r="E296" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F294" t="inlineStr" s="3">
+      <c r="F296" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…見込まれたなら、応えるだけだよ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H294"/>
+  <autoFilter ref="A1:H296"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/鷹揚×ノーマル.xlsx
+++ b/セリフ編集/キャラタイプ別/鷹揚×ノーマル.xlsx
@@ -411,7 +411,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H296"/>
+  <dimension ref="A1:H303"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -4021,7 +4021,7 @@
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.composed.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_accept.composed.normal[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.composed.normal[1]</t>
+          <t xml:space="preserve">decline_accept.composed.normal[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -4046,14 +4046,14 @@
       </c>
       <c r="F113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふぅん…悪くないね。まあ、期待に応えるよ。</t>
+          <t xml:space="preserve">うん、妥当だ。…変に庇われるほうが、よっぽど居心地が悪いからね。</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.composed.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_hold.composed.normal[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.composed.normal[1]</t>
+          <t xml:space="preserve">decline_hold.composed.normal[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -4078,14 +4078,14 @@
       </c>
       <c r="F114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ…気持ちは受け取ったよ。悪くないね。</t>
+          <t xml:space="preserve">……社長、それは商売として下手だよ。…でも、ありがとう。無駄にはしないんだ。</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.composed.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_open.composed.normal[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.composed.normal[1]</t>
+          <t xml:space="preserve">decline_open.composed.normal[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -4110,14 +4110,14 @@
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう。まあ…そういうこともあるよね。</t>
+          <t xml:space="preserve">…ああ、その話か。{tenure}まあ、薄々そんな気はしてたんだ。…続けて、社長。</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.composed.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_strict.composed.normal[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.composed.normal[1]</t>
+          <t xml:space="preserve">decline_strict.composed.normal[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -4142,14 +4142,14 @@
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ…社長、少しいいかな。{tenure}{record}悪くない環境だと思ってるけど…もう少し、考えてもらえると嬉しいね。</t>
+          <t xml:space="preserve">……そこまでやるんだ。……分かった。うん、社長は社長の仕事をしただけだ。</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.composed.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_accept.composed.normal[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.composed.normal[1]</t>
+          <t xml:space="preserve">decline_voluntary_accept.composed.normal[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4174,14 +4174,14 @@
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう。まあ…残念だけど、仕方ないね。</t>
+          <t xml:space="preserve">うん、それでいい。……変に庇われないのが、一番の敬意だからね。……さ、来季の話をしよう。</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.composed.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_hold.composed.normal[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.composed.normal[1]</t>
+          <t xml:space="preserve">decline_voluntary_hold.composed.normal[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4206,14 +4206,14 @@
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。手短に言うね。…辞めます。もう決めたことだから。</t>
+          <t xml:space="preserve">……せっかく格好つけたのに。……まったく、社長は人が悪いね。……ありがたく、受け取るよ。</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.composed.normal[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_open.composed.normal[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.composed.normal[2]</t>
+          <t xml:space="preserve">decline_voluntary_open.composed.normal[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -4238,14 +4238,14 @@
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…世話になったよ。…でも、もうここでは続けられない。</t>
+          <t xml:space="preserve">社長、先に言わせて。……もう全盛期じゃないんだ。下げていい。若い子に回して。</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.composed.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.composed.normal[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.composed.normal[1]</t>
+          <t xml:space="preserve">raise_accept.composed.normal[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -4270,14 +4270,14 @@
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…聞いてくれるんだ。{record}…まあ、新しい場所で試してみたくてね。</t>
+          <t xml:space="preserve">ふぅん…悪くないね。まあ、期待に応えるよ。</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.composed.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.composed.normal[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.composed.normal[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.composed.normal[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
@@ -4302,14 +4302,14 @@
       </c>
       <c r="F121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長…少し話がある。{tenure}ここを離れようかと…まあ、そういうことです。</t>
+          <t xml:space="preserve">まあ…気持ちは受け取ったよ。悪くないね。</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.composed.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.composed.normal[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4324,7 +4324,7 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.composed.normal[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.composed.normal[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -4334,14 +4334,14 @@
       </c>
       <c r="F122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…分かった。{tenure_farewell}{rivalry}…ここでの時間は、悪くなかったよ。</t>
+          <t xml:space="preserve">…そう。まあ…そういうこともあるよね。</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.composed.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.composed.normal[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.composed.normal[1]</t>
+          <t xml:space="preserve">raise_open.composed.normal[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
@@ -4366,14 +4366,14 @@
       </c>
       <c r="F123" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがたいけど…もう決めたんだ。…悪いね。</t>
+          <t xml:space="preserve">まあ…社長、少しいいかな。{tenure}{record}悪くない環境だと思ってるけど…もう少し、考えてもらえると嬉しいね。</t>
         </is>
       </c>
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.composed.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.composed.normal[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.composed.normal[1]</t>
+          <t xml:space="preserve">raise_refuse.composed.normal[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
@@ -4398,370 +4398,370 @@
       </c>
       <c r="F124" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふぅん。そこまでしてくれるんだ。…まあ…もう少しだけ、いるよ。</t>
+          <t xml:space="preserve">…そう。まあ…残念だけど、仕方ないね。</t>
         </is>
       </c>
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.composed.normal[1]</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.composed.normal[1]</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長。手短に言うね。…辞めます。もう決めたことだから。</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="40" customHeight="1">
+      <c r="A126" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.composed.normal[2]</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.composed.normal[2]</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…世話になったよ。…でも、もうここでは続けられない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="40" customHeight="1">
+      <c r="A127" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.composed.normal[1]</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_listen.composed.normal[1]</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…聞いてくれるんだ。{record}…まあ、新しい場所で試してみたくてね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="40" customHeight="1">
+      <c r="A128" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.composed.normal[1]</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_open.composed.normal[1]</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長…少し話がある。{tenure}ここを離れようかと…まあ、そういうことです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="40" customHeight="1">
+      <c r="A129" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.composed.normal[1]</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_release.composed.normal[1]</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…分かった。{tenure_farewell}{rivalry}…ここでの時間は、悪くなかったよ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="40" customHeight="1">
+      <c r="A130" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.composed.normal[1]</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_fail.composed.normal[1]</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがたいけど…もう決めたんだ。…悪いね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="40" customHeight="1">
+      <c r="A131" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.composed.normal[1]</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_success.composed.normal[1]</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ふぅん。そこまでしてくれるんだ。…まあ…もう少しだけ、いるよ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="40" customHeight="1">
+      <c r="A132" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">NEGOTIATE_LINES.blocked.composed.normal[1]</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr" s="2">
+      <c r="B132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr" s="12">
+      <c r="D132" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">blocked.composed.normal[1]</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr" s="2">
+      <c r="E132" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr" s="3">
+      <c r="F132" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…悪いけど、今の仲間を置いていく気にはなれない。
 …ごめんね</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="40" customHeight="1">
-      <c r="A126" t="inlineStr" s="15">
+    <row r="133" ht="40" customHeight="1">
+      <c r="A133" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.fail.composed.normal[1]</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr" s="2">
+      <c r="B133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr" s="12">
+      <c r="D133" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fail.composed.normal[1]</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr" s="2">
+      <c r="E133" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr" s="3">
+      <c r="F133" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…悪いけど、パスで。
 縁があればまた</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="40" customHeight="1">
-      <c r="A127" t="inlineStr" s="15">
+    <row r="134" ht="40" customHeight="1">
+      <c r="A134" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.start.composed.normal[1]</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr" s="2">
+      <c r="B134" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr" s="12">
+      <c r="D134" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">start.composed.normal[1]</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr" s="2">
+      <c r="E134" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr" s="3">
+      <c r="F134" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…ふぅん、私に来いって？
 …聞くだけ聞こうか</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="40" customHeight="1">
-      <c r="A128" t="inlineStr" s="15">
+    <row r="135" ht="40" customHeight="1">
+      <c r="A135" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.success.composed.normal[1]</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr" s="2">
+      <c r="B135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr" s="12">
+      <c r="D135" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">success.composed.normal[1]</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr" s="2">
+      <c r="E135" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr" s="3">
+      <c r="F135" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…わかった、行くよ。
 …やるべきことをやるだけだ</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="40" customHeight="1">
-      <c r="A129" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.composed.normal[1]</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">composed.normal[1]</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…なるほど。壁を越えたみたいだね</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="40" customHeight="1">
-      <c r="A130" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">BT_HINT_LINES.composed.normal[1]</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">composed.normal[1]</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">（…ふぅん。…いつもと違う。悪くないね——）</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="40" customHeight="1">
-      <c r="A131" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.composed.normal[1]</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">fresh.composed.normal[1]</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…体は軽いね。こういう日は、伸びるんだよ</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="40" customHeight="1">
-      <c r="A132" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.composed.normal[1]</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">heavy.composed.normal[1]</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…体が重いね。今日やっても、たぶん流れるだけ</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="40" customHeight="1">
-      <c r="A133" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.composed.normal[1]</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">warm.composed.normal[1]</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…悪くはないよ。…ただ、切れが一つ落ちたかな</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="40" customHeight="1">
-      <c r="A134" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.composed.normal[1]</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">cap_reached.composed.normal[1]</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…ここが限界か。…まあ、上出来じゃない？</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="40" customHeight="1">
-      <c r="A135" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.composed.normal[1]</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">ovr_elite.composed.normal[1]</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…ここまで来たか。…悪くないね</t>
-        </is>
-      </c>
-    </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.composed.normal[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="C136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.composed.normal[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -4786,14 +4786,14 @@
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くないペースだね</t>
+          <t xml:space="preserve">…なるほど。壁を越えたみたいだね</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.composed.normal[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="C137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.composed.normal[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4818,14 +4818,14 @@
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここまで来ると、逆に静かな気持ちになるね</t>
+          <t xml:space="preserve">（…ふぅん。…いつもと違う。悪くないね——）</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.composed.normal[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.composed.normal[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4835,12 +4835,12 @@
       </c>
       <c r="C138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.composed.normal[1]</t>
+          <t xml:space="preserve">fresh.composed.normal[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
@@ -4850,14 +4850,14 @@
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…知ってもらえるのは、素直に嬉しいね</t>
+          <t xml:space="preserve">…体は軽いね。こういう日は、伸びるんだよ</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.composed.normal[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.composed.normal[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="C139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.composed.normal[1]</t>
+          <t xml:space="preserve">heavy.composed.normal[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
@@ -4882,14 +4882,14 @@
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…こんなに応援してくれる人がいるんだ。…頑張らないとね</t>
+          <t xml:space="preserve">…体が重いね。今日やっても、たぶん流れるだけ</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.composed.normal[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.composed.normal[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4899,12 +4899,12 @@
       </c>
       <c r="C140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[1]</t>
+          <t xml:space="preserve">warm.composed.normal[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
@@ -4914,14 +4914,14 @@
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…何のために闘ってるのか。…わからなくなった</t>
+          <t xml:space="preserve">…悪くはないよ。…ただ、切れが一つ落ちたかな</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.composed.normal[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.composed.normal[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4931,12 +4931,12 @@
       </c>
       <c r="C141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[1]</t>
+          <t xml:space="preserve">cap_reached.composed.normal[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
@@ -4946,14 +4946,14 @@
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだやれる。…うん、やってみよう</t>
+          <t xml:space="preserve">…ここが限界か。…まあ、上出来じゃない？</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.composed.normal[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.composed.normal[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="C142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[1]</t>
+          <t xml:space="preserve">ovr_elite.composed.normal[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
@@ -4978,14 +4978,14 @@
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やっと、戻ってこれたかな</t>
+          <t xml:space="preserve">…ここまで来たか。…悪くないね</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.composed.normal[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.composed.normal[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4995,12 +4995,12 @@
       </c>
       <c r="C143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.composed.normal[1]</t>
+          <t xml:space="preserve">ovr_growth.composed.normal[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
@@ -5010,14 +5010,14 @@
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの負けから、どこか噛み合わない</t>
+          <t xml:space="preserve">…悪くないペースだね</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.composed.normal[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.composed.normal[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -5027,12 +5027,12 @@
       </c>
       <c r="C144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.composed.normal[1]</t>
+          <t xml:space="preserve">ovr_legend.composed.normal[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
@@ -5042,14 +5042,14 @@
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…治ったはずなのに。…まあ、焦らないよ</t>
+          <t xml:space="preserve">…ここまで来ると、逆に静かな気持ちになるね</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.composed.normal[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.composed.normal[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -5059,12 +5059,12 @@
       </c>
       <c r="C145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.composed.normal[1]</t>
+          <t xml:space="preserve">pop_growth.composed.normal[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
@@ -5074,14 +5074,14 @@
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…戻ってきた。…のに、少し怖いかな</t>
+          <t xml:space="preserve">…知ってもらえるのは、素直に嬉しいね</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.composed.normal[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.composed.normal[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="C146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.composed.normal[1]</t>
+          <t xml:space="preserve">pop_star.composed.normal[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
@@ -5106,14 +5106,14 @@
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…怪我は治った。…でも気力が、まだ</t>
+          <t xml:space="preserve">…こんなに応援してくれる人がいるんだ。…頑張らないとね</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.composed.normal[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -5123,29 +5123,29 @@
       </c>
       <c r="C147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">autumnWarChampion.composed.normal[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体の看板を守れた。それが何よりだ。</t>
+          <t xml:space="preserve">…何のために闘ってるのか。…わからなくなった</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.composed.normal[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5155,29 +5155,29 @@
       </c>
       <c r="C148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.composed.normal[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くなかった。あの相手だから、出せたものがある</t>
+          <t xml:space="preserve">…まだやれる。…うん、やってみよう</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.composed.normal[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5187,29 +5187,29 @@
       </c>
       <c r="C149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.normal[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…このベルトの重さ、悪くない。…来るなら来なよ</t>
+          <t xml:space="preserve">…やっと、戻ってこれたかな</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.composed.normal[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.composed.normal[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5219,29 +5219,29 @@
       </c>
       <c r="C150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.composed.normal[1]</t>
+          <t xml:space="preserve">defeat.composed.normal[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい時間だった。後悔？ …ないよ</t>
+          <t xml:space="preserve">…あの負けから、どこか噛み合わない</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.composed.normal[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.composed.normal[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5251,29 +5251,29 @@
       </c>
       <c r="C151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.composed.normal[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.composed.normal[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふぅん、こういう賞もあるんだね。…ありがとう</t>
+          <t xml:space="preserve">…治ったはずなのに。…まあ、焦らないよ</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.composed.normal[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.composed.normal[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5283,29 +5283,29 @@
       </c>
       <c r="C152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.composed.normal[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.composed.normal[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一年間、やるべきことをやった。それだけだよ</t>
+          <t xml:space="preserve">…戻ってきた。…のに、少し怖いかな</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.composed.normal[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.composed.normal[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5315,29 +5315,29 @@
       </c>
       <c r="C153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.composed.normal[1]</t>
+          <t xml:space="preserve">penalty_end.composed.normal[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、悪くないスタートかな。ここからだよ</t>
+          <t xml:space="preserve">…怪我は治った。…でも気力が、まだ</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.springTagChampion.composed.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.composed.normal[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">springTagChampion.composed.normal[1]</t>
+          <t xml:space="preserve">autumnWarChampion.composed.normal[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
@@ -5362,14 +5362,14 @@
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相棒との信頼を、結果として示せてよかった。</t>
+          <t xml:space="preserve">団体の看板を守れた。それが何よりだ。</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.composed.normal[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[1]</t>
+          <t xml:space="preserve">bestMatch.composed.normal[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
@@ -5394,14 +5394,14 @@
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドーム。…ついに辿り着きましたね</t>
+          <t xml:space="preserve">…悪くなかった。あの相手だから、出せたものがある</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.normal[2]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.composed.normal[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[2]</t>
+          <t xml:space="preserve">champion.composed.normal[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
@@ -5426,14 +5426,14 @@
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">感慨深いものがあります。しかし、今は試合に集中します</t>
+          <t xml:space="preserve">…このベルトの重さ、悪くない。…来るなら来なよ</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.normal[3]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.composed.normal[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[3]</t>
+          <t xml:space="preserve">hallOfFame.composed.normal[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
@@ -5458,14 +5458,14 @@
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この瞬間を、しっかり刻んでおきます</t>
+          <t xml:space="preserve">…いい時間だった。後悔？ …ないよ</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.composed.normal[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[1]</t>
+          <t xml:space="preserve">mediaAward.composed.normal[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
@@ -5490,14 +5490,14 @@
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員。…団体として、一つの到達点ですね</t>
+          <t xml:space="preserve">…ふぅん、こういう賞もあるんだね。…ありがとう</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.normal[2]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.composed.normal[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5507,12 +5507,12 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[2]</t>
+          <t xml:space="preserve">mvp.composed.normal[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
@@ -5522,14 +5522,14 @@
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お客様の拍手、今も胸に響いています</t>
+          <t xml:space="preserve">…一年間、やるべきことをやった。それだけだよ</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.normal[3]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.composed.normal[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[3]</t>
+          <t xml:space="preserve">rookie.composed.normal[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
@@ -5554,14 +5554,14 @@
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この記録、大切にしていきましょう</t>
+          <t xml:space="preserve">…ま、悪くないスタートかな。ここからだよ</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.composed.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.composed.normal[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5571,29 +5571,29 @@
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.composed.normal[1]</t>
+          <t xml:space="preserve">springTagChampion.composed.normal[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、少しずつ馴染んできたかな</t>
+          <t xml:space="preserve">相棒との信頼を、結果として示せてよかった。</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.composed.normal[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5603,29 +5603,29 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.composed.normal[2]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悪くない感触だね。この調子で行こう</t>
+          <t xml:space="preserve">ドーム。…ついに辿り着きましたね</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.composed.normal[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.normal[2]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5635,29 +5635,29 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.composed.normal[1]</t>
+          <t xml:space="preserve">composed.normal[2]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい仲間だね。悪くない環境だよ</t>
+          <t xml:space="preserve">感慨深いものがあります。しかし、今は試合に集中します</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.composed.normal[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.normal[3]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5667,29 +5667,29 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.composed.normal[1]</t>
+          <t xml:space="preserve">composed.normal[3]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ちょっと疲れただけ。すぐ戻るよ</t>
+          <t xml:space="preserve">この瞬間を、しっかり刻んでおきます</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.composed.normal[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5699,29 +5699,29 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.composed.normal[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがたいね。ちゃんと届いてるよ</t>
+          <t xml:space="preserve">満員。…団体として、一つの到達点ですね</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.composed.normal[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.normal[2]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5731,29 +5731,29 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.composed.normal[1]</t>
+          <t xml:space="preserve">composed.normal[2]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もういいよ。分かったから</t>
+          <t xml:space="preserve">お客様の拍手、今も胸に響いています</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.composed.normal[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.normal[3]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5763,29 +5763,29 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.composed.normal[1]</t>
+          <t xml:space="preserve">composed.normal[3]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ん、ちょっと考え事。気にしないで</t>
+          <t xml:space="preserve">この記録、大切にしていきましょう</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.composed.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.composed.normal[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5795,12 +5795,12 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">breakthrough.voice.composed.normal[1]</t>
+          <t xml:space="preserve">N1.composed.normal[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
@@ -5810,14 +5810,14 @@
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くない環境だね。…感謝してる</t>
+          <t xml:space="preserve">…ま、少しずつ馴染んできたかな</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.composed.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.composed.normal[2]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.composed.normal[1]</t>
+          <t xml:space="preserve">N1.composed.normal[2]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
@@ -5842,14 +5842,14 @@
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、こんなものか</t>
+          <t xml:space="preserve">悪くない感触だね。この調子で行こう</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.composed.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.composed.normal[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice.composed.normal[1]</t>
+          <t xml:space="preserve">N2.composed.normal[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5874,14 +5874,14 @@
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…伸びたね。…まあ、焦ることはない</t>
+          <t xml:space="preserve">…いい仲間だね。悪くない環境だよ</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.composed.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.composed.normal[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.composed.normal[1]</t>
+          <t xml:space="preserve">N3.composed.normal[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5906,14 +5906,14 @@
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、待つさ</t>
+          <t xml:space="preserve">…ちょっと疲れただけ。すぐ戻るよ</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.composed.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.composed.normal[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G4.voice.composed.normal[1]</t>
+          <t xml:space="preserve">N4.composed.normal[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -5938,14 +5938,14 @@
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、待つよ</t>
+          <t xml:space="preserve">…ありがたいね。ちゃんと届いてるよ</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.composed.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.composed.normal[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice.composed.normal[1]</t>
+          <t xml:space="preserve">N5_low.composed.normal[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -5970,14 +5970,14 @@
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…別に。一人でも困らない</t>
+          <t xml:space="preserve">…もういいよ。分かったから</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.composed.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.composed.normal[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5987,12 +5987,12 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal.composed.normal[1]</t>
+          <t xml:space="preserve">N5_warning.composed.normal[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -6002,14 +6002,14 @@
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうか。…{name2}がいなくなるのか</t>
+          <t xml:space="preserve">…ん、ちょっと考え事。気にしないで</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.composed.normal[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice.composed.normal[1]</t>
+          <t xml:space="preserve">breakthrough.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -6034,14 +6034,14 @@
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くない。…やっと追いついた</t>
+          <t xml:space="preserve">…悪くない環境だね。…感謝してる</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.composed.normal[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice.composed.normal[1]</t>
+          <t xml:space="preserve">G1.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -6066,14 +6066,14 @@
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…足りなかった。…次、だね</t>
+          <t xml:space="preserve">…まあ、こんなものか</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.composed.normal[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -6083,29 +6083,29 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_insult.composed.normal[1]</t>
+          <t xml:space="preserve">G2.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…これで済ませるつもりかい。そうか</t>
+          <t xml:space="preserve">…伸びたね。…まあ、焦ることはない</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.composed.normal[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6115,29 +6115,29 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.composed.normal[1]</t>
+          <t xml:space="preserve">G3.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう。大事に使うよ</t>
+          <t xml:space="preserve">…まあ、待つさ</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.composed.normal[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6147,29 +6147,29 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.composed.normal[1]</t>
+          <t xml:space="preserve">G4.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…合宿か。じっくりやろう</t>
+          <t xml:space="preserve">…まあ、待つよ</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.composed.normal[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6179,29 +6179,29 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.composed.normal[1]</t>
+          <t xml:space="preserve">R2.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…見てくれてたんだ。…悪くないね</t>
+          <t xml:space="preserve">…別に。一人でも困らない</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.composed.normal[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.composed.normal[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6211,29 +6211,29 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.composed.normal[1]</t>
+          <t xml:space="preserve">R3.modal.composed.normal[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう。もう少しやってみるよ</t>
+          <t xml:space="preserve">…そうか。…{name2}がいなくなるのか</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.composed.normal[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6243,29 +6243,29 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.composed.normal[1]</t>
+          <t xml:space="preserve">R4.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なるほど。やってみるよ</t>
+          <t xml:space="preserve">…悪くない。…やっと追いついた</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.composed.normal[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6275,29 +6275,29 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.composed.normal[1]</t>
+          <t xml:space="preserve">R5.voice.composed.normal[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい時間だったね。悪くないよ</t>
+          <t xml:space="preserve">…足りなかった。…次、だね</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.composed.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.composed.normal[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.composed.normal[1]</t>
+          <t xml:space="preserve">bonus_insult.composed.normal[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6322,14 +6322,14 @@
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう。少し休んでくるよ</t>
+          <t xml:space="preserve">…これで済ませるつもりかい。そうか</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.composed.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.composed.normal[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.composed.normal[1]</t>
+          <t xml:space="preserve">bonus.composed.normal[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6354,14 +6354,14 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう。リング、待たせちゃ悪いね</t>
+          <t xml:space="preserve">…ありがとう。大事に使うよ</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.composed.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.composed.normal[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.composed.normal[1]</t>
+          <t xml:space="preserve">camp.composed.normal[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6386,14 +6386,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…了解。しっかり吸収するよ</t>
+          <t xml:space="preserve">…合宿か。じっくりやろう</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.composed.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.composed.normal[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6403,12 +6403,12 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.composed.normal[1]</t>
+          <t xml:space="preserve">encourage_high_trust.composed.normal[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6418,14 +6418,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…メディアか。いい機会だね</t>
+          <t xml:space="preserve">…見てくれてたんだ。…悪くないね</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E4.composed.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.composed.normal[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E4.composed.normal[1]</t>
+          <t xml:space="preserve">encourage.composed.normal[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6450,14 +6450,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…スカウトから、新しい話が来てるみたいだよ</t>
+          <t xml:space="preserve">…ありがとう。もう少しやってみるよ</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.composed.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.composed.normal[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6467,12 +6467,12 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.composed.normal[1]</t>
+          <t xml:space="preserve">media.composed.normal[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6482,14 +6482,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…他所から話が来てるんだ。一応報告しておくね</t>
+          <t xml:space="preserve">…なるほど。やってみるよ</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.composed.normal[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.composed.normal[1]</t>
+          <t xml:space="preserve">party.composed.normal[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6514,14 +6514,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…今日はいいかな。少し考えたいことがあって</t>
+          <t xml:space="preserve">…いい時間だったね。悪くないよ</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.composed.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.composed.normal[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6531,12 +6531,12 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.composed.normal[1]</t>
+          <t xml:space="preserve">refresh_leave.composed.normal[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6546,14 +6546,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（いつもの穏やかさが消え、「…ま、そういうことだよね」と静かに呟いている）</t>
+          <t xml:space="preserve">…ありがとう。少し休んでくるよ</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.composed.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.composed.normal[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6563,12 +6563,12 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.composed.normal[1]</t>
+          <t xml:space="preserve">special_treatment.composed.normal[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6578,14 +6578,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに夕焼けの写真と「…少し考える時間が欲しいかな」と投稿。ファンがざわついている）</t>
+          <t xml:space="preserve">…ありがとう。リング、待たせちゃ悪いね</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.composed.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.composed.normal[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6595,12 +6595,12 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.composed.normal[1]</t>
+          <t xml:space="preserve">trainer.composed.normal[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6610,14 +6610,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そろそろベルトに挑戦させてもらえないかな</t>
+          <t xml:space="preserve">…了解。しっかり吸収するよ</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.composed.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.composed.normal[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6632,7 +6632,7 @@
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.composed.normal[1]</t>
+          <t xml:space="preserve">E1.composed.normal[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6642,14 +6642,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの人との試合、そろそろ組んでもらえないかな</t>
+          <t xml:space="preserve">…メディアか。いい機会だね</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.composed.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E4.composed.normal[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.composed.normal[1]</t>
+          <t xml:space="preserve">E4.composed.normal[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6674,14 +6674,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…少し休ませてもらえるかな</t>
+          <t xml:space="preserve">…スカウトから、新しい話が来てるみたいだよ</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.composed.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.composed.normal[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.composed.normal[1]</t>
+          <t xml:space="preserve">E6.composed.normal[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6706,14 +6706,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…このままだと困るんだよね。少し考えてもらえるかな</t>
+          <t xml:space="preserve">…他所から話が来てるんだ。一応報告しておくね</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.composed.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.normal[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.composed.normal[1]</t>
+          <t xml:space="preserve">S_boycott.composed.normal[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6738,14 +6738,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…（少し間を置いて）…いや、なんでもないよ</t>
+          <t xml:space="preserve">…今日はいいかな。少し考えたいことがあって</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.composed.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.composed.normal[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.composed.normal[1]</t>
+          <t xml:space="preserve">S_grumble.composed.normal[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6770,14 +6770,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…少し追い込みたいんだ。特訓させてもらえるかな</t>
+          <t xml:space="preserve">（いつもの穏やかさが消え、「…ま、そういうことだよね」と静かに呟いている）</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.composed.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.composed.normal[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6792,7 +6792,7 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.composed.normal[1]</t>
+          <t xml:space="preserve">S_sns.composed.normal[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6802,14 +6802,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…後輩の面倒、見させてもらえないかな</t>
+          <t xml:space="preserve">（SNSに夕焼けの写真と「…少し考える時間が欲しいかな」と投稿。ファンがざわついている）</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.composed.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.composed.normal[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.composed.normal[1]</t>
+          <t xml:space="preserve">S1.composed.normal[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6834,14 +6834,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やっちゃったね。まあ、焦らず治すよ</t>
+          <t xml:space="preserve">…そろそろベルトに挑戦させてもらえないかな</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.composed.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.composed.normal[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.composed.normal[1]</t>
+          <t xml:space="preserve">S2.composed.normal[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6866,14 +6866,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、合わない人もいるよね。少し距離を置きたいな</t>
+          <t xml:space="preserve">…あの人との試合、そろそろ組んでもらえないかな</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.composed.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.composed.normal[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.composed.normal[1]</t>
+          <t xml:space="preserve">S3.composed.normal[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6898,14 +6898,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふぅん。まあ、お互い様だと思うけどね</t>
+          <t xml:space="preserve">…少し休ませてもらえるかな</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.composed.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.composed.normal[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.composed.normal[1]</t>
+          <t xml:space="preserve">S4_direct.composed.normal[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6930,14 +6930,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…コラボか。なるほどね、面白そう</t>
+          <t xml:space="preserve">…このままだと困るんだよね。少し考えてもらえるかな</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.composed.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.composed.normal[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.composed.normal[1]</t>
+          <t xml:space="preserve">S4_silent.composed.normal[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6962,14 +6962,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…CMか。まあ、悪くないね</t>
+          <t xml:space="preserve">…（少し間を置いて）…いや、なんでもないよ</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.composed.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.composed.normal[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.composed.normal[1]</t>
+          <t xml:space="preserve">S5.composed.normal[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6994,14 +6994,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…直接話せるんだ。…それは、楽しみだね</t>
+          <t xml:space="preserve">…少し追い込みたいんだ。特訓させてもらえるかな</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.composed.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.composed.normal[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -7011,12 +7011,12 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.composed.normal[1]</t>
+          <t xml:space="preserve">S6.composed.normal[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -7026,14 +7026,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ランウェイか。歩けるかな。…まあ、やってみるよ</t>
+          <t xml:space="preserve">…後輩の面倒、見させてもらえないかな</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.composed.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.composed.normal[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -7048,7 +7048,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.composed.normal[1]</t>
+          <t xml:space="preserve">B1.composed.normal[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -7058,14 +7058,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…グラビアか。まあ、たまにはいいんじゃない</t>
+          <t xml:space="preserve">…やっちゃったね。まあ、焦らず治すよ</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.composed.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.composed.normal[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.composed.normal[1]</t>
+          <t xml:space="preserve">B2_fighter1.composed.normal[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -7090,14 +7090,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…バラエティか。まあ、のんびり喋るよ</t>
+          <t xml:space="preserve">…まあ、合わない人もいるよね。少し距離を置きたいな</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.composed.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.composed.normal[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -7112,7 +7112,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.composed.normal[1]</t>
+          <t xml:space="preserve">B2_fighter2.composed.normal[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -7122,14 +7122,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…取材か。まあ、いつも通りやるよ</t>
+          <t xml:space="preserve">…ふぅん。まあ、お互い様だと思うけどね</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.composed.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.composed.normal[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7139,29 +7139,29 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[1]</t>
+          <t xml:space="preserve">B4_brand.composed.normal[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…選んでくれるなら、応えるよ</t>
+          <t xml:space="preserve">…コラボか。なるほどね、面白そう</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.composed.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.composed.normal[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7171,29 +7171,29 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[1]</t>
+          <t xml:space="preserve">B4_cm.composed.normal[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。精一杯やるよ</t>
+          <t xml:space="preserve">…CMか。まあ、悪くないね</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.composed.normal[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.composed.normal[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7203,29 +7203,29 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[2]</t>
+          <t xml:space="preserve">B4_fan.composed.normal[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…選んでくれてありがとう</t>
+          <t xml:space="preserve">…直接話せるんだ。…それは、楽しみだね</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.composed.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.composed.normal[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7235,29 +7235,29 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[1]</t>
+          <t xml:space="preserve">B4_fashion.composed.normal[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。力になるよ</t>
+          <t xml:space="preserve">…ランウェイか。歩けるかな。…まあ、やってみるよ</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.composed.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.composed.normal[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7267,29 +7267,29 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[1]</t>
+          <t xml:space="preserve">B4_gravure.composed.normal[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。精一杯やるよ</t>
+          <t xml:space="preserve">…グラビアか。まあ、たまにはいいんじゃない</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.composed.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.composed.normal[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7299,29 +7299,29 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[1]</t>
+          <t xml:space="preserve">B4_variety.composed.normal[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…少し休むよ。すぐ戻る</t>
+          <t xml:space="preserve">…バラエティか。まあ、のんびり喋るよ</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.composed.normal[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.composed.normal[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7331,29 +7331,29 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[2]</t>
+          <t xml:space="preserve">B4.composed.normal[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…大したことじゃないから、安心して</t>
+          <t xml:space="preserve">…取材か。まあ、いつも通りやるよ</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.composed.normal[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7378,14 +7378,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…決着はついてる。…なのに、まだ喉に引っかかってる</t>
+          <t xml:space="preserve">…選んでくれるなら、応えるよ</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7395,12 +7395,12 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.composed.normal[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7410,14 +7410,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…片がついたらしいよ。…誰の中で、って話だけど</t>
+          <t xml:space="preserve">…よろしく。精一杯やるよ</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.composed.normal[2]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.composed.normal[1]</t>
+          <t xml:space="preserve">composed.normal[2]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7442,14 +7442,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…選んでくれるなら、応えるよ</t>
+          <t xml:space="preserve">…選んでくれてありがとう</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.composed.normal[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7474,14 +7474,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。精一杯やるよ</t>
+          <t xml:space="preserve">…よろしく。力になるよ</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.composed.normal[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.composed.normal[2]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7506,14 +7506,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…選んでくれてありがとう</t>
+          <t xml:space="preserve">…よろしく。精一杯やるよ</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.composed.normal[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7538,14 +7538,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…また名前を呼ばれる場所ができた。悪くないよ</t>
+          <t xml:space="preserve">…少し休むよ。すぐ戻る</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.composed.normal[2]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7555,12 +7555,12 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.composed.normal[1]</t>
+          <t xml:space="preserve">composed.normal[2]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7570,14 +7570,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。力になるよ</t>
+          <t xml:space="preserve">…大したことじゃないから、安心して</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.composed.normal[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.composed.normal[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.composed.normal[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7602,14 +7602,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。精一杯やるよ</t>
+          <t xml:space="preserve">…決着はついてる。…なのに、まだ喉に引っかかってる</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.composed.normal[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7624,7 +7624,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.composed.normal[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.composed.normal[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7634,14 +7634,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…体は軽いね。こういう日は、伸びるんだよ</t>
+          <t xml:space="preserve">…片がついたらしいよ。…誰の中で、って話だけど</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.composed.normal[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7656,7 +7656,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.composed.normal[1]</t>
+          <t xml:space="preserve">draftInterest.composed.normal[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7666,14 +7666,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…体が重いね。今日やっても、たぶん流れるだけ</t>
+          <t xml:space="preserve">…選んでくれるなら、応えるよ</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.composed.normal[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7688,7 +7688,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.composed.normal[1]</t>
+          <t xml:space="preserve">draftJoin.composed.normal[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7698,14 +7698,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くはないよ。…ただ、切れが一つ落ちたかな</t>
+          <t xml:space="preserve">…よろしく。精一杯やるよ</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.composed.normal[2]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7720,7 +7720,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.composed.normal[1]</t>
+          <t xml:space="preserve">draftJoin.composed.normal[2]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7730,14 +7730,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…少し休むよ。すぐ戻る</t>
+          <t xml:space="preserve">…選んでくれてありがとう</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.composed.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.composed.normal[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7752,7 +7752,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.composed.normal[2]</t>
+          <t xml:space="preserve">faGreeting.composed.normal[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7762,14 +7762,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…大したことじゃないから、安心して</t>
+          <t xml:space="preserve">…また名前を呼ばれる場所ができた。悪くないよ</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.composed.normal[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.composed.normal[1]</t>
+          <t xml:space="preserve">faSigning.composed.normal[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7794,14 +7794,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうか。お世話になったね</t>
+          <t xml:space="preserve">…よろしく。力になるよ</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.composed.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.composed.normal[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.composed.normal[2]</t>
+          <t xml:space="preserve">faWelcome.composed.normal[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7826,14 +7826,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…短い間だったけど、ありがとう</t>
+          <t xml:space="preserve">…よろしく。精一杯やるよ</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.composed.normal[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.composed.normal[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.composed.normal[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7858,14 +7858,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…短い間だけど、手は抜かないよ</t>
+          <t xml:space="preserve">…体は軽いね。こういう日は、伸びるんだよ</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.composed.normal[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.composed.normal[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.composed.normal[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7890,14 +7890,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…見込まれたなら、応えるだけだよ</t>
+          <t xml:space="preserve">…体が重いね。今日やっても、たぶん流れるだけ</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.composed.normal[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7912,7 +7912,7 @@
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.composed.normal[1]</t>
+          <t xml:space="preserve">heatSelf.warm.composed.normal[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7922,14 +7922,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…届かなかったか。…次だね</t>
+          <t xml:space="preserve">…悪くはないよ。…ただ、切れが一つ落ちたかな</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.composed.normal[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7944,7 +7944,7 @@
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.composed.normal[1]</t>
+          <t xml:space="preserve">injury.composed.normal[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7954,14 +7954,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…防衛か。…まだ渡すつもりはないよ</t>
+          <t xml:space="preserve">…少し休むよ。すぐ戻る</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.composed.normal[2]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.composed.normal[1]</t>
+          <t xml:space="preserve">injury.composed.normal[2]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7986,14 +7986,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…失ったか。…でも終わりじゃない</t>
+          <t xml:space="preserve">…大したことじゃないから、安心して</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.composed.normal[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -8008,7 +8008,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.composed.normal[1]</t>
+          <t xml:space="preserve">release.composed.normal[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -8018,14 +8018,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…チャンピオンか。…悪くないね</t>
+          <t xml:space="preserve">…そうか。お世話になったね</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.composed.normal[2]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -8035,12 +8035,12 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[1]</t>
+          <t xml:space="preserve">release.composed.normal[2]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -8050,14 +8050,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうか。お世話になったね</t>
+          <t xml:space="preserve">…短い間だったけど、ありがとう</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.composed.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.composed.normal[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[2]</t>
+          <t xml:space="preserve">rentalGreeting.composed.normal[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -8082,14 +8082,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…短い間だったけど、ありがとう</t>
+          <t xml:space="preserve">…短い間だけど、手は抜かないよ</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.composed.normal[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[1]</t>
+          <t xml:space="preserve">scoutGreeting.composed.normal[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -8114,14 +8114,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…短い間だけど、手は抜かないよ</t>
+          <t xml:space="preserve">…見込まれたなら、応えるだけだよ</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.composed.normal[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.composed.normal[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8153,7 +8153,7 @@
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.composed.normal[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[1]</t>
+          <t xml:space="preserve">titleDefense.composed.normal[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8185,7 +8185,7 @@
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.composed.normal[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[1]</t>
+          <t xml:space="preserve">titleLoss.composed.normal[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8217,7 +8217,7 @@
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.composed.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.composed.normal[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8227,12 +8227,12 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[1]</t>
+          <t xml:space="preserve">titleWin.composed.normal[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8249,7 +8249,7 @@
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8259,29 +8259,29 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.normal.composed[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…合わないね。…仕方ない</t>
+          <t xml:space="preserve">…そうか。お世話になったね</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.composed.normal[2]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8291,29 +8291,29 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.normal.composed[1]</t>
+          <t xml:space="preserve">composed.normal[2]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…少し距離が開いたかな</t>
+          <t xml:space="preserve">…短い間だったけど、ありがとう</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8323,29 +8323,29 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.normal.composed[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くない距離感だね。一緒にいて楽だ</t>
+          <t xml:space="preserve">…短い間だけど、手は抜かないよ</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8355,29 +8355,29 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.normal.composed[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…大事な存在。…それだけで十分</t>
+          <t xml:space="preserve">…届かなかったか。…次だね</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8387,29 +8387,29 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.normal.composed[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう終わったことだね</t>
+          <t xml:space="preserve">…防衛か。…まだ渡すつもりはないよ</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8419,29 +8419,29 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.normal.composed[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…気になるね。…負けたくない</t>
+          <t xml:space="preserve">…失ったか。…でも終わりじゃない</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.normal.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8451,29 +8451,29 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.normal.composed[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…負けるわけにはいかない。…絶対に</t>
+          <t xml:space="preserve">…チャンピオンか。…悪くないね</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.normal.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.normal.composed[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.normal.composed[1]</t>
+          <t xml:space="preserve">bond_39_down.normal.composed[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8498,14 +8498,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…運命みたいなものだね。…この人とは</t>
+          <t xml:space="preserve">…合わないね。…仕方ない</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.normal.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.normal.composed[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.normal.composed[1]</t>
+          <t xml:space="preserve">bond_59_down.normal.composed[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8530,14 +8530,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここが自分の居場所だね。…悪くない</t>
+          <t xml:space="preserve">…少し距離が開いたかな</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.normal.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.normal.composed[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.normal.composed[1]</t>
+          <t xml:space="preserve">bond_60_up.normal.composed[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8562,14 +8562,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここにいる理由が、見つからなくなった</t>
+          <t xml:space="preserve">…悪くない距離感だね。一緒にいて楽だ</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.normal.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.normal.composed[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.normal.composed[1]</t>
+          <t xml:space="preserve">bond_80_up.normal.composed[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8594,14 +8594,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここで本当にやれるのかな</t>
+          <t xml:space="preserve">…大事な存在。…それだけで十分</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.composed.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.normal.composed[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8611,12 +8611,12 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-11.composed.normal[1]</t>
+          <t xml:space="preserve">rivalry_29_down.normal.composed[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8626,14 +8626,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの子は、もう心の中にはいない。ただ、それだけのことだ</t>
+          <t xml:space="preserve">…もう終わったことだね</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.composed.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.normal.composed[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[1]</t>
+          <t xml:space="preserve">rivalry_30_up.normal.composed[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8658,14 +8658,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…好調は終わったか。…でも悪くない経験だった</t>
+          <t xml:space="preserve">…気になるね。…負けたくない</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.normal.composed[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8675,29 +8675,29 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.normal[1]</t>
+          <t xml:space="preserve">rivalry_50_up.normal.composed[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…満身創痍だね。でも、ここで降りる理由はないよ</t>
+          <t xml:space="preserve">…負けるわけにはいかない。…絶対に</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.normal.composed[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8707,29 +8707,29 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.normal[2]</t>
+          <t xml:space="preserve">rivalry_70_up.normal.composed[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…身体は限界に近い。それでも、最後の一戦だけは立って迎えるよ</t>
+          <t xml:space="preserve">…運命みたいなものだね。…この人とは</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.normal[3]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.normal.composed[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8739,29 +8739,29 @@
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.normal[3]</t>
+          <t xml:space="preserve">trust_above_75.normal.composed[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…傷は数えきれない。まあ、最後まで残った証だと思えばいいよ</t>
+          <t xml:space="preserve">…ここが自分の居場所だね。…悪くない</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.normal.composed[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8771,29 +8771,29 @@
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.normal[1]</t>
+          <t xml:space="preserve">trust_below_20.normal.composed[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…相手は選べない。来た順に、真っ向から受けるだけだよ</t>
+          <t xml:space="preserve">…ここにいる理由が、見つからなくなった</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.normal.composed[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8803,29 +8803,29 @@
       </c>
       <c r="C262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.normal[2]</t>
+          <t xml:space="preserve">trust_below_35.normal.composed[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…焦らない。目の前の一人に集中する。それでリングは渡さない</t>
+          <t xml:space="preserve">…ここで本当にやれるのかな</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.normal[3]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.composed.normal[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8835,29 +8835,29 @@
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.normal[3]</t>
+          <t xml:space="preserve">GL-11.composed.normal[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この一戦から、始まる。落ち着いていこうか</t>
+          <t xml:space="preserve">あの子は、もう心の中にはいない。ただ、それだけのことだ</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8867,29 +8867,29 @@
       </c>
       <c r="C264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.composed.normal[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一人片づけた。息は上がってるけど、退く理由はないよ。次、来なよ</t>
+          <t xml:space="preserve">…好調は終わったか。…でも悪くない経験だった</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.normal[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.composed.normal[2]</t>
+          <t xml:space="preserve">preFinal.composed.normal[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8914,14 +8914,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ足は動く。このリングは渡さない。次は誰だ</t>
+          <t xml:space="preserve">…満身創痍だね。でも、ここで降りる理由はないよ</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.normal[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.normal[2]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8936,7 +8936,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.composed.normal[3]</t>
+          <t xml:space="preserve">preFinal.composed.normal[2]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8946,14 +8946,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふぅ。まだ立ってる。この場所、そう簡単には空けないよ。次</t>
+          <t xml:space="preserve">…身体は限界に近い。それでも、最後の一戦だけは立って迎えるよ</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.normal[3]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.normal[1]</t>
+          <t xml:space="preserve">preFinal.composed.normal[3]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8978,14 +8978,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で繋いだ結果だ。誰が欠けても……この景色はなかった</t>
+          <t xml:space="preserve">…傷は数えきれない。まあ、最後まで残った証だと思えばいいよ</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.normal[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.normal[2]</t>
+          <t xml:space="preserve">preMatch.composed.normal[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -9010,14 +9010,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人の手柄にするつもりはない。これは、三人の勝利だ</t>
+          <t xml:space="preserve">…相手は選べない。来た順に、真っ向から受けるだけだよ</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.normal[2]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -9027,12 +9027,12 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.composed.normal[1]</t>
+          <t xml:space="preserve">preMatch.composed.normal[2]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -9042,14 +9042,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">個人の栄誉は受け取る。だが……これで満足する理由にはならない</t>
+          <t xml:space="preserve">…焦らない。目の前の一人に集中する。それでリングは渡さない</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.normal[3]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -9059,12 +9059,12 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.composed.normal[2]</t>
+          <t xml:space="preserve">preMatch.composed.normal[3]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -9074,14 +9074,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次がある。その時は、チーム全員で最後に立つ</t>
+          <t xml:space="preserve">…この一戦から、始まる。落ち着いていこうか</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.normal[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -9091,12 +9091,12 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.composed.normal[1]</t>
+          <t xml:space="preserve">survivor.composed.normal[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -9106,14 +9106,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体は限界を告げている。それでも……最後の一人を見届けるまで、退けなかった</t>
+          <t xml:space="preserve">…一人片づけた。息は上がってるけど、退く理由はないよ。次、来なよ</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.normal[2]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.composed.normal[2]</t>
+          <t xml:space="preserve">survivor.composed.normal[2]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9138,14 +9138,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何度か意識が揺れた。だが、リングを降りる理由にはならなかった</t>
+          <t xml:space="preserve">…まだ足は動く。このリングは渡さない。次は誰だ</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.composed.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.normal[3]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.normal[1]</t>
+          <t xml:space="preserve">survivor.composed.normal[3]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9170,14 +9170,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…優勝か。…悪くないね。…次も行こう</t>
+          <t xml:space="preserve">…ふぅ。まだ立ってる。この場所、そう簡単には空けないよ。次</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.composed.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.normal[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9187,12 +9187,12 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.composed.normal[1]</t>
+          <t xml:space="preserve">champion.composed.normal[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9202,14 +9202,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ足りないか。…次までに詰めよう</t>
+          <t xml:space="preserve">三人で繋いだ結果だ。誰が欠けても……この景色はなかった</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.composed.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.normal[2]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.composed.normal[1]</t>
+          <t xml:space="preserve">champion.composed.normal[2]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9234,14 +9234,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一つ勝ち。…次もこの調子で</t>
+          <t xml:space="preserve">一人の手柄にするつもりはない。これは、三人の勝利だ</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.composed.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.normal[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.composed.normal[1]</t>
+          <t xml:space="preserve">defiant.composed.normal[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9266,14 +9266,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くなかったね。…いい経験になった</t>
+          <t xml:space="preserve">個人の栄誉は受け取る。だが……これで満足する理由にはならない</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.composed.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.normal[2]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9283,12 +9283,12 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.normal[1]</t>
+          <t xml:space="preserve">defiant.composed.normal[2]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9298,14 +9298,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…決勝か。…全部出し切るよ</t>
+          <t xml:space="preserve">次がある。その時は、チーム全員で最後に立つ</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.normal[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9315,12 +9315,12 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.normal[1]</t>
+          <t xml:space="preserve">gauntlet.composed.normal[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9330,14 +9330,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いつも通りやるよ</t>
+          <t xml:space="preserve">身体は限界を告げている。それでも……最後の一人を見届けるまで、退けなかった</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.normal[2]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9347,12 +9347,12 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.normal[2]</t>
+          <t xml:space="preserve">gauntlet.composed.normal[2]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9362,14 +9362,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…集中。…行こうか</t>
+          <t xml:space="preserve">何度か意識が揺れた。だが、リングを降りる理由にはならなかった</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.composed.normal[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9384,7 +9384,7 @@
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.composed.normal[1]</t>
+          <t xml:space="preserve">champion.composed.normal[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9394,14 +9394,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…出るよ。…やるだけだね</t>
+          <t xml:space="preserve">…優勝か。…悪くないね。…次も行こう</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.composed.normal[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.composed.normal[2]</t>
+          <t xml:space="preserve">postLose.composed.normal[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9426,14 +9426,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なるほど。じゃあ、行こうか</t>
+          <t xml:space="preserve">…まだ足りないか。…次までに詰めよう</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.composed.normal[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[1]</t>
+          <t xml:space="preserve">postMatchWin.composed.normal[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9458,14 +9458,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい舞台だね。…全力で行くよ</t>
+          <t xml:space="preserve">…一つ勝ち。…次もこの調子で</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.composed.normal[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9475,12 +9475,12 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[2]</t>
+          <t xml:space="preserve">postWin.composed.normal[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9490,14 +9490,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…負けるつもりはないよ。よろしく</t>
+          <t xml:space="preserve">…悪くなかったね。…いい経験になった</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.composed.normal[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[1]</t>
+          <t xml:space="preserve">preFinal.composed.normal[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9522,14 +9522,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やったよ。…ここまで来れたか</t>
+          <t xml:space="preserve">…決勝か。…全部出し切るよ</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.normal[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[2]</t>
+          <t xml:space="preserve">preMatch.composed.normal[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9554,14 +9554,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くない結末だね。みんな、ありがとう</t>
+          <t xml:space="preserve">…いつも通りやるよ</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.normal[2]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[1]</t>
+          <t xml:space="preserve">preMatch.composed.normal[2]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9586,14 +9586,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そちらの実力、確かめさせてもらうよ</t>
+          <t xml:space="preserve">…集中。…行こうか</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.normal[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[2]</t>
+          <t xml:space="preserve">summon.composed.normal[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9618,14 +9618,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…本気で来なよ。受けて立つから</t>
+          <t xml:space="preserve">…出るよ。…やるだけだね</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.normal[2]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[1]</t>
+          <t xml:space="preserve">summon.composed.normal[2]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9650,14 +9650,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうか。そんな時もあるね</t>
+          <t xml:space="preserve">…なるほど。じゃあ、行こうか</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.normal[2]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9667,12 +9667,12 @@
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[2]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9682,14 +9682,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、そういうこともあるか</t>
+          <t xml:space="preserve">…いい舞台だね。…全力で行くよ</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.composed.normal[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.normal[2]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9699,12 +9699,12 @@
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.composed.normal[1]</t>
+          <t xml:space="preserve">composed.normal[2]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9714,14 +9714,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…負けたか。…次は違う結果にする</t>
+          <t xml:space="preserve">…負けるつもりはないよ。よろしく</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.composed.normal[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.composed.normal[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9746,14 +9746,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝ったね。…いい対抗戦だった</t>
+          <t xml:space="preserve">…やったよ。…ここまで来れたか</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.composed.normal[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.normal[2]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9763,12 +9763,12 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[1]</t>
+          <t xml:space="preserve">composed.normal[2]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9778,14 +9778,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…団体の看板、守れたかな。…悪くないね</t>
+          <t xml:space="preserve">…悪くない結末だね。みんな、ありがとう</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.composed.normal[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.normal[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[2]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9810,14 +9810,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝った。…うちの力を見せられたと思う</t>
+          <t xml:space="preserve">…そちらの実力、確かめさせてもらうよ</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.composed.normal[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.normal[2]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9827,29 +9827,29 @@
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.composed.normal[1]</t>
+          <t xml:space="preserve">composed.normal[2]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここまで来れたか。…悪くない景色だね</t>
+          <t xml:space="preserve">…本気で来なよ。受けて立つから</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.composed.normal[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.normal[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="12">
@@ -9869,49 +9869,273 @@
       </c>
       <c r="E295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…また名前を呼ばれる場所ができた。悪くないよ</t>
+          <t xml:space="preserve">…そうか。そんな時もあるね</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.normal[2]</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.normal[2]</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…まあ、そういうこともあるか</t>
+        </is>
+      </c>
+    </row>
+    <row r="297" ht="40" customHeight="1">
+      <c r="A297" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.composed.normal[1]</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.composed.normal[1]</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…負けたか。…次は違う結果にする</t>
+        </is>
+      </c>
+    </row>
+    <row r="298" ht="40" customHeight="1">
+      <c r="A298" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.composed.normal[1]</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.composed.normal[1]</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…勝ったね。…いい対抗戦だった</t>
+        </is>
+      </c>
+    </row>
+    <row r="299" ht="40" customHeight="1">
+      <c r="A299" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.composed.normal[1]</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.normal[1]</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…団体の看板、守れたかな。…悪くないね</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="40" customHeight="1">
+      <c r="A300" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.composed.normal[2]</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.normal[2]</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…勝った。…うちの力を見せられたと思う</t>
+        </is>
+      </c>
+    </row>
+    <row r="301" ht="40" customHeight="1">
+      <c r="A301" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.composed.normal[1]</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.composed.normal[1]</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ここまで来れたか。…悪くない景色だね</t>
+        </is>
+      </c>
+    </row>
+    <row r="302" ht="40" customHeight="1">
+      <c r="A302" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.composed.normal[1]</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.normal[1]</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…また名前を呼ばれる場所ができた。悪くないよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="303" ht="40" customHeight="1">
+      <c r="A303" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.composed.normal[1]</t>
         </is>
       </c>
-      <c r="B296" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr" s="2">
+      <c r="B303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr" s="12">
+      <c r="D303" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
-      <c r="E296" t="inlineStr" s="2">
+      <c r="E303" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F296" t="inlineStr" s="3">
+      <c r="F303" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…見込まれたなら、応えるだけだよ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H296"/>
+  <autoFilter ref="A1:H303"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/鷹揚×ノーマル.xlsx
+++ b/セリフ編集/キャラタイプ別/鷹揚×ノーマル.xlsx
@@ -411,7 +411,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H296"/>
+  <dimension ref="A1:H304"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -8601,7 +8601,7 @@
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.composed.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.composed.normal[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-11.composed.normal[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss.composed.normal[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8626,14 +8626,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの子は、もう心の中にはいない。ただ、それだけのことだ</t>
+          <t xml:space="preserve">…負けたけど…悪くない試合だった</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.composed.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.composed.normal[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.composed.normal[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8658,14 +8658,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…好調は終わったか。…でも悪くない経験だった</t>
+          <t xml:space="preserve">…最高の試合で勝てた。…こういう日もあるね</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.composed.normal[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8675,29 +8675,29 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.normal[1]</t>
+          <t xml:space="preserve">GL-01.loss.composed.normal[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…満身創痍だね。でも、ここで降りる理由はないよ</t>
+          <t xml:space="preserve">…負けたか。…次だね</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.composed.normal[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8707,29 +8707,29 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.normal[2]</t>
+          <t xml:space="preserve">GL-01.win.composed.normal[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…身体は限界に近い。それでも、最後の一戦だけは立って迎えるよ</t>
+          <t xml:space="preserve">…勝ったね。…こんなもんかな</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.normal[3]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02-hostile.composed.normal[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8739,29 +8739,29 @@
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.normal[3]</t>
+          <t xml:space="preserve">GL-02-hostile.composed.normal[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…傷は数えきれない。まあ、最後まで残った証だと思えばいいよ</t>
+          <t xml:space="preserve">…あの子のせいで、今日の調子は最悪だった</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.composed.normal[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8771,29 +8771,29 @@
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.normal[1]</t>
+          <t xml:space="preserve">GL-02.composed.normal[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…相手は選べない。来た順に、真っ向から受けるだけだよ</t>
+          <t xml:space="preserve">…まあ、いい感じだ</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.composed.normal[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8803,29 +8803,29 @@
       </c>
       <c r="C262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.normal[2]</t>
+          <t xml:space="preserve">GL-03.down.composed.normal[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…焦らない。目の前の一人に集中する。それでリングは渡さない</t>
+          <t xml:space="preserve">…最近、ちょっと引っかかることがあるかな</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.normal[3]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.composed.normal[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8835,29 +8835,29 @@
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.normal[3]</t>
+          <t xml:space="preserve">GL-03.up.composed.normal[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この一戦から、始まる。落ち着いていこうか</t>
+          <t xml:space="preserve">…悪くない環境だね</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.composed.normal[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8867,29 +8867,29 @@
       </c>
       <c r="C264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.composed.normal[1]</t>
+          <t xml:space="preserve">GL-11.composed.normal[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一人片づけた。息は上がってるけど、退く理由はないよ。次、来なよ</t>
+          <t xml:space="preserve">あの子は、もう心の中にはいない。ただ、それだけのことだ</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8899,29 +8899,29 @@
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.composed.normal[2]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ足は動く。このリングは渡さない。次は誰だ</t>
+          <t xml:space="preserve">…好調は終わったか。…でも悪くない経験だった</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.normal[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.normal[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8936,7 +8936,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.composed.normal[3]</t>
+          <t xml:space="preserve">preFinal.composed.normal[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8946,14 +8946,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふぅ。まだ立ってる。この場所、そう簡単には空けないよ。次</t>
+          <t xml:space="preserve">…満身創痍だね。でも、ここで降りる理由はないよ</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.normal[2]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.normal[1]</t>
+          <t xml:space="preserve">preFinal.composed.normal[2]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8978,14 +8978,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で繋いだ結果だ。誰が欠けても……この景色はなかった</t>
+          <t xml:space="preserve">…身体は限界に近い。それでも、最後の一戦だけは立って迎えるよ</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.normal[3]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.normal[2]</t>
+          <t xml:space="preserve">preFinal.composed.normal[3]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -9010,14 +9010,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人の手柄にするつもりはない。これは、三人の勝利だ</t>
+          <t xml:space="preserve">…傷は数えきれない。まあ、最後まで残った証だと思えばいいよ</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.normal[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -9027,12 +9027,12 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.composed.normal[1]</t>
+          <t xml:space="preserve">preMatch.composed.normal[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -9042,14 +9042,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">個人の栄誉は受け取る。だが……これで満足する理由にはならない</t>
+          <t xml:space="preserve">…相手は選べない。来た順に、真っ向から受けるだけだよ</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.normal[2]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -9059,12 +9059,12 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.composed.normal[2]</t>
+          <t xml:space="preserve">preMatch.composed.normal[2]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -9074,14 +9074,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次がある。その時は、チーム全員で最後に立つ</t>
+          <t xml:space="preserve">…焦らない。目の前の一人に集中する。それでリングは渡さない</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.normal[3]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -9091,12 +9091,12 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.composed.normal[1]</t>
+          <t xml:space="preserve">preMatch.composed.normal[3]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -9106,14 +9106,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体は限界を告げている。それでも……最後の一人を見届けるまで、退けなかった</t>
+          <t xml:space="preserve">…この一戦から、始まる。落ち着いていこうか</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.normal[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.composed.normal[2]</t>
+          <t xml:space="preserve">survivor.composed.normal[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9138,14 +9138,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何度か意識が揺れた。だが、リングを降りる理由にはならなかった</t>
+          <t xml:space="preserve">…一人片づけた。息は上がってるけど、退く理由はないよ。次、来なよ</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.composed.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.normal[2]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.normal[1]</t>
+          <t xml:space="preserve">survivor.composed.normal[2]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9170,14 +9170,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…優勝か。…悪くないね。…次も行こう</t>
+          <t xml:space="preserve">…まだ足は動く。このリングは渡さない。次は誰だ</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.composed.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.normal[3]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9187,12 +9187,12 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.composed.normal[1]</t>
+          <t xml:space="preserve">survivor.composed.normal[3]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9202,14 +9202,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ足りないか。…次までに詰めよう</t>
+          <t xml:space="preserve">…ふぅ。まだ立ってる。この場所、そう簡単には空けないよ。次</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.composed.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.normal[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.composed.normal[1]</t>
+          <t xml:space="preserve">champion.composed.normal[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9234,14 +9234,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一つ勝ち。…次もこの調子で</t>
+          <t xml:space="preserve">三人で繋いだ結果だ。誰が欠けても……この景色はなかった</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.composed.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.normal[2]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.composed.normal[1]</t>
+          <t xml:space="preserve">champion.composed.normal[2]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9266,14 +9266,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くなかったね。…いい経験になった</t>
+          <t xml:space="preserve">一人の手柄にするつもりはない。これは、三人の勝利だ</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.composed.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.normal[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9283,12 +9283,12 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.normal[1]</t>
+          <t xml:space="preserve">defiant.composed.normal[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9298,14 +9298,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…決勝か。…全部出し切るよ</t>
+          <t xml:space="preserve">個人の栄誉は受け取る。だが……これで満足する理由にはならない</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.normal[2]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9315,12 +9315,12 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.normal[1]</t>
+          <t xml:space="preserve">defiant.composed.normal[2]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9330,14 +9330,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いつも通りやるよ</t>
+          <t xml:space="preserve">次がある。その時は、チーム全員で最後に立つ</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.normal[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9347,12 +9347,12 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.normal[2]</t>
+          <t xml:space="preserve">gauntlet.composed.normal[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9362,14 +9362,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…集中。…行こうか</t>
+          <t xml:space="preserve">身体は限界を告げている。それでも……最後の一人を見届けるまで、退けなかった</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.normal[2]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.composed.normal[1]</t>
+          <t xml:space="preserve">gauntlet.composed.normal[2]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9394,14 +9394,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…出るよ。…やるだけだね</t>
+          <t xml:space="preserve">何度か意識が揺れた。だが、リングを降りる理由にはならなかった</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.composed.normal[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.composed.normal[2]</t>
+          <t xml:space="preserve">champion.composed.normal[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9426,14 +9426,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なるほど。じゃあ、行こうか</t>
+          <t xml:space="preserve">…優勝か。…悪くないね。…次も行こう</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.composed.normal[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[1]</t>
+          <t xml:space="preserve">postLose.composed.normal[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9458,14 +9458,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい舞台だね。…全力で行くよ</t>
+          <t xml:space="preserve">…まだ足りないか。…次までに詰めよう</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.composed.normal[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9475,12 +9475,12 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[2]</t>
+          <t xml:space="preserve">postMatchWin.composed.normal[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9490,14 +9490,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…負けるつもりはないよ。よろしく</t>
+          <t xml:space="preserve">…一つ勝ち。…次もこの調子で</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.composed.normal[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[1]</t>
+          <t xml:space="preserve">postWin.composed.normal[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9522,14 +9522,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やったよ。…ここまで来れたか</t>
+          <t xml:space="preserve">…悪くなかったね。…いい経験になった</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.composed.normal[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[2]</t>
+          <t xml:space="preserve">preFinal.composed.normal[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9554,14 +9554,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くない結末だね。みんな、ありがとう</t>
+          <t xml:space="preserve">…決勝か。…全部出し切るよ</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.normal[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[1]</t>
+          <t xml:space="preserve">preMatch.composed.normal[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9586,14 +9586,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そちらの実力、確かめさせてもらうよ</t>
+          <t xml:space="preserve">…いつも通りやるよ</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.normal[2]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[2]</t>
+          <t xml:space="preserve">preMatch.composed.normal[2]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9618,14 +9618,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…本気で来なよ。受けて立つから</t>
+          <t xml:space="preserve">…集中。…行こうか</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.normal[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[1]</t>
+          <t xml:space="preserve">summon.composed.normal[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9650,14 +9650,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうか。そんな時もあるね</t>
+          <t xml:space="preserve">…出るよ。…やるだけだね</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.normal[2]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9667,12 +9667,12 @@
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[2]</t>
+          <t xml:space="preserve">summon.composed.normal[2]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9682,14 +9682,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、そういうこともあるか</t>
+          <t xml:space="preserve">…なるほど。じゃあ、行こうか</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.composed.normal[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9699,12 +9699,12 @@
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.composed.normal[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9714,14 +9714,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…負けたか。…次は違う結果にする</t>
+          <t xml:space="preserve">…いい舞台だね。…全力で行くよ</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.composed.normal[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.normal[2]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.composed.normal[1]</t>
+          <t xml:space="preserve">composed.normal[2]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9746,14 +9746,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝ったね。…いい対抗戦だった</t>
+          <t xml:space="preserve">…負けるつもりはないよ。よろしく</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.composed.normal[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.normal[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="12">
@@ -9778,14 +9778,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…団体の看板、守れたかな。…悪くないね</t>
+          <t xml:space="preserve">…やったよ。…ここまで来れたか</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.composed.normal[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.normal[2]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="12">
@@ -9810,14 +9810,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝った。…うちの力を見せられたと思う</t>
+          <t xml:space="preserve">…悪くない結末だね。みんな、ありがとう</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.composed.normal[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.normal[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9827,29 +9827,29 @@
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.composed.normal[1]</t>
+          <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここまで来れたか。…悪くない景色だね</t>
+          <t xml:space="preserve">…そちらの実力、確かめさせてもらうよ</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.composed.normal[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.normal[2]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9859,59 +9859,315 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.normal[1]</t>
+          <t xml:space="preserve">composed.normal[2]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…また名前を呼ばれる場所ができた。悪くないよ</t>
+          <t xml:space="preserve">…本気で来なよ。受けて立つから</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.normal[1]</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.normal[1]</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…そうか。そんな時もあるね</t>
+        </is>
+      </c>
+    </row>
+    <row r="297" ht="40" customHeight="1">
+      <c r="A297" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.normal[2]</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.normal[2]</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…まあ、そういうこともあるか</t>
+        </is>
+      </c>
+    </row>
+    <row r="298" ht="40" customHeight="1">
+      <c r="A298" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.composed.normal[1]</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.composed.normal[1]</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…負けたか。…次は違う結果にする</t>
+        </is>
+      </c>
+    </row>
+    <row r="299" ht="40" customHeight="1">
+      <c r="A299" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.composed.normal[1]</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.composed.normal[1]</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…勝ったね。…いい対抗戦だった</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="40" customHeight="1">
+      <c r="A300" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.composed.normal[1]</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.normal[1]</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…団体の看板、守れたかな。…悪くないね</t>
+        </is>
+      </c>
+    </row>
+    <row r="301" ht="40" customHeight="1">
+      <c r="A301" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.composed.normal[2]</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.normal[2]</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…勝った。…うちの力を見せられたと思う</t>
+        </is>
+      </c>
+    </row>
+    <row r="302" ht="40" customHeight="1">
+      <c r="A302" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.composed.normal[1]</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.composed.normal[1]</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ここまで来れたか。…悪くない景色だね</t>
+        </is>
+      </c>
+    </row>
+    <row r="303" ht="40" customHeight="1">
+      <c r="A303" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.composed.normal[1]</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.normal[1]</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…また名前を呼ばれる場所ができた。悪くないよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="304" ht="40" customHeight="1">
+      <c r="A304" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.composed.normal[1]</t>
         </is>
       </c>
-      <c r="B296" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr" s="2">
+      <c r="B304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr" s="12">
+      <c r="D304" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">composed.normal[1]</t>
         </is>
       </c>
-      <c r="E296" t="inlineStr" s="2">
+      <c r="E304" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F296" t="inlineStr" s="3">
+      <c r="F304" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…見込まれたなら、応えるだけだよ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H296"/>
+  <autoFilter ref="A1:H304"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/鷹揚×ノーマル.xlsx
+++ b/セリフ編集/キャラタイプ別/鷹揚×ノーマル.xlsx
@@ -2574,7 +2574,7 @@
       </c>
       <c r="F67" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。……頼みがあります。あの人と、やらせてください。</t>
+          <t xml:space="preserve">社長。……頼みがあります。三人で、あちらへ行かせてください。</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="F68" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人と、一度やってみたい。……それだけなんです。</t>
+          <t xml:space="preserve">三人で、一度あちらへ乗り込みたい。……それだけなんです。</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="F69" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">無茶を言ってる自覚はあります。……それでも、お願いします。</t>
+          <t xml:space="preserve">無茶を言ってる自覚はあります。……それでも、三人で行かせてください。</t>
         </is>
       </c>
     </row>
